--- a/docs/ISO7200_A3_圖框標題欄範本_4.xlsx
+++ b/docs/ISO7200_A3_圖框標題欄範本_4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jason_m3max/Documents/ClaudeCodeDev/qet-mcp/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AFD3FC7F-4197-2547-A8B2-A397DD9986A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1860CA96-9314-1745-81B2-7AF7B65087B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1000" yWindow="600" windowWidth="45080" windowHeight="25320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="141">
   <si>
     <t>A</t>
   </si>
@@ -108,35 +108,34 @@
     <t>正式發行 Released</t>
   </si>
   <si>
+    <t>文件識別號 Identification number *</t>
+  </si>
+  <si>
+    <t>圖名 Title</t>
+  </si>
+  <si>
+    <t>HC-2026-001-&amp;EFS-001</t>
+  </si>
+  <si>
+    <t>○○○機 控制迴路圖  Control circuit diagram</t>
+  </si>
+  <si>
+    <t>補充圖名 Supplementary title</t>
+  </si>
+  <si>
+    <t>主迴路／控制迴路 Main &amp; control circuits</t>
+  </si>
+  <si>
     <t>法定所有者 Legal owner *</t>
   </si>
   <si>
-    <t>圖名 Title</t>
-  </si>
-  <si>
-    <t>虎承科技
-Huchen Technology</t>
-  </si>
-  <si>
-    <t>○○○機 控制迴路圖  Control circuit diagram</t>
-  </si>
-  <si>
-    <t>補充圖名 Supplementary title</t>
-  </si>
-  <si>
-    <t>主迴路／控制迴路 Main &amp; control circuits</t>
-  </si>
-  <si>
-    <t>文件識別號 Identification number *</t>
-  </si>
-  <si>
     <t>頁次 Sheet *</t>
   </si>
   <si>
     <t>圖幅 Size</t>
   </si>
   <si>
-    <t>HC-2026-E001-&amp;EFS-001</t>
+    <t>虎承科技  Huchen Technology</t>
   </si>
   <si>
     <t>1 / 10</t>
@@ -151,7 +150,7 @@
     <t>欄位說明（本區位於圖框外，不在列印範圍內）　必要性依 ISO 7200：強制＝必填（圖框內以 * 標示）、建議＝選用、配套＝相關標準要求</t>
   </si>
   <si>
-    <t>建議寬度單位 mm。ISO 7200 唯一硬性尺寸為標題欄總寬 ≤180 mm（配合 A4 直式裝訂裁切）；內部分割標準未強制，下列為依本範本配置換算之建議值，各行寬度合計 = 180。一般欄位高度（含標籤）建議 9。</t>
+    <t>建議寬度單位 px，換算基準 4 px＝1 mm（QET 10 px 網格＝2.5 mm）。ISO 7200 唯一硬性尺寸為標題欄總寬 ≤180 mm＝720 px；各橫排寬度合計＝720。一般欄位高度（含標籤）建議 36 px（9 mm）；欄位上方小標籤字體建議 7 pt。</t>
   </si>
   <si>
     <t>欄位</t>
@@ -160,7 +159,10 @@
     <t>必要性</t>
   </si>
   <si>
-    <t>建議寬度 mm</t>
+    <t>建議寬度 px</t>
+  </si>
+  <si>
+    <t>建議字體</t>
   </si>
   <si>
     <t>說明</t>
@@ -172,123 +174,150 @@
     <t>強制</t>
   </si>
   <si>
-    <t>65</t>
+    <t>460</t>
+  </si>
+  <si>
+    <t>14 pt 粗體</t>
+  </si>
+  <si>
+    <t>圖面法律上的所有者（公司名稱或標誌），代表版權與責任歸屬。欄高建議 ≥60 px。</t>
+  </si>
+  <si>
+    <t>文件識別號 Identification number</t>
+  </si>
+  <si>
+    <t>260</t>
+  </si>
+  <si>
+    <t>11–12 pt 粗體</t>
+  </si>
+  <si>
+    <t>在該所有者範圍內必須唯一；建議內含 IEC 61355 文件分類碼（DCC）。欄高建議 ≥60 px。</t>
+  </si>
+  <si>
+    <t>發行日期 Date of issue</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>10 pt 粗體</t>
+  </si>
+  <si>
+    <t>文件正式發行（非繪製）日期，法律追溯依據；建議 ISO 8601 格式（YYYY-MM-DD）。</t>
+  </si>
+  <si>
+    <t>頁次 Sheet</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>本頁編號，建議同時標示總頁數（x / y）。</t>
+  </si>
+  <si>
+    <t>建議</t>
+  </si>
+  <si>
+    <t>描述文件內容的主標題。欄高建議 ≥48 px。</t>
+  </si>
+  <si>
+    <t>10 pt</t>
+  </si>
+  <si>
+    <t>對主標題的補充說明。</t>
+  </si>
+  <si>
+    <t>版次代號，須與上方修訂記錄欄對應；查驗重點。</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>依 IEC 61355 文件分類碼，電氣領域為 E 開頭，電路圖為 &amp;EFS。</t>
+  </si>
+  <si>
+    <t>草稿／審核中／正式發行／作廢等生命週期狀態。</t>
+  </si>
+  <si>
+    <t>圖面繪製人員。</t>
+  </si>
+  <si>
+    <t>審核 Checked by／核准 Approved by</t>
+  </si>
+  <si>
+    <t>各 160</t>
+  </si>
+  <si>
+    <t>審核與核准簽署；CE 技術文件要求可追溯的簽核紀錄。</t>
+  </si>
+  <si>
+    <t>圖面技術問題的聯絡窗口。</t>
+  </si>
+  <si>
+    <t>依 ISO 5457 圖紙規格。</t>
+  </si>
+  <si>
+    <t>其他補充資訊。</t>
+  </si>
+  <si>
+    <t>修訂記錄欄（標題欄上方表格）</t>
+  </si>
+  <si>
+    <t>配套</t>
+  </si>
+  <si>
+    <t>720</t>
+  </si>
+  <si>
+    <t>表頭 7 pt／內容 8 pt</t>
+  </si>
+  <si>
+    <t>與標題欄同寬；內部建議：版次 50／日期 100／修改內容 430／修改人 70／核准 70，列高 30 px。</t>
+  </si>
+  <si>
+    <t>頁緣座標網格（1–8／A–F）</t>
+  </si>
+  <si>
+    <t>格距約 200</t>
+  </si>
+  <si>
+    <t>依 ISO 5457；A3 橫式 8 欄（1680÷8＝210）× 6 列（1188÷6＝198），邊條寬 40 px。</t>
+  </si>
+  <si>
+    <t>首次發行</t>
+  </si>
+  <si>
+    <t>○○○機 控制迴路圖</t>
+  </si>
+  <si>
+    <t>主迴路／控制迴路</t>
+  </si>
+  <si>
+    <t>全寬底欄版（A3 內寬 400 mm＝1600 px，4 px＝1 mm；底帶高 240 px，上下兩層各 120 px，修訂記錄欄跨全高）。左區 修訂記錄欄 520 px：版次 80／日期 120／修改內容 160／修改人 80／核准 80，表頭 7 pt、內容 8 pt，列高 30 px。上層 1080 px：修訂索引 120／文件類別 120／技術參考 160／繪製 160／審核 120／核准 120／文件狀態 160／發行日期 120，標籤 7 pt、值 10 pt（修訂索引與發行日期粗體），欄高 120 px。下層 1080 px：法定所有者 320（14 pt 粗體，高 120）／文件識別號 240（11 pt 粗體，高 120）／圖名 280（10 pt 粗體，高 60）＋補充圖名 280（10 pt，高 60）／頁次 120＋圖幅 120（10 pt，高 60）／備註 240（10 pt，高 60）。</t>
+  </si>
+  <si>
+    <t>欄位（中文）</t>
+  </si>
+  <si>
+    <t>Field (EN)</t>
+  </si>
+  <si>
+    <t>ISO 7200 屬性</t>
+  </si>
+  <si>
+    <t>範例</t>
+  </si>
+  <si>
+    <t>法定所有者</t>
+  </si>
+  <si>
+    <t>Legal owner</t>
   </si>
   <si>
     <t>圖面法律上的所有者（公司名稱或標誌），代表版權與責任歸屬。</t>
   </si>
   <si>
-    <t>文件識別號 Identification number</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>在該所有者範圍內必須唯一；建議內含 IEC 61355 文件分類碼（DCC）。欄高建議 ≥15，字高 ≥5。</t>
-  </si>
-  <si>
-    <t>發行日期 Date of issue</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>文件正式發行（非繪製）日期，法律追溯依據；建議 ISO 8601 格式（YYYY-MM-DD）。</t>
-  </si>
-  <si>
-    <t>頁次 Sheet</t>
-  </si>
-  <si>
-    <t>本頁編號，建議同時標示總頁數（x / y）。</t>
-  </si>
-  <si>
-    <t>建議</t>
-  </si>
-  <si>
-    <t>描述文件內容的主標題。欄高建議 ≥12。</t>
-  </si>
-  <si>
-    <t>對主標題的補充說明。</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>版次代號，須與上方修訂記錄欄對應；查驗重點。</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>依 IEC 61355 文件分類碼，電氣領域為 E 開頭，電路圖為 &amp;EFS。</t>
-  </si>
-  <si>
-    <t>草稿／審核中／正式發行／作廢等生命週期狀態。</t>
-  </si>
-  <si>
-    <t>圖面繪製人員。</t>
-  </si>
-  <si>
-    <t>審核 Checked by／核准 Approved by</t>
-  </si>
-  <si>
-    <t>各 41</t>
-  </si>
-  <si>
-    <t>審核與核准簽署；CE 技術文件要求可追溯的簽核紀錄。</t>
-  </si>
-  <si>
-    <t>圖面技術問題的聯絡窗口。</t>
-  </si>
-  <si>
-    <t>依 ISO 5457 圖紙規格。</t>
-  </si>
-  <si>
-    <t>其他補充資訊。</t>
-  </si>
-  <si>
-    <t>修訂記錄欄（標題欄上方表格）</t>
-  </si>
-  <si>
-    <t>配套</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>與標題欄同寬；內部建議：版次 12／日期 25／修改內容 110／修改人 17／核准 16，列高 7。</t>
-  </si>
-  <si>
-    <t>頁緣座標網格（1–8／A–F）</t>
-  </si>
-  <si>
-    <t>格距約 50</t>
-  </si>
-  <si>
-    <t>依 ISO 5457；A3 橫式 8 欄（420÷8≈52.5）× 6 列（297÷6≈49.5），邊條寬 10。</t>
-  </si>
-  <si>
-    <t>全寬底欄版：底部橫帶佔滿圖框內寬（A3 內寬 400 mm）。右側標題欄維持 ISO 7200 ≤180 mm；左側為修訂記錄欄（寬 220 mm），內部建議寬度：版次 20／日期 33／修改內容 115／修改人 25／核准 27，列高 7。標題欄各欄位說明與建議寬度詳見「A3圖框範本」工作表下方之欄位說明表。</t>
-  </si>
-  <si>
-    <t>欄位（中文）</t>
-  </si>
-  <si>
-    <t>Field (EN)</t>
-  </si>
-  <si>
-    <t>ISO 7200 屬性</t>
-  </si>
-  <si>
-    <t>範例</t>
-  </si>
-  <si>
-    <t>法定所有者</t>
-  </si>
-  <si>
-    <t>Legal owner</t>
-  </si>
-  <si>
     <t>虎承科技 Huchen Technology</t>
   </si>
   <si>
@@ -335,9 +364,6 @@
   </si>
   <si>
     <t>Supplementary title</t>
-  </si>
-  <si>
-    <t>主迴路／控制迴路</t>
   </si>
   <si>
     <t>修訂索引</t>
@@ -434,7 +460,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -479,6 +505,12 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -543,7 +575,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="51">
+  <borders count="54">
     <border>
       <left/>
       <right/>
@@ -1005,10 +1037,10 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1018,6 +1050,26 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
@@ -1131,11 +1183,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
@@ -1161,38 +1224,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1202,23 +1265,26 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1229,14 +1295,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1247,14 +1313,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
@@ -1262,23 +1328,20 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1289,9 +1352,28 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1662,7 +1744,7 @@
       <c r="AO1" s="39"/>
     </row>
     <row r="2" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="33" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1"/>
@@ -1705,12 +1787,12 @@
       <c r="AM2" s="2"/>
       <c r="AN2" s="2"/>
       <c r="AO2" s="3"/>
-      <c r="AP2" s="34" t="s">
+      <c r="AP2" s="33" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A3" s="35"/>
+      <c r="A3" s="34"/>
       <c r="B3" s="4"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -1751,10 +1833,10 @@
       <c r="AM3" s="5"/>
       <c r="AN3" s="5"/>
       <c r="AO3" s="6"/>
-      <c r="AP3" s="35"/>
+      <c r="AP3" s="34"/>
     </row>
     <row r="4" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A4" s="35"/>
+      <c r="A4" s="34"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -1795,10 +1877,10 @@
       <c r="AM4" s="5"/>
       <c r="AN4" s="5"/>
       <c r="AO4" s="6"/>
-      <c r="AP4" s="35"/>
+      <c r="AP4" s="34"/>
     </row>
     <row r="5" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A5" s="35"/>
+      <c r="A5" s="34"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -1839,10 +1921,10 @@
       <c r="AM5" s="5"/>
       <c r="AN5" s="5"/>
       <c r="AO5" s="6"/>
-      <c r="AP5" s="35"/>
+      <c r="AP5" s="34"/>
     </row>
     <row r="6" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A6" s="35"/>
+      <c r="A6" s="34"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -1883,10 +1965,10 @@
       <c r="AM6" s="5"/>
       <c r="AN6" s="5"/>
       <c r="AO6" s="6"/>
-      <c r="AP6" s="35"/>
+      <c r="AP6" s="34"/>
     </row>
     <row r="7" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A7" s="35"/>
+      <c r="A7" s="34"/>
       <c r="B7" s="4"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -1927,10 +2009,10 @@
       <c r="AM7" s="5"/>
       <c r="AN7" s="5"/>
       <c r="AO7" s="6"/>
-      <c r="AP7" s="35"/>
+      <c r="AP7" s="34"/>
     </row>
     <row r="8" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A8" s="35"/>
+      <c r="A8" s="34"/>
       <c r="B8" s="4"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -1971,10 +2053,10 @@
       <c r="AM8" s="5"/>
       <c r="AN8" s="5"/>
       <c r="AO8" s="6"/>
-      <c r="AP8" s="35"/>
+      <c r="AP8" s="34"/>
     </row>
     <row r="9" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A9" s="35"/>
+      <c r="A9" s="34"/>
       <c r="B9" s="4"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -2015,10 +2097,10 @@
       <c r="AM9" s="5"/>
       <c r="AN9" s="5"/>
       <c r="AO9" s="6"/>
-      <c r="AP9" s="35"/>
+      <c r="AP9" s="34"/>
     </row>
     <row r="10" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A10" s="35"/>
+      <c r="A10" s="34"/>
       <c r="B10" s="4"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -2059,10 +2141,10 @@
       <c r="AM10" s="5"/>
       <c r="AN10" s="5"/>
       <c r="AO10" s="6"/>
-      <c r="AP10" s="35"/>
+      <c r="AP10" s="34"/>
     </row>
     <row r="11" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A11" s="36"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="4"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -2103,10 +2185,10 @@
       <c r="AM11" s="5"/>
       <c r="AN11" s="5"/>
       <c r="AO11" s="6"/>
-      <c r="AP11" s="36"/>
+      <c r="AP11" s="35"/>
     </row>
     <row r="12" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="33" t="s">
         <v>1</v>
       </c>
       <c r="B12" s="4"/>
@@ -2149,12 +2231,12 @@
       <c r="AM12" s="5"/>
       <c r="AN12" s="5"/>
       <c r="AO12" s="6"/>
-      <c r="AP12" s="34" t="s">
+      <c r="AP12" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A13" s="35"/>
+      <c r="A13" s="34"/>
       <c r="B13" s="4"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
@@ -2195,10 +2277,10 @@
       <c r="AM13" s="5"/>
       <c r="AN13" s="5"/>
       <c r="AO13" s="6"/>
-      <c r="AP13" s="35"/>
+      <c r="AP13" s="34"/>
     </row>
     <row r="14" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A14" s="35"/>
+      <c r="A14" s="34"/>
       <c r="B14" s="4"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -2239,10 +2321,10 @@
       <c r="AM14" s="5"/>
       <c r="AN14" s="5"/>
       <c r="AO14" s="6"/>
-      <c r="AP14" s="35"/>
+      <c r="AP14" s="34"/>
     </row>
     <row r="15" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A15" s="35"/>
+      <c r="A15" s="34"/>
       <c r="B15" s="4"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -2283,10 +2365,10 @@
       <c r="AM15" s="5"/>
       <c r="AN15" s="5"/>
       <c r="AO15" s="6"/>
-      <c r="AP15" s="35"/>
+      <c r="AP15" s="34"/>
     </row>
     <row r="16" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A16" s="35"/>
+      <c r="A16" s="34"/>
       <c r="B16" s="4"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -2327,10 +2409,10 @@
       <c r="AM16" s="5"/>
       <c r="AN16" s="5"/>
       <c r="AO16" s="6"/>
-      <c r="AP16" s="35"/>
+      <c r="AP16" s="34"/>
     </row>
     <row r="17" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A17" s="35"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
@@ -2371,10 +2453,10 @@
       <c r="AM17" s="5"/>
       <c r="AN17" s="5"/>
       <c r="AO17" s="6"/>
-      <c r="AP17" s="35"/>
+      <c r="AP17" s="34"/>
     </row>
     <row r="18" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A18" s="35"/>
+      <c r="A18" s="34"/>
       <c r="B18" s="4"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -2415,10 +2497,10 @@
       <c r="AM18" s="5"/>
       <c r="AN18" s="5"/>
       <c r="AO18" s="6"/>
-      <c r="AP18" s="35"/>
+      <c r="AP18" s="34"/>
     </row>
     <row r="19" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A19" s="35"/>
+      <c r="A19" s="34"/>
       <c r="B19" s="4"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
@@ -2459,10 +2541,10 @@
       <c r="AM19" s="5"/>
       <c r="AN19" s="5"/>
       <c r="AO19" s="6"/>
-      <c r="AP19" s="35"/>
+      <c r="AP19" s="34"/>
     </row>
     <row r="20" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A20" s="35"/>
+      <c r="A20" s="34"/>
       <c r="B20" s="4"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
@@ -2471,32 +2553,32 @@
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
-      <c r="J20" s="60" t="s">
+      <c r="J20" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="K20" s="59"/>
-      <c r="L20" s="59"/>
-      <c r="M20" s="59"/>
-      <c r="N20" s="59"/>
-      <c r="O20" s="59"/>
-      <c r="P20" s="59"/>
-      <c r="Q20" s="59"/>
-      <c r="R20" s="59"/>
-      <c r="S20" s="59"/>
-      <c r="T20" s="59"/>
-      <c r="U20" s="59"/>
-      <c r="V20" s="59"/>
-      <c r="W20" s="59"/>
-      <c r="X20" s="59"/>
-      <c r="Y20" s="59"/>
-      <c r="Z20" s="59"/>
-      <c r="AA20" s="59"/>
-      <c r="AB20" s="59"/>
-      <c r="AC20" s="59"/>
-      <c r="AD20" s="59"/>
-      <c r="AE20" s="59"/>
-      <c r="AF20" s="59"/>
-      <c r="AG20" s="59"/>
+      <c r="K20" s="60"/>
+      <c r="L20" s="60"/>
+      <c r="M20" s="60"/>
+      <c r="N20" s="60"/>
+      <c r="O20" s="60"/>
+      <c r="P20" s="60"/>
+      <c r="Q20" s="60"/>
+      <c r="R20" s="60"/>
+      <c r="S20" s="60"/>
+      <c r="T20" s="60"/>
+      <c r="U20" s="60"/>
+      <c r="V20" s="60"/>
+      <c r="W20" s="60"/>
+      <c r="X20" s="60"/>
+      <c r="Y20" s="60"/>
+      <c r="Z20" s="60"/>
+      <c r="AA20" s="60"/>
+      <c r="AB20" s="60"/>
+      <c r="AC20" s="60"/>
+      <c r="AD20" s="60"/>
+      <c r="AE20" s="60"/>
+      <c r="AF20" s="60"/>
+      <c r="AG20" s="60"/>
       <c r="AH20" s="5"/>
       <c r="AI20" s="5"/>
       <c r="AJ20" s="5"/>
@@ -2505,10 +2587,10 @@
       <c r="AM20" s="5"/>
       <c r="AN20" s="5"/>
       <c r="AO20" s="6"/>
-      <c r="AP20" s="35"/>
+      <c r="AP20" s="34"/>
     </row>
     <row r="21" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A21" s="36"/>
+      <c r="A21" s="35"/>
       <c r="B21" s="4"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
@@ -2517,30 +2599,30 @@
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
-      <c r="J21" s="59"/>
-      <c r="K21" s="59"/>
-      <c r="L21" s="59"/>
-      <c r="M21" s="59"/>
-      <c r="N21" s="59"/>
-      <c r="O21" s="59"/>
-      <c r="P21" s="59"/>
-      <c r="Q21" s="59"/>
-      <c r="R21" s="59"/>
-      <c r="S21" s="59"/>
-      <c r="T21" s="59"/>
-      <c r="U21" s="59"/>
-      <c r="V21" s="59"/>
-      <c r="W21" s="59"/>
-      <c r="X21" s="59"/>
-      <c r="Y21" s="59"/>
-      <c r="Z21" s="59"/>
-      <c r="AA21" s="59"/>
-      <c r="AB21" s="59"/>
-      <c r="AC21" s="59"/>
-      <c r="AD21" s="59"/>
-      <c r="AE21" s="59"/>
-      <c r="AF21" s="59"/>
-      <c r="AG21" s="59"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="60"/>
+      <c r="L21" s="60"/>
+      <c r="M21" s="60"/>
+      <c r="N21" s="60"/>
+      <c r="O21" s="60"/>
+      <c r="P21" s="60"/>
+      <c r="Q21" s="60"/>
+      <c r="R21" s="60"/>
+      <c r="S21" s="60"/>
+      <c r="T21" s="60"/>
+      <c r="U21" s="60"/>
+      <c r="V21" s="60"/>
+      <c r="W21" s="60"/>
+      <c r="X21" s="60"/>
+      <c r="Y21" s="60"/>
+      <c r="Z21" s="60"/>
+      <c r="AA21" s="60"/>
+      <c r="AB21" s="60"/>
+      <c r="AC21" s="60"/>
+      <c r="AD21" s="60"/>
+      <c r="AE21" s="60"/>
+      <c r="AF21" s="60"/>
+      <c r="AG21" s="60"/>
       <c r="AH21" s="5"/>
       <c r="AI21" s="5"/>
       <c r="AJ21" s="5"/>
@@ -2549,10 +2631,10 @@
       <c r="AM21" s="5"/>
       <c r="AN21" s="5"/>
       <c r="AO21" s="6"/>
-      <c r="AP21" s="36"/>
+      <c r="AP21" s="35"/>
     </row>
     <row r="22" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A22" s="34" t="s">
+      <c r="A22" s="33" t="s">
         <v>3</v>
       </c>
       <c r="B22" s="4"/>
@@ -2563,30 +2645,30 @@
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
-      <c r="J22" s="59"/>
-      <c r="K22" s="59"/>
-      <c r="L22" s="59"/>
-      <c r="M22" s="59"/>
-      <c r="N22" s="59"/>
-      <c r="O22" s="59"/>
-      <c r="P22" s="59"/>
-      <c r="Q22" s="59"/>
-      <c r="R22" s="59"/>
-      <c r="S22" s="59"/>
-      <c r="T22" s="59"/>
-      <c r="U22" s="59"/>
-      <c r="V22" s="59"/>
-      <c r="W22" s="59"/>
-      <c r="X22" s="59"/>
-      <c r="Y22" s="59"/>
-      <c r="Z22" s="59"/>
-      <c r="AA22" s="59"/>
-      <c r="AB22" s="59"/>
-      <c r="AC22" s="59"/>
-      <c r="AD22" s="59"/>
-      <c r="AE22" s="59"/>
-      <c r="AF22" s="59"/>
-      <c r="AG22" s="59"/>
+      <c r="J22" s="60"/>
+      <c r="K22" s="60"/>
+      <c r="L22" s="60"/>
+      <c r="M22" s="60"/>
+      <c r="N22" s="60"/>
+      <c r="O22" s="60"/>
+      <c r="P22" s="60"/>
+      <c r="Q22" s="60"/>
+      <c r="R22" s="60"/>
+      <c r="S22" s="60"/>
+      <c r="T22" s="60"/>
+      <c r="U22" s="60"/>
+      <c r="V22" s="60"/>
+      <c r="W22" s="60"/>
+      <c r="X22" s="60"/>
+      <c r="Y22" s="60"/>
+      <c r="Z22" s="60"/>
+      <c r="AA22" s="60"/>
+      <c r="AB22" s="60"/>
+      <c r="AC22" s="60"/>
+      <c r="AD22" s="60"/>
+      <c r="AE22" s="60"/>
+      <c r="AF22" s="60"/>
+      <c r="AG22" s="60"/>
       <c r="AH22" s="5"/>
       <c r="AI22" s="5"/>
       <c r="AJ22" s="5"/>
@@ -2595,12 +2677,12 @@
       <c r="AM22" s="5"/>
       <c r="AN22" s="5"/>
       <c r="AO22" s="6"/>
-      <c r="AP22" s="34" t="s">
+      <c r="AP22" s="33" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A23" s="35"/>
+      <c r="A23" s="34"/>
       <c r="B23" s="4"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
@@ -2641,10 +2723,10 @@
       <c r="AM23" s="5"/>
       <c r="AN23" s="5"/>
       <c r="AO23" s="6"/>
-      <c r="AP23" s="35"/>
+      <c r="AP23" s="34"/>
     </row>
     <row r="24" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A24" s="35"/>
+      <c r="A24" s="34"/>
       <c r="B24" s="4"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
@@ -2685,10 +2767,10 @@
       <c r="AM24" s="5"/>
       <c r="AN24" s="5"/>
       <c r="AO24" s="6"/>
-      <c r="AP24" s="35"/>
+      <c r="AP24" s="34"/>
     </row>
     <row r="25" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A25" s="35"/>
+      <c r="A25" s="34"/>
       <c r="B25" s="4"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
@@ -2729,10 +2811,10 @@
       <c r="AM25" s="5"/>
       <c r="AN25" s="5"/>
       <c r="AO25" s="6"/>
-      <c r="AP25" s="35"/>
+      <c r="AP25" s="34"/>
     </row>
     <row r="26" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A26" s="35"/>
+      <c r="A26" s="34"/>
       <c r="B26" s="4"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
@@ -2773,10 +2855,10 @@
       <c r="AM26" s="5"/>
       <c r="AN26" s="5"/>
       <c r="AO26" s="6"/>
-      <c r="AP26" s="35"/>
+      <c r="AP26" s="34"/>
     </row>
     <row r="27" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A27" s="35"/>
+      <c r="A27" s="34"/>
       <c r="B27" s="4"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -2817,10 +2899,10 @@
       <c r="AM27" s="5"/>
       <c r="AN27" s="5"/>
       <c r="AO27" s="6"/>
-      <c r="AP27" s="35"/>
+      <c r="AP27" s="34"/>
     </row>
     <row r="28" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A28" s="35"/>
+      <c r="A28" s="34"/>
       <c r="B28" s="4"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -2861,10 +2943,10 @@
       <c r="AM28" s="5"/>
       <c r="AN28" s="5"/>
       <c r="AO28" s="6"/>
-      <c r="AP28" s="35"/>
+      <c r="AP28" s="34"/>
     </row>
     <row r="29" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A29" s="35"/>
+      <c r="A29" s="34"/>
       <c r="B29" s="4"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
@@ -2905,10 +2987,10 @@
       <c r="AM29" s="5"/>
       <c r="AN29" s="5"/>
       <c r="AO29" s="6"/>
-      <c r="AP29" s="35"/>
+      <c r="AP29" s="34"/>
     </row>
     <row r="30" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A30" s="35"/>
+      <c r="A30" s="34"/>
       <c r="B30" s="4"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -2949,10 +3031,10 @@
       <c r="AM30" s="5"/>
       <c r="AN30" s="5"/>
       <c r="AO30" s="6"/>
-      <c r="AP30" s="35"/>
+      <c r="AP30" s="34"/>
     </row>
     <row r="31" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A31" s="36"/>
+      <c r="A31" s="35"/>
       <c r="B31" s="4"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -2993,10 +3075,10 @@
       <c r="AM31" s="5"/>
       <c r="AN31" s="5"/>
       <c r="AO31" s="6"/>
-      <c r="AP31" s="36"/>
+      <c r="AP31" s="35"/>
     </row>
     <row r="32" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A32" s="34" t="s">
+      <c r="A32" s="33" t="s">
         <v>4</v>
       </c>
       <c r="B32" s="4"/>
@@ -3039,12 +3121,12 @@
       <c r="AM32" s="5"/>
       <c r="AN32" s="5"/>
       <c r="AO32" s="6"/>
-      <c r="AP32" s="34" t="s">
+      <c r="AP32" s="33" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A33" s="35"/>
+      <c r="A33" s="34"/>
       <c r="B33" s="4"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -3085,10 +3167,10 @@
       <c r="AM33" s="5"/>
       <c r="AN33" s="5"/>
       <c r="AO33" s="6"/>
-      <c r="AP33" s="35"/>
+      <c r="AP33" s="34"/>
     </row>
     <row r="34" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A34" s="35"/>
+      <c r="A34" s="34"/>
       <c r="B34" s="4"/>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
@@ -3129,10 +3211,10 @@
       <c r="AM34" s="5"/>
       <c r="AN34" s="5"/>
       <c r="AO34" s="6"/>
-      <c r="AP34" s="35"/>
+      <c r="AP34" s="34"/>
     </row>
     <row r="35" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A35" s="35"/>
+      <c r="A35" s="34"/>
       <c r="B35" s="4"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
@@ -3173,10 +3255,10 @@
       <c r="AM35" s="5"/>
       <c r="AN35" s="5"/>
       <c r="AO35" s="6"/>
-      <c r="AP35" s="35"/>
+      <c r="AP35" s="34"/>
     </row>
     <row r="36" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A36" s="35"/>
+      <c r="A36" s="34"/>
       <c r="B36" s="4"/>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
@@ -3217,10 +3299,10 @@
       <c r="AM36" s="5"/>
       <c r="AN36" s="5"/>
       <c r="AO36" s="6"/>
-      <c r="AP36" s="35"/>
+      <c r="AP36" s="34"/>
     </row>
     <row r="37" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A37" s="35"/>
+      <c r="A37" s="34"/>
       <c r="B37" s="4"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
@@ -3261,10 +3343,10 @@
       <c r="AM37" s="5"/>
       <c r="AN37" s="5"/>
       <c r="AO37" s="6"/>
-      <c r="AP37" s="35"/>
+      <c r="AP37" s="34"/>
     </row>
     <row r="38" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A38" s="35"/>
+      <c r="A38" s="34"/>
       <c r="B38" s="4"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
@@ -3305,10 +3387,10 @@
       <c r="AM38" s="5"/>
       <c r="AN38" s="5"/>
       <c r="AO38" s="6"/>
-      <c r="AP38" s="35"/>
+      <c r="AP38" s="34"/>
     </row>
     <row r="39" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A39" s="35"/>
+      <c r="A39" s="34"/>
       <c r="B39" s="4"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
@@ -3349,10 +3431,10 @@
       <c r="AM39" s="5"/>
       <c r="AN39" s="5"/>
       <c r="AO39" s="6"/>
-      <c r="AP39" s="35"/>
+      <c r="AP39" s="34"/>
     </row>
     <row r="40" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A40" s="35"/>
+      <c r="A40" s="34"/>
       <c r="B40" s="4"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
@@ -3393,10 +3475,10 @@
       <c r="AM40" s="5"/>
       <c r="AN40" s="5"/>
       <c r="AO40" s="6"/>
-      <c r="AP40" s="35"/>
+      <c r="AP40" s="34"/>
     </row>
     <row r="41" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A41" s="36"/>
+      <c r="A41" s="35"/>
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
@@ -3437,10 +3519,10 @@
       <c r="AM41" s="5"/>
       <c r="AN41" s="5"/>
       <c r="AO41" s="6"/>
-      <c r="AP41" s="36"/>
+      <c r="AP41" s="35"/>
     </row>
     <row r="42" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A42" s="34" t="s">
+      <c r="A42" s="33" t="s">
         <v>5</v>
       </c>
       <c r="B42" s="4"/>
@@ -3483,12 +3565,12 @@
       <c r="AM42" s="5"/>
       <c r="AN42" s="5"/>
       <c r="AO42" s="6"/>
-      <c r="AP42" s="34" t="s">
+      <c r="AP42" s="33" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:42" ht="22" customHeight="1">
-      <c r="A43" s="35"/>
+      <c r="A43" s="34"/>
       <c r="B43" s="4"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
@@ -3507,42 +3589,42 @@
       <c r="Q43" s="5"/>
       <c r="R43" s="5"/>
       <c r="S43" s="5"/>
-      <c r="T43" s="51" t="s">
+      <c r="T43" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="U43" s="52"/>
-      <c r="V43" s="61" t="s">
+      <c r="U43" s="53"/>
+      <c r="V43" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="W43" s="62"/>
-      <c r="X43" s="62"/>
-      <c r="Y43" s="52"/>
-      <c r="Z43" s="61" t="s">
+      <c r="W43" s="63"/>
+      <c r="X43" s="63"/>
+      <c r="Y43" s="53"/>
+      <c r="Z43" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="AA43" s="62"/>
-      <c r="AB43" s="62"/>
-      <c r="AC43" s="62"/>
-      <c r="AD43" s="62"/>
-      <c r="AE43" s="62"/>
-      <c r="AF43" s="62"/>
-      <c r="AG43" s="62"/>
-      <c r="AH43" s="62"/>
-      <c r="AI43" s="52"/>
-      <c r="AJ43" s="61" t="s">
+      <c r="AA43" s="63"/>
+      <c r="AB43" s="63"/>
+      <c r="AC43" s="63"/>
+      <c r="AD43" s="63"/>
+      <c r="AE43" s="63"/>
+      <c r="AF43" s="63"/>
+      <c r="AG43" s="63"/>
+      <c r="AH43" s="63"/>
+      <c r="AI43" s="53"/>
+      <c r="AJ43" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="AK43" s="62"/>
-      <c r="AL43" s="52"/>
+      <c r="AK43" s="63"/>
+      <c r="AL43" s="53"/>
       <c r="AM43" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="AN43" s="62"/>
+      <c r="AN43" s="63"/>
       <c r="AO43" s="80"/>
-      <c r="AP43" s="35"/>
+      <c r="AP43" s="34"/>
     </row>
     <row r="44" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A44" s="35"/>
+      <c r="A44" s="34"/>
       <c r="B44" s="4"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
@@ -3591,10 +3673,10 @@
       <c r="AM44" s="9"/>
       <c r="AN44" s="10"/>
       <c r="AO44" s="11"/>
-      <c r="AP44" s="35"/>
+      <c r="AP44" s="34"/>
     </row>
     <row r="45" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A45" s="35"/>
+      <c r="A45" s="34"/>
       <c r="B45" s="4"/>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
@@ -3635,10 +3717,10 @@
       <c r="AM45" s="13"/>
       <c r="AN45" s="10"/>
       <c r="AO45" s="11"/>
-      <c r="AP45" s="35"/>
+      <c r="AP45" s="34"/>
     </row>
     <row r="46" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A46" s="35"/>
+      <c r="A46" s="34"/>
       <c r="B46" s="4"/>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
@@ -3679,10 +3761,10 @@
       <c r="AM46" s="13"/>
       <c r="AN46" s="10"/>
       <c r="AO46" s="11"/>
-      <c r="AP46" s="35"/>
+      <c r="AP46" s="34"/>
     </row>
     <row r="47" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A47" s="35"/>
+      <c r="A47" s="34"/>
       <c r="B47" s="4"/>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
@@ -3723,10 +3805,10 @@
       <c r="AM47" s="13"/>
       <c r="AN47" s="10"/>
       <c r="AO47" s="11"/>
-      <c r="AP47" s="35"/>
+      <c r="AP47" s="34"/>
     </row>
     <row r="48" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A48" s="35"/>
+      <c r="A48" s="34"/>
       <c r="B48" s="4"/>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
@@ -3767,10 +3849,10 @@
       <c r="AM48" s="13"/>
       <c r="AN48" s="10"/>
       <c r="AO48" s="11"/>
-      <c r="AP48" s="35"/>
+      <c r="AP48" s="34"/>
     </row>
     <row r="49" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A49" s="35"/>
+      <c r="A49" s="34"/>
       <c r="B49" s="4"/>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
@@ -3811,10 +3893,10 @@
       <c r="AM49" s="16"/>
       <c r="AN49" s="17"/>
       <c r="AO49" s="18"/>
-      <c r="AP49" s="35"/>
+      <c r="AP49" s="34"/>
     </row>
     <row r="50" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A50" s="35"/>
+      <c r="A50" s="34"/>
       <c r="B50" s="4"/>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
@@ -3833,29 +3915,29 @@
       <c r="Q50" s="5"/>
       <c r="R50" s="5"/>
       <c r="S50" s="5"/>
-      <c r="T50" s="54" t="s">
+      <c r="T50" s="55" t="s">
         <v>14</v>
       </c>
       <c r="U50" s="49"/>
       <c r="V50" s="49"/>
       <c r="W50" s="49"/>
       <c r="X50" s="49"/>
-      <c r="Y50" s="55"/>
-      <c r="Z50" s="72" t="s">
+      <c r="Y50" s="56"/>
+      <c r="Z50" s="73" t="s">
         <v>15</v>
       </c>
       <c r="AA50" s="49"/>
       <c r="AB50" s="49"/>
       <c r="AC50" s="49"/>
       <c r="AD50" s="49"/>
-      <c r="AE50" s="55"/>
-      <c r="AF50" s="72" t="s">
+      <c r="AE50" s="56"/>
+      <c r="AF50" s="73" t="s">
         <v>16</v>
       </c>
       <c r="AG50" s="49"/>
       <c r="AH50" s="49"/>
       <c r="AI50" s="49"/>
-      <c r="AJ50" s="55"/>
+      <c r="AJ50" s="56"/>
       <c r="AK50" s="48" t="s">
         <v>17</v>
       </c>
@@ -3863,10 +3945,10 @@
       <c r="AM50" s="49"/>
       <c r="AN50" s="49"/>
       <c r="AO50" s="50"/>
-      <c r="AP50" s="35"/>
+      <c r="AP50" s="34"/>
     </row>
     <row r="51" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A51" s="36"/>
+      <c r="A51" s="35"/>
       <c r="B51" s="4"/>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
@@ -3885,7 +3967,7 @@
       <c r="Q51" s="5"/>
       <c r="R51" s="5"/>
       <c r="S51" s="5"/>
-      <c r="T51" s="57" t="s">
+      <c r="T51" s="58" t="s">
         <v>13</v>
       </c>
       <c r="U51" s="25"/>
@@ -3906,15 +3988,15 @@
       <c r="AH51" s="25"/>
       <c r="AI51" s="25"/>
       <c r="AJ51" s="41"/>
-      <c r="AK51" s="71"/>
+      <c r="AK51" s="72"/>
       <c r="AL51" s="25"/>
       <c r="AM51" s="25"/>
       <c r="AN51" s="25"/>
       <c r="AO51" s="26"/>
-      <c r="AP51" s="36"/>
+      <c r="AP51" s="35"/>
     </row>
     <row r="52" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A52" s="34" t="s">
+      <c r="A52" s="33" t="s">
         <v>18</v>
       </c>
       <c r="B52" s="4"/>
@@ -3943,7 +4025,7 @@
       <c r="W52" s="43"/>
       <c r="X52" s="43"/>
       <c r="Y52" s="44"/>
-      <c r="Z52" s="73" t="s">
+      <c r="Z52" s="74" t="s">
         <v>20</v>
       </c>
       <c r="AA52" s="43"/>
@@ -3951,7 +4033,7 @@
       <c r="AC52" s="43"/>
       <c r="AD52" s="43"/>
       <c r="AE52" s="44"/>
-      <c r="AF52" s="73" t="s">
+      <c r="AF52" s="74" t="s">
         <v>21</v>
       </c>
       <c r="AG52" s="43"/>
@@ -3965,12 +4047,12 @@
       <c r="AM52" s="43"/>
       <c r="AN52" s="43"/>
       <c r="AO52" s="47"/>
-      <c r="AP52" s="34" t="s">
+      <c r="AP52" s="33" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="53" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A53" s="35"/>
+      <c r="A53" s="34"/>
       <c r="B53" s="4"/>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
@@ -3989,7 +4071,7 @@
       <c r="Q53" s="5"/>
       <c r="R53" s="5"/>
       <c r="S53" s="5"/>
-      <c r="T53" s="57" t="s">
+      <c r="T53" s="58" t="s">
         <v>23</v>
       </c>
       <c r="U53" s="25"/>
@@ -4019,10 +4101,10 @@
       <c r="AM53" s="25"/>
       <c r="AN53" s="25"/>
       <c r="AO53" s="26"/>
-      <c r="AP53" s="35"/>
+      <c r="AP53" s="34"/>
     </row>
     <row r="54" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A54" s="35"/>
+      <c r="A54" s="34"/>
       <c r="B54" s="4"/>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
@@ -4067,10 +4149,10 @@
       <c r="AM54" s="43"/>
       <c r="AN54" s="43"/>
       <c r="AO54" s="47"/>
-      <c r="AP54" s="35"/>
+      <c r="AP54" s="34"/>
     </row>
     <row r="55" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A55" s="35"/>
+      <c r="A55" s="34"/>
       <c r="B55" s="4"/>
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
@@ -4089,17 +4171,17 @@
       <c r="Q55" s="5"/>
       <c r="R55" s="5"/>
       <c r="S55" s="5"/>
-      <c r="T55" s="63" t="s">
+      <c r="T55" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="U55" s="64"/>
-      <c r="V55" s="64"/>
-      <c r="W55" s="64"/>
-      <c r="X55" s="64"/>
-      <c r="Y55" s="64"/>
-      <c r="Z55" s="64"/>
-      <c r="AA55" s="65"/>
-      <c r="AB55" s="56" t="s">
+      <c r="U55" s="65"/>
+      <c r="V55" s="65"/>
+      <c r="W55" s="65"/>
+      <c r="X55" s="65"/>
+      <c r="Y55" s="65"/>
+      <c r="Z55" s="65"/>
+      <c r="AA55" s="66"/>
+      <c r="AB55" s="57" t="s">
         <v>28</v>
       </c>
       <c r="AC55" s="25"/>
@@ -4115,10 +4197,10 @@
       <c r="AM55" s="25"/>
       <c r="AN55" s="25"/>
       <c r="AO55" s="26"/>
-      <c r="AP55" s="35"/>
+      <c r="AP55" s="34"/>
     </row>
     <row r="56" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A56" s="35"/>
+      <c r="A56" s="34"/>
       <c r="B56" s="4"/>
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
@@ -4137,14 +4219,14 @@
       <c r="Q56" s="5"/>
       <c r="R56" s="5"/>
       <c r="S56" s="5"/>
-      <c r="T56" s="66"/>
-      <c r="U56" s="64"/>
-      <c r="V56" s="64"/>
-      <c r="W56" s="64"/>
-      <c r="X56" s="64"/>
-      <c r="Y56" s="64"/>
-      <c r="Z56" s="64"/>
-      <c r="AA56" s="65"/>
+      <c r="T56" s="67"/>
+      <c r="U56" s="65"/>
+      <c r="V56" s="65"/>
+      <c r="W56" s="65"/>
+      <c r="X56" s="65"/>
+      <c r="Y56" s="65"/>
+      <c r="Z56" s="65"/>
+      <c r="AA56" s="66"/>
       <c r="AB56" s="46" t="s">
         <v>29</v>
       </c>
@@ -4161,10 +4243,10 @@
       <c r="AM56" s="43"/>
       <c r="AN56" s="43"/>
       <c r="AO56" s="47"/>
-      <c r="AP56" s="35"/>
+      <c r="AP56" s="34"/>
     </row>
     <row r="57" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A57" s="35"/>
+      <c r="A57" s="34"/>
       <c r="B57" s="4"/>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
@@ -4183,7 +4265,7 @@
       <c r="Q57" s="5"/>
       <c r="R57" s="5"/>
       <c r="S57" s="5"/>
-      <c r="T57" s="67"/>
+      <c r="T57" s="68"/>
       <c r="U57" s="25"/>
       <c r="V57" s="25"/>
       <c r="W57" s="25"/>
@@ -4191,7 +4273,7 @@
       <c r="Y57" s="25"/>
       <c r="Z57" s="25"/>
       <c r="AA57" s="41"/>
-      <c r="AB57" s="71" t="s">
+      <c r="AB57" s="72" t="s">
         <v>30</v>
       </c>
       <c r="AC57" s="25"/>
@@ -4207,10 +4289,10 @@
       <c r="AM57" s="25"/>
       <c r="AN57" s="25"/>
       <c r="AO57" s="26"/>
-      <c r="AP57" s="35"/>
+      <c r="AP57" s="34"/>
     </row>
     <row r="58" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A58" s="35"/>
+      <c r="A58" s="34"/>
       <c r="B58" s="4"/>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
@@ -4245,7 +4327,7 @@
       <c r="AE58" s="43"/>
       <c r="AF58" s="43"/>
       <c r="AG58" s="44"/>
-      <c r="AH58" s="73" t="s">
+      <c r="AH58" s="74" t="s">
         <v>32</v>
       </c>
       <c r="AI58" s="43"/>
@@ -4257,10 +4339,10 @@
       <c r="AM58" s="43"/>
       <c r="AN58" s="43"/>
       <c r="AO58" s="47"/>
-      <c r="AP58" s="35"/>
+      <c r="AP58" s="34"/>
     </row>
     <row r="59" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A59" s="35"/>
+      <c r="A59" s="34"/>
       <c r="B59" s="4"/>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
@@ -4282,20 +4364,20 @@
       <c r="T59" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="U59" s="64"/>
-      <c r="V59" s="64"/>
-      <c r="W59" s="64"/>
-      <c r="X59" s="64"/>
-      <c r="Y59" s="64"/>
-      <c r="Z59" s="64"/>
-      <c r="AA59" s="64"/>
-      <c r="AB59" s="64"/>
-      <c r="AC59" s="64"/>
-      <c r="AD59" s="64"/>
-      <c r="AE59" s="64"/>
-      <c r="AF59" s="64"/>
-      <c r="AG59" s="65"/>
-      <c r="AH59" s="53" t="s">
+      <c r="U59" s="65"/>
+      <c r="V59" s="65"/>
+      <c r="W59" s="65"/>
+      <c r="X59" s="65"/>
+      <c r="Y59" s="65"/>
+      <c r="Z59" s="65"/>
+      <c r="AA59" s="65"/>
+      <c r="AB59" s="65"/>
+      <c r="AC59" s="65"/>
+      <c r="AD59" s="65"/>
+      <c r="AE59" s="65"/>
+      <c r="AF59" s="65"/>
+      <c r="AG59" s="66"/>
+      <c r="AH59" s="54" t="s">
         <v>35</v>
       </c>
       <c r="AI59" s="25"/>
@@ -4307,10 +4389,10 @@
       <c r="AM59" s="25"/>
       <c r="AN59" s="25"/>
       <c r="AO59" s="26"/>
-      <c r="AP59" s="35"/>
+      <c r="AP59" s="34"/>
     </row>
     <row r="60" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A60" s="35"/>
+      <c r="A60" s="34"/>
       <c r="B60" s="4"/>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
@@ -4329,20 +4411,20 @@
       <c r="Q60" s="5"/>
       <c r="R60" s="5"/>
       <c r="S60" s="5"/>
-      <c r="T60" s="66"/>
-      <c r="U60" s="64"/>
-      <c r="V60" s="64"/>
-      <c r="W60" s="64"/>
-      <c r="X60" s="64"/>
-      <c r="Y60" s="64"/>
-      <c r="Z60" s="64"/>
-      <c r="AA60" s="64"/>
-      <c r="AB60" s="64"/>
-      <c r="AC60" s="64"/>
-      <c r="AD60" s="64"/>
-      <c r="AE60" s="64"/>
-      <c r="AF60" s="64"/>
-      <c r="AG60" s="65"/>
+      <c r="T60" s="67"/>
+      <c r="U60" s="65"/>
+      <c r="V60" s="65"/>
+      <c r="W60" s="65"/>
+      <c r="X60" s="65"/>
+      <c r="Y60" s="65"/>
+      <c r="Z60" s="65"/>
+      <c r="AA60" s="65"/>
+      <c r="AB60" s="65"/>
+      <c r="AC60" s="65"/>
+      <c r="AD60" s="65"/>
+      <c r="AE60" s="65"/>
+      <c r="AF60" s="65"/>
+      <c r="AG60" s="66"/>
       <c r="AH60" s="46" t="s">
         <v>37</v>
       </c>
@@ -4353,10 +4435,10 @@
       <c r="AM60" s="43"/>
       <c r="AN60" s="43"/>
       <c r="AO60" s="47"/>
-      <c r="AP60" s="35"/>
+      <c r="AP60" s="34"/>
     </row>
     <row r="61" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A61" s="36"/>
+      <c r="A61" s="35"/>
       <c r="B61" s="19"/>
       <c r="C61" s="20"/>
       <c r="D61" s="20"/>
@@ -4376,28 +4458,28 @@
       <c r="R61" s="20"/>
       <c r="S61" s="20"/>
       <c r="T61" s="77"/>
-      <c r="U61" s="69"/>
-      <c r="V61" s="69"/>
-      <c r="W61" s="69"/>
-      <c r="X61" s="69"/>
-      <c r="Y61" s="69"/>
-      <c r="Z61" s="69"/>
-      <c r="AA61" s="69"/>
-      <c r="AB61" s="69"/>
-      <c r="AC61" s="69"/>
-      <c r="AD61" s="69"/>
-      <c r="AE61" s="69"/>
-      <c r="AF61" s="69"/>
+      <c r="U61" s="70"/>
+      <c r="V61" s="70"/>
+      <c r="W61" s="70"/>
+      <c r="X61" s="70"/>
+      <c r="Y61" s="70"/>
+      <c r="Z61" s="70"/>
+      <c r="AA61" s="70"/>
+      <c r="AB61" s="70"/>
+      <c r="AC61" s="70"/>
+      <c r="AD61" s="70"/>
+      <c r="AE61" s="70"/>
+      <c r="AF61" s="70"/>
       <c r="AG61" s="78"/>
-      <c r="AH61" s="68"/>
-      <c r="AI61" s="69"/>
-      <c r="AJ61" s="69"/>
-      <c r="AK61" s="69"/>
-      <c r="AL61" s="69"/>
-      <c r="AM61" s="69"/>
-      <c r="AN61" s="69"/>
-      <c r="AO61" s="70"/>
-      <c r="AP61" s="36"/>
+      <c r="AH61" s="69"/>
+      <c r="AI61" s="70"/>
+      <c r="AJ61" s="70"/>
+      <c r="AK61" s="70"/>
+      <c r="AL61" s="70"/>
+      <c r="AM61" s="70"/>
+      <c r="AN61" s="70"/>
+      <c r="AO61" s="71"/>
+      <c r="AP61" s="35"/>
     </row>
     <row r="62" spans="1:42" ht="11.5" customHeight="1">
       <c r="B62" s="37">
@@ -4457,90 +4539,1133 @@
       <c r="AN62" s="38"/>
       <c r="AO62" s="39"/>
     </row>
-    <row r="67" ht="13" customHeight="1"/>
-    <row r="68" ht="13" customHeight="1"/>
-    <row r="69" ht="13" customHeight="1"/>
-    <row r="70" ht="13" customHeight="1"/>
-    <row r="71" ht="13" customHeight="1"/>
-    <row r="72" ht="13" customHeight="1"/>
-    <row r="73" ht="13" customHeight="1"/>
-    <row r="74" ht="13" customHeight="1"/>
-    <row r="75" ht="13" customHeight="1"/>
-    <row r="76" ht="13" customHeight="1"/>
-    <row r="77" ht="13" customHeight="1"/>
-    <row r="78" ht="13" customHeight="1"/>
-    <row r="79" ht="13" customHeight="1"/>
-    <row r="80" ht="13" customHeight="1"/>
-    <row r="81" ht="13" customHeight="1"/>
-    <row r="82" ht="13" customHeight="1"/>
+    <row r="64" spans="1:42">
+      <c r="B64" s="75" t="s">
+        <v>38</v>
+      </c>
+      <c r="C64" s="60"/>
+      <c r="D64" s="60"/>
+      <c r="E64" s="60"/>
+      <c r="F64" s="60"/>
+      <c r="G64" s="60"/>
+      <c r="H64" s="60"/>
+      <c r="I64" s="60"/>
+      <c r="J64" s="60"/>
+      <c r="K64" s="60"/>
+      <c r="L64" s="60"/>
+      <c r="M64" s="60"/>
+      <c r="N64" s="60"/>
+      <c r="O64" s="60"/>
+      <c r="P64" s="60"/>
+      <c r="Q64" s="60"/>
+      <c r="R64" s="60"/>
+      <c r="S64" s="60"/>
+      <c r="T64" s="60"/>
+      <c r="U64" s="60"/>
+      <c r="V64" s="60"/>
+      <c r="W64" s="60"/>
+      <c r="X64" s="60"/>
+      <c r="Y64" s="60"/>
+      <c r="Z64" s="60"/>
+      <c r="AA64" s="60"/>
+      <c r="AB64" s="60"/>
+      <c r="AC64" s="60"/>
+      <c r="AD64" s="60"/>
+      <c r="AE64" s="60"/>
+      <c r="AF64" s="60"/>
+      <c r="AG64" s="60"/>
+      <c r="AH64" s="60"/>
+      <c r="AI64" s="60"/>
+      <c r="AJ64" s="60"/>
+      <c r="AK64" s="60"/>
+      <c r="AL64" s="60"/>
+      <c r="AM64" s="60"/>
+      <c r="AN64" s="60"/>
+      <c r="AO64" s="60"/>
+    </row>
+    <row r="65" spans="2:41">
+      <c r="B65" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="C65" s="60"/>
+      <c r="D65" s="60"/>
+      <c r="E65" s="60"/>
+      <c r="F65" s="60"/>
+      <c r="G65" s="60"/>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="60"/>
+      <c r="K65" s="60"/>
+      <c r="L65" s="60"/>
+      <c r="M65" s="60"/>
+      <c r="N65" s="60"/>
+      <c r="O65" s="60"/>
+      <c r="P65" s="60"/>
+      <c r="Q65" s="60"/>
+      <c r="R65" s="60"/>
+      <c r="S65" s="60"/>
+      <c r="T65" s="60"/>
+      <c r="U65" s="60"/>
+      <c r="V65" s="60"/>
+      <c r="W65" s="60"/>
+      <c r="X65" s="60"/>
+      <c r="Y65" s="60"/>
+      <c r="Z65" s="60"/>
+      <c r="AA65" s="60"/>
+      <c r="AB65" s="60"/>
+      <c r="AC65" s="60"/>
+      <c r="AD65" s="60"/>
+      <c r="AE65" s="60"/>
+      <c r="AF65" s="60"/>
+      <c r="AG65" s="60"/>
+      <c r="AH65" s="60"/>
+      <c r="AI65" s="60"/>
+      <c r="AJ65" s="60"/>
+      <c r="AK65" s="60"/>
+      <c r="AL65" s="60"/>
+      <c r="AM65" s="60"/>
+      <c r="AN65" s="60"/>
+      <c r="AO65" s="60"/>
+    </row>
+    <row r="66" spans="2:41">
+      <c r="B66" s="45" t="s">
+        <v>40</v>
+      </c>
+      <c r="C66" s="31"/>
+      <c r="D66" s="31"/>
+      <c r="E66" s="31"/>
+      <c r="F66" s="31"/>
+      <c r="G66" s="31"/>
+      <c r="H66" s="31"/>
+      <c r="I66" s="31"/>
+      <c r="J66" s="32"/>
+      <c r="K66" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="L66" s="31"/>
+      <c r="M66" s="32"/>
+      <c r="N66" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="O66" s="31"/>
+      <c r="P66" s="31"/>
+      <c r="Q66" s="32"/>
+      <c r="R66" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="S66" s="31"/>
+      <c r="T66" s="31"/>
+      <c r="U66" s="32"/>
+      <c r="V66" s="45" t="s">
+        <v>44</v>
+      </c>
+      <c r="W66" s="31"/>
+      <c r="X66" s="31"/>
+      <c r="Y66" s="31"/>
+      <c r="Z66" s="31"/>
+      <c r="AA66" s="31"/>
+      <c r="AB66" s="31"/>
+      <c r="AC66" s="31"/>
+      <c r="AD66" s="31"/>
+      <c r="AE66" s="31"/>
+      <c r="AF66" s="31"/>
+      <c r="AG66" s="31"/>
+      <c r="AH66" s="31"/>
+      <c r="AI66" s="31"/>
+      <c r="AJ66" s="31"/>
+      <c r="AK66" s="31"/>
+      <c r="AL66" s="31"/>
+      <c r="AM66" s="31"/>
+      <c r="AN66" s="31"/>
+      <c r="AO66" s="32"/>
+    </row>
+    <row r="67" spans="2:41" ht="13" customHeight="1">
+      <c r="B67" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C67" s="28"/>
+      <c r="D67" s="28"/>
+      <c r="E67" s="28"/>
+      <c r="F67" s="28"/>
+      <c r="G67" s="28"/>
+      <c r="H67" s="28"/>
+      <c r="I67" s="28"/>
+      <c r="J67" s="29"/>
+      <c r="K67" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="L67" s="28"/>
+      <c r="M67" s="29"/>
+      <c r="N67" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="O67" s="28"/>
+      <c r="P67" s="28"/>
+      <c r="Q67" s="29"/>
+      <c r="R67" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="S67" s="28"/>
+      <c r="T67" s="28"/>
+      <c r="U67" s="29"/>
+      <c r="V67" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="W67" s="28"/>
+      <c r="X67" s="28"/>
+      <c r="Y67" s="28"/>
+      <c r="Z67" s="28"/>
+      <c r="AA67" s="28"/>
+      <c r="AB67" s="28"/>
+      <c r="AC67" s="28"/>
+      <c r="AD67" s="28"/>
+      <c r="AE67" s="28"/>
+      <c r="AF67" s="28"/>
+      <c r="AG67" s="28"/>
+      <c r="AH67" s="28"/>
+      <c r="AI67" s="28"/>
+      <c r="AJ67" s="28"/>
+      <c r="AK67" s="28"/>
+      <c r="AL67" s="28"/>
+      <c r="AM67" s="28"/>
+      <c r="AN67" s="28"/>
+      <c r="AO67" s="29"/>
+    </row>
+    <row r="68" spans="2:41" ht="13" customHeight="1">
+      <c r="B68" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C68" s="28"/>
+      <c r="D68" s="28"/>
+      <c r="E68" s="28"/>
+      <c r="F68" s="28"/>
+      <c r="G68" s="28"/>
+      <c r="H68" s="28"/>
+      <c r="I68" s="28"/>
+      <c r="J68" s="29"/>
+      <c r="K68" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="L68" s="28"/>
+      <c r="M68" s="29"/>
+      <c r="N68" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="O68" s="28"/>
+      <c r="P68" s="28"/>
+      <c r="Q68" s="29"/>
+      <c r="R68" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="S68" s="28"/>
+      <c r="T68" s="28"/>
+      <c r="U68" s="29"/>
+      <c r="V68" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="W68" s="28"/>
+      <c r="X68" s="28"/>
+      <c r="Y68" s="28"/>
+      <c r="Z68" s="28"/>
+      <c r="AA68" s="28"/>
+      <c r="AB68" s="28"/>
+      <c r="AC68" s="28"/>
+      <c r="AD68" s="28"/>
+      <c r="AE68" s="28"/>
+      <c r="AF68" s="28"/>
+      <c r="AG68" s="28"/>
+      <c r="AH68" s="28"/>
+      <c r="AI68" s="28"/>
+      <c r="AJ68" s="28"/>
+      <c r="AK68" s="28"/>
+      <c r="AL68" s="28"/>
+      <c r="AM68" s="28"/>
+      <c r="AN68" s="28"/>
+      <c r="AO68" s="29"/>
+    </row>
+    <row r="69" spans="2:41" ht="13" customHeight="1">
+      <c r="B69" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C69" s="28"/>
+      <c r="D69" s="28"/>
+      <c r="E69" s="28"/>
+      <c r="F69" s="28"/>
+      <c r="G69" s="28"/>
+      <c r="H69" s="28"/>
+      <c r="I69" s="28"/>
+      <c r="J69" s="29"/>
+      <c r="K69" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="L69" s="28"/>
+      <c r="M69" s="29"/>
+      <c r="N69" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="O69" s="28"/>
+      <c r="P69" s="28"/>
+      <c r="Q69" s="29"/>
+      <c r="R69" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="S69" s="28"/>
+      <c r="T69" s="28"/>
+      <c r="U69" s="29"/>
+      <c r="V69" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="W69" s="28"/>
+      <c r="X69" s="28"/>
+      <c r="Y69" s="28"/>
+      <c r="Z69" s="28"/>
+      <c r="AA69" s="28"/>
+      <c r="AB69" s="28"/>
+      <c r="AC69" s="28"/>
+      <c r="AD69" s="28"/>
+      <c r="AE69" s="28"/>
+      <c r="AF69" s="28"/>
+      <c r="AG69" s="28"/>
+      <c r="AH69" s="28"/>
+      <c r="AI69" s="28"/>
+      <c r="AJ69" s="28"/>
+      <c r="AK69" s="28"/>
+      <c r="AL69" s="28"/>
+      <c r="AM69" s="28"/>
+      <c r="AN69" s="28"/>
+      <c r="AO69" s="29"/>
+    </row>
+    <row r="70" spans="2:41" ht="13" customHeight="1">
+      <c r="B70" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C70" s="28"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="28"/>
+      <c r="H70" s="28"/>
+      <c r="I70" s="28"/>
+      <c r="J70" s="29"/>
+      <c r="K70" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="L70" s="28"/>
+      <c r="M70" s="29"/>
+      <c r="N70" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="O70" s="28"/>
+      <c r="P70" s="28"/>
+      <c r="Q70" s="29"/>
+      <c r="R70" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="S70" s="28"/>
+      <c r="T70" s="28"/>
+      <c r="U70" s="29"/>
+      <c r="V70" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="W70" s="28"/>
+      <c r="X70" s="28"/>
+      <c r="Y70" s="28"/>
+      <c r="Z70" s="28"/>
+      <c r="AA70" s="28"/>
+      <c r="AB70" s="28"/>
+      <c r="AC70" s="28"/>
+      <c r="AD70" s="28"/>
+      <c r="AE70" s="28"/>
+      <c r="AF70" s="28"/>
+      <c r="AG70" s="28"/>
+      <c r="AH70" s="28"/>
+      <c r="AI70" s="28"/>
+      <c r="AJ70" s="28"/>
+      <c r="AK70" s="28"/>
+      <c r="AL70" s="28"/>
+      <c r="AM70" s="28"/>
+      <c r="AN70" s="28"/>
+      <c r="AO70" s="29"/>
+    </row>
+    <row r="71" spans="2:41" ht="13" customHeight="1">
+      <c r="B71" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71" s="31"/>
+      <c r="D71" s="31"/>
+      <c r="E71" s="31"/>
+      <c r="F71" s="31"/>
+      <c r="G71" s="31"/>
+      <c r="H71" s="31"/>
+      <c r="I71" s="31"/>
+      <c r="J71" s="32"/>
+      <c r="K71" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="L71" s="31"/>
+      <c r="M71" s="32"/>
+      <c r="N71" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="O71" s="31"/>
+      <c r="P71" s="31"/>
+      <c r="Q71" s="32"/>
+      <c r="R71" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="S71" s="31"/>
+      <c r="T71" s="31"/>
+      <c r="U71" s="32"/>
+      <c r="V71" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="W71" s="31"/>
+      <c r="X71" s="31"/>
+      <c r="Y71" s="31"/>
+      <c r="Z71" s="31"/>
+      <c r="AA71" s="31"/>
+      <c r="AB71" s="31"/>
+      <c r="AC71" s="31"/>
+      <c r="AD71" s="31"/>
+      <c r="AE71" s="31"/>
+      <c r="AF71" s="31"/>
+      <c r="AG71" s="31"/>
+      <c r="AH71" s="31"/>
+      <c r="AI71" s="31"/>
+      <c r="AJ71" s="31"/>
+      <c r="AK71" s="31"/>
+      <c r="AL71" s="31"/>
+      <c r="AM71" s="31"/>
+      <c r="AN71" s="31"/>
+      <c r="AO71" s="32"/>
+    </row>
+    <row r="72" spans="2:41" ht="13" customHeight="1">
+      <c r="B72" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C72" s="31"/>
+      <c r="D72" s="31"/>
+      <c r="E72" s="31"/>
+      <c r="F72" s="31"/>
+      <c r="G72" s="31"/>
+      <c r="H72" s="31"/>
+      <c r="I72" s="31"/>
+      <c r="J72" s="32"/>
+      <c r="K72" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="L72" s="31"/>
+      <c r="M72" s="32"/>
+      <c r="N72" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="O72" s="31"/>
+      <c r="P72" s="31"/>
+      <c r="Q72" s="32"/>
+      <c r="R72" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="S72" s="31"/>
+      <c r="T72" s="31"/>
+      <c r="U72" s="32"/>
+      <c r="V72" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="W72" s="31"/>
+      <c r="X72" s="31"/>
+      <c r="Y72" s="31"/>
+      <c r="Z72" s="31"/>
+      <c r="AA72" s="31"/>
+      <c r="AB72" s="31"/>
+      <c r="AC72" s="31"/>
+      <c r="AD72" s="31"/>
+      <c r="AE72" s="31"/>
+      <c r="AF72" s="31"/>
+      <c r="AG72" s="31"/>
+      <c r="AH72" s="31"/>
+      <c r="AI72" s="31"/>
+      <c r="AJ72" s="31"/>
+      <c r="AK72" s="31"/>
+      <c r="AL72" s="31"/>
+      <c r="AM72" s="31"/>
+      <c r="AN72" s="31"/>
+      <c r="AO72" s="32"/>
+    </row>
+    <row r="73" spans="2:41" ht="13" customHeight="1">
+      <c r="B73" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C73" s="31"/>
+      <c r="D73" s="31"/>
+      <c r="E73" s="31"/>
+      <c r="F73" s="31"/>
+      <c r="G73" s="31"/>
+      <c r="H73" s="31"/>
+      <c r="I73" s="31"/>
+      <c r="J73" s="32"/>
+      <c r="K73" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="L73" s="31"/>
+      <c r="M73" s="32"/>
+      <c r="N73" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="O73" s="31"/>
+      <c r="P73" s="31"/>
+      <c r="Q73" s="32"/>
+      <c r="R73" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="S73" s="31"/>
+      <c r="T73" s="31"/>
+      <c r="U73" s="32"/>
+      <c r="V73" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="W73" s="31"/>
+      <c r="X73" s="31"/>
+      <c r="Y73" s="31"/>
+      <c r="Z73" s="31"/>
+      <c r="AA73" s="31"/>
+      <c r="AB73" s="31"/>
+      <c r="AC73" s="31"/>
+      <c r="AD73" s="31"/>
+      <c r="AE73" s="31"/>
+      <c r="AF73" s="31"/>
+      <c r="AG73" s="31"/>
+      <c r="AH73" s="31"/>
+      <c r="AI73" s="31"/>
+      <c r="AJ73" s="31"/>
+      <c r="AK73" s="31"/>
+      <c r="AL73" s="31"/>
+      <c r="AM73" s="31"/>
+      <c r="AN73" s="31"/>
+      <c r="AO73" s="32"/>
+    </row>
+    <row r="74" spans="2:41" ht="13" customHeight="1">
+      <c r="B74" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C74" s="31"/>
+      <c r="D74" s="31"/>
+      <c r="E74" s="31"/>
+      <c r="F74" s="31"/>
+      <c r="G74" s="31"/>
+      <c r="H74" s="31"/>
+      <c r="I74" s="31"/>
+      <c r="J74" s="32"/>
+      <c r="K74" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="L74" s="31"/>
+      <c r="M74" s="32"/>
+      <c r="N74" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="O74" s="31"/>
+      <c r="P74" s="31"/>
+      <c r="Q74" s="32"/>
+      <c r="R74" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="S74" s="31"/>
+      <c r="T74" s="31"/>
+      <c r="U74" s="32"/>
+      <c r="V74" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="W74" s="31"/>
+      <c r="X74" s="31"/>
+      <c r="Y74" s="31"/>
+      <c r="Z74" s="31"/>
+      <c r="AA74" s="31"/>
+      <c r="AB74" s="31"/>
+      <c r="AC74" s="31"/>
+      <c r="AD74" s="31"/>
+      <c r="AE74" s="31"/>
+      <c r="AF74" s="31"/>
+      <c r="AG74" s="31"/>
+      <c r="AH74" s="31"/>
+      <c r="AI74" s="31"/>
+      <c r="AJ74" s="31"/>
+      <c r="AK74" s="31"/>
+      <c r="AL74" s="31"/>
+      <c r="AM74" s="31"/>
+      <c r="AN74" s="31"/>
+      <c r="AO74" s="32"/>
+    </row>
+    <row r="75" spans="2:41" ht="13" customHeight="1">
+      <c r="B75" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75" s="31"/>
+      <c r="D75" s="31"/>
+      <c r="E75" s="31"/>
+      <c r="F75" s="31"/>
+      <c r="G75" s="31"/>
+      <c r="H75" s="31"/>
+      <c r="I75" s="31"/>
+      <c r="J75" s="32"/>
+      <c r="K75" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="L75" s="31"/>
+      <c r="M75" s="32"/>
+      <c r="N75" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="O75" s="31"/>
+      <c r="P75" s="31"/>
+      <c r="Q75" s="32"/>
+      <c r="R75" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="S75" s="31"/>
+      <c r="T75" s="31"/>
+      <c r="U75" s="32"/>
+      <c r="V75" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="W75" s="31"/>
+      <c r="X75" s="31"/>
+      <c r="Y75" s="31"/>
+      <c r="Z75" s="31"/>
+      <c r="AA75" s="31"/>
+      <c r="AB75" s="31"/>
+      <c r="AC75" s="31"/>
+      <c r="AD75" s="31"/>
+      <c r="AE75" s="31"/>
+      <c r="AF75" s="31"/>
+      <c r="AG75" s="31"/>
+      <c r="AH75" s="31"/>
+      <c r="AI75" s="31"/>
+      <c r="AJ75" s="31"/>
+      <c r="AK75" s="31"/>
+      <c r="AL75" s="31"/>
+      <c r="AM75" s="31"/>
+      <c r="AN75" s="31"/>
+      <c r="AO75" s="32"/>
+    </row>
+    <row r="76" spans="2:41" ht="13" customHeight="1">
+      <c r="B76" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C76" s="31"/>
+      <c r="D76" s="31"/>
+      <c r="E76" s="31"/>
+      <c r="F76" s="31"/>
+      <c r="G76" s="31"/>
+      <c r="H76" s="31"/>
+      <c r="I76" s="31"/>
+      <c r="J76" s="32"/>
+      <c r="K76" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="L76" s="31"/>
+      <c r="M76" s="32"/>
+      <c r="N76" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="O76" s="31"/>
+      <c r="P76" s="31"/>
+      <c r="Q76" s="32"/>
+      <c r="R76" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="S76" s="31"/>
+      <c r="T76" s="31"/>
+      <c r="U76" s="32"/>
+      <c r="V76" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="W76" s="31"/>
+      <c r="X76" s="31"/>
+      <c r="Y76" s="31"/>
+      <c r="Z76" s="31"/>
+      <c r="AA76" s="31"/>
+      <c r="AB76" s="31"/>
+      <c r="AC76" s="31"/>
+      <c r="AD76" s="31"/>
+      <c r="AE76" s="31"/>
+      <c r="AF76" s="31"/>
+      <c r="AG76" s="31"/>
+      <c r="AH76" s="31"/>
+      <c r="AI76" s="31"/>
+      <c r="AJ76" s="31"/>
+      <c r="AK76" s="31"/>
+      <c r="AL76" s="31"/>
+      <c r="AM76" s="31"/>
+      <c r="AN76" s="31"/>
+      <c r="AO76" s="32"/>
+    </row>
+    <row r="77" spans="2:41" ht="13" customHeight="1">
+      <c r="B77" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="C77" s="31"/>
+      <c r="D77" s="31"/>
+      <c r="E77" s="31"/>
+      <c r="F77" s="31"/>
+      <c r="G77" s="31"/>
+      <c r="H77" s="31"/>
+      <c r="I77" s="31"/>
+      <c r="J77" s="32"/>
+      <c r="K77" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="L77" s="31"/>
+      <c r="M77" s="32"/>
+      <c r="N77" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="O77" s="31"/>
+      <c r="P77" s="31"/>
+      <c r="Q77" s="32"/>
+      <c r="R77" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="S77" s="31"/>
+      <c r="T77" s="31"/>
+      <c r="U77" s="32"/>
+      <c r="V77" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="W77" s="31"/>
+      <c r="X77" s="31"/>
+      <c r="Y77" s="31"/>
+      <c r="Z77" s="31"/>
+      <c r="AA77" s="31"/>
+      <c r="AB77" s="31"/>
+      <c r="AC77" s="31"/>
+      <c r="AD77" s="31"/>
+      <c r="AE77" s="31"/>
+      <c r="AF77" s="31"/>
+      <c r="AG77" s="31"/>
+      <c r="AH77" s="31"/>
+      <c r="AI77" s="31"/>
+      <c r="AJ77" s="31"/>
+      <c r="AK77" s="31"/>
+      <c r="AL77" s="31"/>
+      <c r="AM77" s="31"/>
+      <c r="AN77" s="31"/>
+      <c r="AO77" s="32"/>
+    </row>
+    <row r="78" spans="2:41" ht="13" customHeight="1">
+      <c r="B78" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C78" s="31"/>
+      <c r="D78" s="31"/>
+      <c r="E78" s="31"/>
+      <c r="F78" s="31"/>
+      <c r="G78" s="31"/>
+      <c r="H78" s="31"/>
+      <c r="I78" s="31"/>
+      <c r="J78" s="32"/>
+      <c r="K78" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="L78" s="31"/>
+      <c r="M78" s="32"/>
+      <c r="N78" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="O78" s="31"/>
+      <c r="P78" s="31"/>
+      <c r="Q78" s="32"/>
+      <c r="R78" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="S78" s="31"/>
+      <c r="T78" s="31"/>
+      <c r="U78" s="32"/>
+      <c r="V78" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="W78" s="31"/>
+      <c r="X78" s="31"/>
+      <c r="Y78" s="31"/>
+      <c r="Z78" s="31"/>
+      <c r="AA78" s="31"/>
+      <c r="AB78" s="31"/>
+      <c r="AC78" s="31"/>
+      <c r="AD78" s="31"/>
+      <c r="AE78" s="31"/>
+      <c r="AF78" s="31"/>
+      <c r="AG78" s="31"/>
+      <c r="AH78" s="31"/>
+      <c r="AI78" s="31"/>
+      <c r="AJ78" s="31"/>
+      <c r="AK78" s="31"/>
+      <c r="AL78" s="31"/>
+      <c r="AM78" s="31"/>
+      <c r="AN78" s="31"/>
+      <c r="AO78" s="32"/>
+    </row>
+    <row r="79" spans="2:41" ht="13" customHeight="1">
+      <c r="B79" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C79" s="31"/>
+      <c r="D79" s="31"/>
+      <c r="E79" s="31"/>
+      <c r="F79" s="31"/>
+      <c r="G79" s="31"/>
+      <c r="H79" s="31"/>
+      <c r="I79" s="31"/>
+      <c r="J79" s="32"/>
+      <c r="K79" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="L79" s="31"/>
+      <c r="M79" s="32"/>
+      <c r="N79" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="O79" s="31"/>
+      <c r="P79" s="31"/>
+      <c r="Q79" s="32"/>
+      <c r="R79" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="S79" s="31"/>
+      <c r="T79" s="31"/>
+      <c r="U79" s="32"/>
+      <c r="V79" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="W79" s="31"/>
+      <c r="X79" s="31"/>
+      <c r="Y79" s="31"/>
+      <c r="Z79" s="31"/>
+      <c r="AA79" s="31"/>
+      <c r="AB79" s="31"/>
+      <c r="AC79" s="31"/>
+      <c r="AD79" s="31"/>
+      <c r="AE79" s="31"/>
+      <c r="AF79" s="31"/>
+      <c r="AG79" s="31"/>
+      <c r="AH79" s="31"/>
+      <c r="AI79" s="31"/>
+      <c r="AJ79" s="31"/>
+      <c r="AK79" s="31"/>
+      <c r="AL79" s="31"/>
+      <c r="AM79" s="31"/>
+      <c r="AN79" s="31"/>
+      <c r="AO79" s="32"/>
+    </row>
+    <row r="80" spans="2:41" ht="13" customHeight="1">
+      <c r="B80" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C80" s="31"/>
+      <c r="D80" s="31"/>
+      <c r="E80" s="31"/>
+      <c r="F80" s="31"/>
+      <c r="G80" s="31"/>
+      <c r="H80" s="31"/>
+      <c r="I80" s="31"/>
+      <c r="J80" s="32"/>
+      <c r="K80" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="L80" s="31"/>
+      <c r="M80" s="32"/>
+      <c r="N80" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="O80" s="31"/>
+      <c r="P80" s="31"/>
+      <c r="Q80" s="32"/>
+      <c r="R80" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="S80" s="31"/>
+      <c r="T80" s="31"/>
+      <c r="U80" s="32"/>
+      <c r="V80" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="W80" s="31"/>
+      <c r="X80" s="31"/>
+      <c r="Y80" s="31"/>
+      <c r="Z80" s="31"/>
+      <c r="AA80" s="31"/>
+      <c r="AB80" s="31"/>
+      <c r="AC80" s="31"/>
+      <c r="AD80" s="31"/>
+      <c r="AE80" s="31"/>
+      <c r="AF80" s="31"/>
+      <c r="AG80" s="31"/>
+      <c r="AH80" s="31"/>
+      <c r="AI80" s="31"/>
+      <c r="AJ80" s="31"/>
+      <c r="AK80" s="31"/>
+      <c r="AL80" s="31"/>
+      <c r="AM80" s="31"/>
+      <c r="AN80" s="31"/>
+      <c r="AO80" s="32"/>
+    </row>
+    <row r="81" spans="2:41" ht="13" customHeight="1">
+      <c r="B81" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="C81" s="31"/>
+      <c r="D81" s="31"/>
+      <c r="E81" s="31"/>
+      <c r="F81" s="31"/>
+      <c r="G81" s="31"/>
+      <c r="H81" s="31"/>
+      <c r="I81" s="31"/>
+      <c r="J81" s="32"/>
+      <c r="K81" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="L81" s="31"/>
+      <c r="M81" s="32"/>
+      <c r="N81" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="O81" s="31"/>
+      <c r="P81" s="31"/>
+      <c r="Q81" s="32"/>
+      <c r="R81" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="S81" s="31"/>
+      <c r="T81" s="31"/>
+      <c r="U81" s="32"/>
+      <c r="V81" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="W81" s="31"/>
+      <c r="X81" s="31"/>
+      <c r="Y81" s="31"/>
+      <c r="Z81" s="31"/>
+      <c r="AA81" s="31"/>
+      <c r="AB81" s="31"/>
+      <c r="AC81" s="31"/>
+      <c r="AD81" s="31"/>
+      <c r="AE81" s="31"/>
+      <c r="AF81" s="31"/>
+      <c r="AG81" s="31"/>
+      <c r="AH81" s="31"/>
+      <c r="AI81" s="31"/>
+      <c r="AJ81" s="31"/>
+      <c r="AK81" s="31"/>
+      <c r="AL81" s="31"/>
+      <c r="AM81" s="31"/>
+      <c r="AN81" s="31"/>
+      <c r="AO81" s="32"/>
+    </row>
+    <row r="82" spans="2:41" ht="13" customHeight="1">
+      <c r="B82" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="C82" s="31"/>
+      <c r="D82" s="31"/>
+      <c r="E82" s="31"/>
+      <c r="F82" s="31"/>
+      <c r="G82" s="31"/>
+      <c r="H82" s="31"/>
+      <c r="I82" s="31"/>
+      <c r="J82" s="32"/>
+      <c r="K82" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="L82" s="31"/>
+      <c r="M82" s="32"/>
+      <c r="N82" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="O82" s="31"/>
+      <c r="P82" s="31"/>
+      <c r="Q82" s="32"/>
+      <c r="R82" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="S82" s="31"/>
+      <c r="T82" s="31"/>
+      <c r="U82" s="32"/>
+      <c r="V82" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="W82" s="31"/>
+      <c r="X82" s="31"/>
+      <c r="Y82" s="31"/>
+      <c r="Z82" s="31"/>
+      <c r="AA82" s="31"/>
+      <c r="AB82" s="31"/>
+      <c r="AC82" s="31"/>
+      <c r="AD82" s="31"/>
+      <c r="AE82" s="31"/>
+      <c r="AF82" s="31"/>
+      <c r="AG82" s="31"/>
+      <c r="AH82" s="31"/>
+      <c r="AI82" s="31"/>
+      <c r="AJ82" s="31"/>
+      <c r="AK82" s="31"/>
+      <c r="AL82" s="31"/>
+      <c r="AM82" s="31"/>
+      <c r="AN82" s="31"/>
+      <c r="AO82" s="32"/>
+    </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="151">
+    <mergeCell ref="N71:Q71"/>
     <mergeCell ref="AP22:AP31"/>
     <mergeCell ref="AH58:AK58"/>
     <mergeCell ref="AF1:AJ1"/>
+    <mergeCell ref="N73:Q73"/>
+    <mergeCell ref="B77:J77"/>
     <mergeCell ref="V62:Z62"/>
+    <mergeCell ref="A2:A11"/>
+    <mergeCell ref="V66:AO66"/>
+    <mergeCell ref="N82:Q82"/>
+    <mergeCell ref="A42:A51"/>
+    <mergeCell ref="K79:M79"/>
+    <mergeCell ref="R76:U76"/>
+    <mergeCell ref="AF52:AJ52"/>
+    <mergeCell ref="B70:J70"/>
+    <mergeCell ref="AM43:AO43"/>
     <mergeCell ref="A22:A31"/>
+    <mergeCell ref="K72:M72"/>
+    <mergeCell ref="R66:U66"/>
+    <mergeCell ref="V80:AO80"/>
+    <mergeCell ref="K81:M81"/>
+    <mergeCell ref="R75:U75"/>
     <mergeCell ref="AL58:AO58"/>
     <mergeCell ref="Q62:U62"/>
+    <mergeCell ref="R68:U68"/>
+    <mergeCell ref="R77:U77"/>
+    <mergeCell ref="B73:J73"/>
     <mergeCell ref="AK62:AO62"/>
+    <mergeCell ref="B82:J82"/>
     <mergeCell ref="AF53:AJ53"/>
-    <mergeCell ref="AK51:AO51"/>
-    <mergeCell ref="AL59:AO59"/>
-    <mergeCell ref="Z43:AI43"/>
-    <mergeCell ref="AP52:AP61"/>
+    <mergeCell ref="V69:AO69"/>
+    <mergeCell ref="A32:A41"/>
+    <mergeCell ref="K76:M76"/>
+    <mergeCell ref="Z50:AE50"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="N69:Q69"/>
+    <mergeCell ref="N78:Q78"/>
+    <mergeCell ref="R72:U72"/>
+    <mergeCell ref="K75:M75"/>
+    <mergeCell ref="R81:U81"/>
+    <mergeCell ref="K67:M67"/>
+    <mergeCell ref="Z52:AE52"/>
+    <mergeCell ref="V76:AO76"/>
+    <mergeCell ref="N80:Q80"/>
+    <mergeCell ref="K77:M77"/>
+    <mergeCell ref="R71:U71"/>
+    <mergeCell ref="V79:AO79"/>
+    <mergeCell ref="B64:AO64"/>
+    <mergeCell ref="N70:Q70"/>
+    <mergeCell ref="N79:Q79"/>
+    <mergeCell ref="L62:P62"/>
+    <mergeCell ref="R73:U73"/>
+    <mergeCell ref="AF62:AJ62"/>
     <mergeCell ref="AB56:AO56"/>
-    <mergeCell ref="T59:AG61"/>
-    <mergeCell ref="AF51:AJ51"/>
-    <mergeCell ref="AF52:AJ52"/>
-    <mergeCell ref="AP42:AP51"/>
+    <mergeCell ref="V74:AO74"/>
+    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="B79:J79"/>
+    <mergeCell ref="N68:Q68"/>
+    <mergeCell ref="AH61:AO61"/>
+    <mergeCell ref="AB57:AO57"/>
+    <mergeCell ref="B72:J72"/>
+    <mergeCell ref="B81:J81"/>
     <mergeCell ref="AP2:AP11"/>
+    <mergeCell ref="V75:AO75"/>
     <mergeCell ref="G1:K1"/>
     <mergeCell ref="AA62:AE62"/>
     <mergeCell ref="T53:Y53"/>
-    <mergeCell ref="A32:A41"/>
-    <mergeCell ref="Z50:AE50"/>
-    <mergeCell ref="B62:F62"/>
-    <mergeCell ref="Z52:AE52"/>
+    <mergeCell ref="N67:Q67"/>
+    <mergeCell ref="B71:J71"/>
     <mergeCell ref="AP12:AP21"/>
-    <mergeCell ref="L62:P62"/>
     <mergeCell ref="B1:F1"/>
-    <mergeCell ref="AF62:AJ62"/>
+    <mergeCell ref="AP52:AP61"/>
+    <mergeCell ref="T59:AG61"/>
+    <mergeCell ref="K78:M78"/>
+    <mergeCell ref="AF51:AJ51"/>
+    <mergeCell ref="B75:J75"/>
     <mergeCell ref="AJ43:AL43"/>
+    <mergeCell ref="R74:U74"/>
     <mergeCell ref="AF50:AJ50"/>
-    <mergeCell ref="A2:A11"/>
-    <mergeCell ref="A42:A51"/>
-    <mergeCell ref="AM43:AO43"/>
     <mergeCell ref="A12:A21"/>
+    <mergeCell ref="R80:U80"/>
+    <mergeCell ref="V70:AO70"/>
     <mergeCell ref="T43:U43"/>
     <mergeCell ref="AK52:AO52"/>
+    <mergeCell ref="B66:J66"/>
+    <mergeCell ref="R70:U70"/>
     <mergeCell ref="AH59:AK59"/>
     <mergeCell ref="Z53:AE53"/>
+    <mergeCell ref="V71:AO71"/>
     <mergeCell ref="T50:Y50"/>
     <mergeCell ref="A52:A61"/>
     <mergeCell ref="AB55:AO55"/>
+    <mergeCell ref="V73:AO73"/>
     <mergeCell ref="T51:Y51"/>
     <mergeCell ref="AB54:AO54"/>
+    <mergeCell ref="B65:AO65"/>
+    <mergeCell ref="N74:Q74"/>
     <mergeCell ref="J20:AG22"/>
     <mergeCell ref="V43:Y43"/>
     <mergeCell ref="T58:AG58"/>
+    <mergeCell ref="K70:M70"/>
+    <mergeCell ref="T55:AA57"/>
+    <mergeCell ref="V77:AO77"/>
     <mergeCell ref="V1:Z1"/>
     <mergeCell ref="Z51:AE51"/>
     <mergeCell ref="T54:AA54"/>
+    <mergeCell ref="V72:AO72"/>
+    <mergeCell ref="R67:U67"/>
+    <mergeCell ref="V81:AO81"/>
+    <mergeCell ref="K73:M73"/>
     <mergeCell ref="G62:K62"/>
+    <mergeCell ref="K82:M82"/>
     <mergeCell ref="T52:Y52"/>
+    <mergeCell ref="N75:Q75"/>
+    <mergeCell ref="K66:M66"/>
+    <mergeCell ref="R69:U69"/>
     <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="R78:U78"/>
     <mergeCell ref="AK1:AO1"/>
+    <mergeCell ref="N77:Q77"/>
     <mergeCell ref="AH60:AO60"/>
     <mergeCell ref="AK50:AO50"/>
+    <mergeCell ref="K74:M74"/>
+    <mergeCell ref="K68:M68"/>
     <mergeCell ref="AA1:AE1"/>
-    <mergeCell ref="T55:AA57"/>
-    <mergeCell ref="L1:P1"/>
-    <mergeCell ref="AH61:AO61"/>
+    <mergeCell ref="R82:U82"/>
+    <mergeCell ref="N76:Q76"/>
     <mergeCell ref="AK53:AO53"/>
+    <mergeCell ref="B67:J67"/>
+    <mergeCell ref="V68:AO68"/>
+    <mergeCell ref="V82:AO82"/>
     <mergeCell ref="AP32:AP41"/>
-    <mergeCell ref="AB57:AO57"/>
+    <mergeCell ref="B69:J69"/>
+    <mergeCell ref="B78:J78"/>
+    <mergeCell ref="V67:AO67"/>
+    <mergeCell ref="K71:M71"/>
+    <mergeCell ref="B80:J80"/>
+    <mergeCell ref="N66:Q66"/>
+    <mergeCell ref="K80:M80"/>
+    <mergeCell ref="V78:AO78"/>
+    <mergeCell ref="AK51:AO51"/>
+    <mergeCell ref="AL59:AO59"/>
+    <mergeCell ref="AP42:AP51"/>
+    <mergeCell ref="B74:J74"/>
+    <mergeCell ref="B68:J68"/>
+    <mergeCell ref="R79:U79"/>
+    <mergeCell ref="N72:Q72"/>
+    <mergeCell ref="B76:J76"/>
+    <mergeCell ref="N81:Q81"/>
+    <mergeCell ref="K69:M69"/>
+    <mergeCell ref="Z43:AI43"/>
   </mergeCells>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup paperSize="8" orientation="landscape"/>
 </worksheet>
@@ -4616,7 +5741,7 @@
       <c r="AO1" s="39"/>
     </row>
     <row r="2" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="33" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1"/>
@@ -4659,12 +5784,12 @@
       <c r="AM2" s="2"/>
       <c r="AN2" s="2"/>
       <c r="AO2" s="3"/>
-      <c r="AP2" s="34" t="s">
+      <c r="AP2" s="33" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A3" s="35"/>
+      <c r="A3" s="34"/>
       <c r="B3" s="4"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -4705,10 +5830,10 @@
       <c r="AM3" s="5"/>
       <c r="AN3" s="5"/>
       <c r="AO3" s="6"/>
-      <c r="AP3" s="35"/>
+      <c r="AP3" s="34"/>
     </row>
     <row r="4" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A4" s="35"/>
+      <c r="A4" s="34"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -4749,10 +5874,10 @@
       <c r="AM4" s="5"/>
       <c r="AN4" s="5"/>
       <c r="AO4" s="6"/>
-      <c r="AP4" s="35"/>
+      <c r="AP4" s="34"/>
     </row>
     <row r="5" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A5" s="35"/>
+      <c r="A5" s="34"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -4793,10 +5918,10 @@
       <c r="AM5" s="5"/>
       <c r="AN5" s="5"/>
       <c r="AO5" s="6"/>
-      <c r="AP5" s="35"/>
+      <c r="AP5" s="34"/>
     </row>
     <row r="6" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A6" s="35"/>
+      <c r="A6" s="34"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -4837,10 +5962,10 @@
       <c r="AM6" s="5"/>
       <c r="AN6" s="5"/>
       <c r="AO6" s="6"/>
-      <c r="AP6" s="35"/>
+      <c r="AP6" s="34"/>
     </row>
     <row r="7" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A7" s="35"/>
+      <c r="A7" s="34"/>
       <c r="B7" s="4"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -4881,10 +6006,10 @@
       <c r="AM7" s="5"/>
       <c r="AN7" s="5"/>
       <c r="AO7" s="6"/>
-      <c r="AP7" s="35"/>
+      <c r="AP7" s="34"/>
     </row>
     <row r="8" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A8" s="35"/>
+      <c r="A8" s="34"/>
       <c r="B8" s="4"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -4925,10 +6050,10 @@
       <c r="AM8" s="5"/>
       <c r="AN8" s="5"/>
       <c r="AO8" s="6"/>
-      <c r="AP8" s="35"/>
+      <c r="AP8" s="34"/>
     </row>
     <row r="9" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A9" s="35"/>
+      <c r="A9" s="34"/>
       <c r="B9" s="4"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -4969,10 +6094,10 @@
       <c r="AM9" s="5"/>
       <c r="AN9" s="5"/>
       <c r="AO9" s="6"/>
-      <c r="AP9" s="35"/>
+      <c r="AP9" s="34"/>
     </row>
     <row r="10" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A10" s="35"/>
+      <c r="A10" s="34"/>
       <c r="B10" s="4"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -5013,10 +6138,10 @@
       <c r="AM10" s="5"/>
       <c r="AN10" s="5"/>
       <c r="AO10" s="6"/>
-      <c r="AP10" s="35"/>
+      <c r="AP10" s="34"/>
     </row>
     <row r="11" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A11" s="36"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="4"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -5057,10 +6182,10 @@
       <c r="AM11" s="5"/>
       <c r="AN11" s="5"/>
       <c r="AO11" s="6"/>
-      <c r="AP11" s="36"/>
+      <c r="AP11" s="35"/>
     </row>
     <row r="12" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="33" t="s">
         <v>1</v>
       </c>
       <c r="B12" s="4"/>
@@ -5103,12 +6228,12 @@
       <c r="AM12" s="5"/>
       <c r="AN12" s="5"/>
       <c r="AO12" s="6"/>
-      <c r="AP12" s="34" t="s">
+      <c r="AP12" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A13" s="35"/>
+      <c r="A13" s="34"/>
       <c r="B13" s="4"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
@@ -5149,10 +6274,10 @@
       <c r="AM13" s="5"/>
       <c r="AN13" s="5"/>
       <c r="AO13" s="6"/>
-      <c r="AP13" s="35"/>
+      <c r="AP13" s="34"/>
     </row>
     <row r="14" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A14" s="35"/>
+      <c r="A14" s="34"/>
       <c r="B14" s="4"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -5193,10 +6318,10 @@
       <c r="AM14" s="5"/>
       <c r="AN14" s="5"/>
       <c r="AO14" s="6"/>
-      <c r="AP14" s="35"/>
+      <c r="AP14" s="34"/>
     </row>
     <row r="15" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A15" s="35"/>
+      <c r="A15" s="34"/>
       <c r="B15" s="4"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -5237,10 +6362,10 @@
       <c r="AM15" s="5"/>
       <c r="AN15" s="5"/>
       <c r="AO15" s="6"/>
-      <c r="AP15" s="35"/>
+      <c r="AP15" s="34"/>
     </row>
     <row r="16" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A16" s="35"/>
+      <c r="A16" s="34"/>
       <c r="B16" s="4"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -5281,10 +6406,10 @@
       <c r="AM16" s="5"/>
       <c r="AN16" s="5"/>
       <c r="AO16" s="6"/>
-      <c r="AP16" s="35"/>
+      <c r="AP16" s="34"/>
     </row>
     <row r="17" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A17" s="35"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
@@ -5325,10 +6450,10 @@
       <c r="AM17" s="5"/>
       <c r="AN17" s="5"/>
       <c r="AO17" s="6"/>
-      <c r="AP17" s="35"/>
+      <c r="AP17" s="34"/>
     </row>
     <row r="18" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A18" s="35"/>
+      <c r="A18" s="34"/>
       <c r="B18" s="4"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -5369,10 +6494,10 @@
       <c r="AM18" s="5"/>
       <c r="AN18" s="5"/>
       <c r="AO18" s="6"/>
-      <c r="AP18" s="35"/>
+      <c r="AP18" s="34"/>
     </row>
     <row r="19" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A19" s="35"/>
+      <c r="A19" s="34"/>
       <c r="B19" s="4"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
@@ -5413,10 +6538,10 @@
       <c r="AM19" s="5"/>
       <c r="AN19" s="5"/>
       <c r="AO19" s="6"/>
-      <c r="AP19" s="35"/>
+      <c r="AP19" s="34"/>
     </row>
     <row r="20" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A20" s="35"/>
+      <c r="A20" s="34"/>
       <c r="B20" s="4"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
@@ -5425,32 +6550,32 @@
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
-      <c r="J20" s="60" t="s">
+      <c r="J20" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="K20" s="59"/>
-      <c r="L20" s="59"/>
-      <c r="M20" s="59"/>
-      <c r="N20" s="59"/>
-      <c r="O20" s="59"/>
-      <c r="P20" s="59"/>
-      <c r="Q20" s="59"/>
-      <c r="R20" s="59"/>
-      <c r="S20" s="59"/>
-      <c r="T20" s="59"/>
-      <c r="U20" s="59"/>
-      <c r="V20" s="59"/>
-      <c r="W20" s="59"/>
-      <c r="X20" s="59"/>
-      <c r="Y20" s="59"/>
-      <c r="Z20" s="59"/>
-      <c r="AA20" s="59"/>
-      <c r="AB20" s="59"/>
-      <c r="AC20" s="59"/>
-      <c r="AD20" s="59"/>
-      <c r="AE20" s="59"/>
-      <c r="AF20" s="59"/>
-      <c r="AG20" s="59"/>
+      <c r="K20" s="60"/>
+      <c r="L20" s="60"/>
+      <c r="M20" s="60"/>
+      <c r="N20" s="60"/>
+      <c r="O20" s="60"/>
+      <c r="P20" s="60"/>
+      <c r="Q20" s="60"/>
+      <c r="R20" s="60"/>
+      <c r="S20" s="60"/>
+      <c r="T20" s="60"/>
+      <c r="U20" s="60"/>
+      <c r="V20" s="60"/>
+      <c r="W20" s="60"/>
+      <c r="X20" s="60"/>
+      <c r="Y20" s="60"/>
+      <c r="Z20" s="60"/>
+      <c r="AA20" s="60"/>
+      <c r="AB20" s="60"/>
+      <c r="AC20" s="60"/>
+      <c r="AD20" s="60"/>
+      <c r="AE20" s="60"/>
+      <c r="AF20" s="60"/>
+      <c r="AG20" s="60"/>
       <c r="AH20" s="5"/>
       <c r="AI20" s="5"/>
       <c r="AJ20" s="5"/>
@@ -5459,10 +6584,10 @@
       <c r="AM20" s="5"/>
       <c r="AN20" s="5"/>
       <c r="AO20" s="6"/>
-      <c r="AP20" s="35"/>
+      <c r="AP20" s="34"/>
     </row>
     <row r="21" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A21" s="36"/>
+      <c r="A21" s="35"/>
       <c r="B21" s="4"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
@@ -5471,30 +6596,30 @@
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
-      <c r="J21" s="59"/>
-      <c r="K21" s="59"/>
-      <c r="L21" s="59"/>
-      <c r="M21" s="59"/>
-      <c r="N21" s="59"/>
-      <c r="O21" s="59"/>
-      <c r="P21" s="59"/>
-      <c r="Q21" s="59"/>
-      <c r="R21" s="59"/>
-      <c r="S21" s="59"/>
-      <c r="T21" s="59"/>
-      <c r="U21" s="59"/>
-      <c r="V21" s="59"/>
-      <c r="W21" s="59"/>
-      <c r="X21" s="59"/>
-      <c r="Y21" s="59"/>
-      <c r="Z21" s="59"/>
-      <c r="AA21" s="59"/>
-      <c r="AB21" s="59"/>
-      <c r="AC21" s="59"/>
-      <c r="AD21" s="59"/>
-      <c r="AE21" s="59"/>
-      <c r="AF21" s="59"/>
-      <c r="AG21" s="59"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="60"/>
+      <c r="L21" s="60"/>
+      <c r="M21" s="60"/>
+      <c r="N21" s="60"/>
+      <c r="O21" s="60"/>
+      <c r="P21" s="60"/>
+      <c r="Q21" s="60"/>
+      <c r="R21" s="60"/>
+      <c r="S21" s="60"/>
+      <c r="T21" s="60"/>
+      <c r="U21" s="60"/>
+      <c r="V21" s="60"/>
+      <c r="W21" s="60"/>
+      <c r="X21" s="60"/>
+      <c r="Y21" s="60"/>
+      <c r="Z21" s="60"/>
+      <c r="AA21" s="60"/>
+      <c r="AB21" s="60"/>
+      <c r="AC21" s="60"/>
+      <c r="AD21" s="60"/>
+      <c r="AE21" s="60"/>
+      <c r="AF21" s="60"/>
+      <c r="AG21" s="60"/>
       <c r="AH21" s="5"/>
       <c r="AI21" s="5"/>
       <c r="AJ21" s="5"/>
@@ -5503,10 +6628,10 @@
       <c r="AM21" s="5"/>
       <c r="AN21" s="5"/>
       <c r="AO21" s="6"/>
-      <c r="AP21" s="36"/>
+      <c r="AP21" s="35"/>
     </row>
     <row r="22" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A22" s="34" t="s">
+      <c r="A22" s="33" t="s">
         <v>3</v>
       </c>
       <c r="B22" s="4"/>
@@ -5517,30 +6642,30 @@
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
-      <c r="J22" s="59"/>
-      <c r="K22" s="59"/>
-      <c r="L22" s="59"/>
-      <c r="M22" s="59"/>
-      <c r="N22" s="59"/>
-      <c r="O22" s="59"/>
-      <c r="P22" s="59"/>
-      <c r="Q22" s="59"/>
-      <c r="R22" s="59"/>
-      <c r="S22" s="59"/>
-      <c r="T22" s="59"/>
-      <c r="U22" s="59"/>
-      <c r="V22" s="59"/>
-      <c r="W22" s="59"/>
-      <c r="X22" s="59"/>
-      <c r="Y22" s="59"/>
-      <c r="Z22" s="59"/>
-      <c r="AA22" s="59"/>
-      <c r="AB22" s="59"/>
-      <c r="AC22" s="59"/>
-      <c r="AD22" s="59"/>
-      <c r="AE22" s="59"/>
-      <c r="AF22" s="59"/>
-      <c r="AG22" s="59"/>
+      <c r="J22" s="60"/>
+      <c r="K22" s="60"/>
+      <c r="L22" s="60"/>
+      <c r="M22" s="60"/>
+      <c r="N22" s="60"/>
+      <c r="O22" s="60"/>
+      <c r="P22" s="60"/>
+      <c r="Q22" s="60"/>
+      <c r="R22" s="60"/>
+      <c r="S22" s="60"/>
+      <c r="T22" s="60"/>
+      <c r="U22" s="60"/>
+      <c r="V22" s="60"/>
+      <c r="W22" s="60"/>
+      <c r="X22" s="60"/>
+      <c r="Y22" s="60"/>
+      <c r="Z22" s="60"/>
+      <c r="AA22" s="60"/>
+      <c r="AB22" s="60"/>
+      <c r="AC22" s="60"/>
+      <c r="AD22" s="60"/>
+      <c r="AE22" s="60"/>
+      <c r="AF22" s="60"/>
+      <c r="AG22" s="60"/>
       <c r="AH22" s="5"/>
       <c r="AI22" s="5"/>
       <c r="AJ22" s="5"/>
@@ -5549,12 +6674,12 @@
       <c r="AM22" s="5"/>
       <c r="AN22" s="5"/>
       <c r="AO22" s="6"/>
-      <c r="AP22" s="34" t="s">
+      <c r="AP22" s="33" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A23" s="35"/>
+      <c r="A23" s="34"/>
       <c r="B23" s="4"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
@@ -5595,10 +6720,10 @@
       <c r="AM23" s="5"/>
       <c r="AN23" s="5"/>
       <c r="AO23" s="6"/>
-      <c r="AP23" s="35"/>
+      <c r="AP23" s="34"/>
     </row>
     <row r="24" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A24" s="35"/>
+      <c r="A24" s="34"/>
       <c r="B24" s="4"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
@@ -5639,10 +6764,10 @@
       <c r="AM24" s="5"/>
       <c r="AN24" s="5"/>
       <c r="AO24" s="6"/>
-      <c r="AP24" s="35"/>
+      <c r="AP24" s="34"/>
     </row>
     <row r="25" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A25" s="35"/>
+      <c r="A25" s="34"/>
       <c r="B25" s="4"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
@@ -5683,10 +6808,10 @@
       <c r="AM25" s="5"/>
       <c r="AN25" s="5"/>
       <c r="AO25" s="6"/>
-      <c r="AP25" s="35"/>
+      <c r="AP25" s="34"/>
     </row>
     <row r="26" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A26" s="35"/>
+      <c r="A26" s="34"/>
       <c r="B26" s="4"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
@@ -5727,10 +6852,10 @@
       <c r="AM26" s="5"/>
       <c r="AN26" s="5"/>
       <c r="AO26" s="6"/>
-      <c r="AP26" s="35"/>
+      <c r="AP26" s="34"/>
     </row>
     <row r="27" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A27" s="35"/>
+      <c r="A27" s="34"/>
       <c r="B27" s="4"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -5771,10 +6896,10 @@
       <c r="AM27" s="5"/>
       <c r="AN27" s="5"/>
       <c r="AO27" s="6"/>
-      <c r="AP27" s="35"/>
+      <c r="AP27" s="34"/>
     </row>
     <row r="28" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A28" s="35"/>
+      <c r="A28" s="34"/>
       <c r="B28" s="4"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -5815,10 +6940,10 @@
       <c r="AM28" s="5"/>
       <c r="AN28" s="5"/>
       <c r="AO28" s="6"/>
-      <c r="AP28" s="35"/>
+      <c r="AP28" s="34"/>
     </row>
     <row r="29" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A29" s="35"/>
+      <c r="A29" s="34"/>
       <c r="B29" s="4"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
@@ -5859,10 +6984,10 @@
       <c r="AM29" s="5"/>
       <c r="AN29" s="5"/>
       <c r="AO29" s="6"/>
-      <c r="AP29" s="35"/>
+      <c r="AP29" s="34"/>
     </row>
     <row r="30" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A30" s="35"/>
+      <c r="A30" s="34"/>
       <c r="B30" s="4"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -5903,10 +7028,10 @@
       <c r="AM30" s="5"/>
       <c r="AN30" s="5"/>
       <c r="AO30" s="6"/>
-      <c r="AP30" s="35"/>
+      <c r="AP30" s="34"/>
     </row>
     <row r="31" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A31" s="36"/>
+      <c r="A31" s="35"/>
       <c r="B31" s="4"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -5947,10 +7072,10 @@
       <c r="AM31" s="5"/>
       <c r="AN31" s="5"/>
       <c r="AO31" s="6"/>
-      <c r="AP31" s="36"/>
+      <c r="AP31" s="35"/>
     </row>
     <row r="32" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A32" s="34" t="s">
+      <c r="A32" s="33" t="s">
         <v>4</v>
       </c>
       <c r="B32" s="4"/>
@@ -5993,12 +7118,12 @@
       <c r="AM32" s="5"/>
       <c r="AN32" s="5"/>
       <c r="AO32" s="6"/>
-      <c r="AP32" s="34" t="s">
+      <c r="AP32" s="33" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A33" s="35"/>
+      <c r="A33" s="34"/>
       <c r="B33" s="4"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -6039,10 +7164,10 @@
       <c r="AM33" s="5"/>
       <c r="AN33" s="5"/>
       <c r="AO33" s="6"/>
-      <c r="AP33" s="35"/>
+      <c r="AP33" s="34"/>
     </row>
     <row r="34" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A34" s="35"/>
+      <c r="A34" s="34"/>
       <c r="B34" s="4"/>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
@@ -6083,10 +7208,10 @@
       <c r="AM34" s="5"/>
       <c r="AN34" s="5"/>
       <c r="AO34" s="6"/>
-      <c r="AP34" s="35"/>
+      <c r="AP34" s="34"/>
     </row>
     <row r="35" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A35" s="35"/>
+      <c r="A35" s="34"/>
       <c r="B35" s="4"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
@@ -6127,10 +7252,10 @@
       <c r="AM35" s="5"/>
       <c r="AN35" s="5"/>
       <c r="AO35" s="6"/>
-      <c r="AP35" s="35"/>
+      <c r="AP35" s="34"/>
     </row>
     <row r="36" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A36" s="35"/>
+      <c r="A36" s="34"/>
       <c r="B36" s="4"/>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
@@ -6171,10 +7296,10 @@
       <c r="AM36" s="5"/>
       <c r="AN36" s="5"/>
       <c r="AO36" s="6"/>
-      <c r="AP36" s="35"/>
+      <c r="AP36" s="34"/>
     </row>
     <row r="37" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A37" s="35"/>
+      <c r="A37" s="34"/>
       <c r="B37" s="4"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
@@ -6215,10 +7340,10 @@
       <c r="AM37" s="5"/>
       <c r="AN37" s="5"/>
       <c r="AO37" s="6"/>
-      <c r="AP37" s="35"/>
+      <c r="AP37" s="34"/>
     </row>
     <row r="38" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A38" s="35"/>
+      <c r="A38" s="34"/>
       <c r="B38" s="4"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
@@ -6259,10 +7384,10 @@
       <c r="AM38" s="5"/>
       <c r="AN38" s="5"/>
       <c r="AO38" s="6"/>
-      <c r="AP38" s="35"/>
+      <c r="AP38" s="34"/>
     </row>
     <row r="39" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A39" s="35"/>
+      <c r="A39" s="34"/>
       <c r="B39" s="4"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
@@ -6303,10 +7428,10 @@
       <c r="AM39" s="5"/>
       <c r="AN39" s="5"/>
       <c r="AO39" s="6"/>
-      <c r="AP39" s="35"/>
+      <c r="AP39" s="34"/>
     </row>
     <row r="40" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A40" s="35"/>
+      <c r="A40" s="34"/>
       <c r="B40" s="4"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
@@ -6347,10 +7472,10 @@
       <c r="AM40" s="5"/>
       <c r="AN40" s="5"/>
       <c r="AO40" s="6"/>
-      <c r="AP40" s="35"/>
+      <c r="AP40" s="34"/>
     </row>
     <row r="41" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A41" s="36"/>
+      <c r="A41" s="35"/>
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
@@ -6391,10 +7516,10 @@
       <c r="AM41" s="5"/>
       <c r="AN41" s="5"/>
       <c r="AO41" s="6"/>
-      <c r="AP41" s="36"/>
+      <c r="AP41" s="35"/>
     </row>
     <row r="42" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A42" s="34" t="s">
+      <c r="A42" s="33" t="s">
         <v>5</v>
       </c>
       <c r="B42" s="4"/>
@@ -6437,12 +7562,12 @@
       <c r="AM42" s="5"/>
       <c r="AN42" s="5"/>
       <c r="AO42" s="6"/>
-      <c r="AP42" s="34" t="s">
+      <c r="AP42" s="33" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A43" s="35"/>
+      <c r="A43" s="34"/>
       <c r="B43" s="4"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
@@ -6483,10 +7608,10 @@
       <c r="AM43" s="5"/>
       <c r="AN43" s="5"/>
       <c r="AO43" s="6"/>
-      <c r="AP43" s="35"/>
+      <c r="AP43" s="34"/>
     </row>
     <row r="44" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A44" s="35"/>
+      <c r="A44" s="34"/>
       <c r="B44" s="4"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
@@ -6527,10 +7652,10 @@
       <c r="AM44" s="5"/>
       <c r="AN44" s="5"/>
       <c r="AO44" s="6"/>
-      <c r="AP44" s="35"/>
+      <c r="AP44" s="34"/>
     </row>
     <row r="45" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A45" s="35"/>
+      <c r="A45" s="34"/>
       <c r="B45" s="4"/>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
@@ -6571,10 +7696,10 @@
       <c r="AM45" s="5"/>
       <c r="AN45" s="5"/>
       <c r="AO45" s="6"/>
-      <c r="AP45" s="35"/>
+      <c r="AP45" s="34"/>
     </row>
     <row r="46" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A46" s="35"/>
+      <c r="A46" s="34"/>
       <c r="B46" s="4"/>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
@@ -6615,10 +7740,10 @@
       <c r="AM46" s="5"/>
       <c r="AN46" s="5"/>
       <c r="AO46" s="6"/>
-      <c r="AP46" s="35"/>
+      <c r="AP46" s="34"/>
     </row>
     <row r="47" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A47" s="35"/>
+      <c r="A47" s="34"/>
       <c r="B47" s="4"/>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
@@ -6659,10 +7784,10 @@
       <c r="AM47" s="5"/>
       <c r="AN47" s="5"/>
       <c r="AO47" s="6"/>
-      <c r="AP47" s="35"/>
+      <c r="AP47" s="34"/>
     </row>
     <row r="48" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A48" s="35"/>
+      <c r="A48" s="34"/>
       <c r="B48" s="4"/>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
@@ -6703,10 +7828,10 @@
       <c r="AM48" s="5"/>
       <c r="AN48" s="5"/>
       <c r="AO48" s="6"/>
-      <c r="AP48" s="35"/>
+      <c r="AP48" s="34"/>
     </row>
     <row r="49" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A49" s="35"/>
+      <c r="A49" s="34"/>
       <c r="B49" s="4"/>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
@@ -6747,332 +7872,324 @@
       <c r="AM49" s="5"/>
       <c r="AN49" s="5"/>
       <c r="AO49" s="6"/>
-      <c r="AP49" s="35"/>
-    </row>
-    <row r="50" spans="1:42" ht="22" customHeight="1">
-      <c r="A50" s="35"/>
-      <c r="B50" s="51" t="s">
+      <c r="AP49" s="34"/>
+    </row>
+    <row r="50" spans="1:42" ht="11.5" customHeight="1">
+      <c r="A50" s="34"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="5"/>
+      <c r="Q50" s="5"/>
+      <c r="R50" s="5"/>
+      <c r="S50" s="5"/>
+      <c r="T50" s="5"/>
+      <c r="U50" s="5"/>
+      <c r="V50" s="5"/>
+      <c r="W50" s="5"/>
+      <c r="X50" s="5"/>
+      <c r="Y50" s="5"/>
+      <c r="Z50" s="5"/>
+      <c r="AA50" s="5"/>
+      <c r="AB50" s="5"/>
+      <c r="AC50" s="5"/>
+      <c r="AD50" s="5"/>
+      <c r="AE50" s="5"/>
+      <c r="AF50" s="5"/>
+      <c r="AG50" s="5"/>
+      <c r="AH50" s="5"/>
+      <c r="AI50" s="5"/>
+      <c r="AJ50" s="5"/>
+      <c r="AK50" s="5"/>
+      <c r="AL50" s="5"/>
+      <c r="AM50" s="5"/>
+      <c r="AN50" s="5"/>
+      <c r="AO50" s="6"/>
+      <c r="AP50" s="34"/>
+    </row>
+    <row r="51" spans="1:42" ht="11.5" customHeight="1">
+      <c r="A51" s="35"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="5"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="5"/>
+      <c r="Q51" s="5"/>
+      <c r="R51" s="5"/>
+      <c r="S51" s="5"/>
+      <c r="T51" s="5"/>
+      <c r="U51" s="5"/>
+      <c r="V51" s="5"/>
+      <c r="W51" s="5"/>
+      <c r="X51" s="5"/>
+      <c r="Y51" s="5"/>
+      <c r="Z51" s="5"/>
+      <c r="AA51" s="5"/>
+      <c r="AB51" s="5"/>
+      <c r="AC51" s="5"/>
+      <c r="AD51" s="5"/>
+      <c r="AE51" s="5"/>
+      <c r="AF51" s="5"/>
+      <c r="AG51" s="5"/>
+      <c r="AH51" s="5"/>
+      <c r="AI51" s="5"/>
+      <c r="AJ51" s="5"/>
+      <c r="AK51" s="5"/>
+      <c r="AL51" s="5"/>
+      <c r="AM51" s="5"/>
+      <c r="AN51" s="5"/>
+      <c r="AO51" s="6"/>
+      <c r="AP51" s="35"/>
+    </row>
+    <row r="52" spans="1:42" ht="11.5" customHeight="1">
+      <c r="A52" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="5"/>
+      <c r="Q52" s="5"/>
+      <c r="R52" s="5"/>
+      <c r="S52" s="5"/>
+      <c r="T52" s="5"/>
+      <c r="U52" s="5"/>
+      <c r="V52" s="5"/>
+      <c r="W52" s="5"/>
+      <c r="X52" s="5"/>
+      <c r="Y52" s="5"/>
+      <c r="Z52" s="5"/>
+      <c r="AA52" s="5"/>
+      <c r="AB52" s="5"/>
+      <c r="AC52" s="5"/>
+      <c r="AD52" s="5"/>
+      <c r="AE52" s="5"/>
+      <c r="AF52" s="5"/>
+      <c r="AG52" s="5"/>
+      <c r="AH52" s="5"/>
+      <c r="AI52" s="5"/>
+      <c r="AJ52" s="5"/>
+      <c r="AK52" s="5"/>
+      <c r="AL52" s="5"/>
+      <c r="AM52" s="5"/>
+      <c r="AN52" s="5"/>
+      <c r="AO52" s="6"/>
+      <c r="AP52" s="33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:42" ht="11.5" customHeight="1">
+      <c r="A53" s="34"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="5"/>
+      <c r="Q53" s="5"/>
+      <c r="R53" s="5"/>
+      <c r="S53" s="5"/>
+      <c r="T53" s="5"/>
+      <c r="U53" s="5"/>
+      <c r="V53" s="5"/>
+      <c r="W53" s="5"/>
+      <c r="X53" s="5"/>
+      <c r="Y53" s="5"/>
+      <c r="Z53" s="5"/>
+      <c r="AA53" s="5"/>
+      <c r="AB53" s="5"/>
+      <c r="AC53" s="5"/>
+      <c r="AD53" s="5"/>
+      <c r="AE53" s="5"/>
+      <c r="AF53" s="5"/>
+      <c r="AG53" s="5"/>
+      <c r="AH53" s="5"/>
+      <c r="AI53" s="5"/>
+      <c r="AJ53" s="5"/>
+      <c r="AK53" s="5"/>
+      <c r="AL53" s="5"/>
+      <c r="AM53" s="5"/>
+      <c r="AN53" s="5"/>
+      <c r="AO53" s="6"/>
+      <c r="AP53" s="34"/>
+    </row>
+    <row r="54" spans="1:42" ht="22" customHeight="1">
+      <c r="A54" s="34"/>
+      <c r="B54" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="C50" s="52"/>
-      <c r="D50" s="61" t="s">
+      <c r="C54" s="53"/>
+      <c r="D54" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="E50" s="62"/>
-      <c r="F50" s="52"/>
-      <c r="G50" s="61" t="s">
+      <c r="E54" s="63"/>
+      <c r="F54" s="53"/>
+      <c r="G54" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="H50" s="62"/>
-      <c r="I50" s="62"/>
-      <c r="J50" s="62"/>
-      <c r="K50" s="62"/>
-      <c r="L50" s="62"/>
-      <c r="M50" s="62"/>
-      <c r="N50" s="62"/>
-      <c r="O50" s="52"/>
-      <c r="P50" s="61" t="s">
+      <c r="H54" s="63"/>
+      <c r="I54" s="63"/>
+      <c r="J54" s="53"/>
+      <c r="K54" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="Q50" s="52"/>
-      <c r="R50" s="61" t="s">
+      <c r="L54" s="53"/>
+      <c r="M54" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="S50" s="80"/>
-      <c r="T50" s="54" t="s">
+      <c r="N54" s="80"/>
+      <c r="O54" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="P54" s="49"/>
+      <c r="Q54" s="56"/>
+      <c r="R54" s="73" t="s">
+        <v>19</v>
+      </c>
+      <c r="S54" s="49"/>
+      <c r="T54" s="56"/>
+      <c r="U54" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="U50" s="49"/>
-      <c r="V50" s="49"/>
-      <c r="W50" s="49"/>
-      <c r="X50" s="49"/>
-      <c r="Y50" s="55"/>
-      <c r="Z50" s="72" t="s">
+      <c r="V54" s="49"/>
+      <c r="W54" s="49"/>
+      <c r="X54" s="56"/>
+      <c r="Y54" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="AA50" s="49"/>
-      <c r="AB50" s="49"/>
-      <c r="AC50" s="49"/>
-      <c r="AD50" s="49"/>
-      <c r="AE50" s="55"/>
-      <c r="AF50" s="72" t="s">
+      <c r="Z54" s="49"/>
+      <c r="AA54" s="49"/>
+      <c r="AB54" s="56"/>
+      <c r="AC54" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="AG50" s="49"/>
-      <c r="AH50" s="49"/>
-      <c r="AI50" s="49"/>
-      <c r="AJ50" s="55"/>
-      <c r="AK50" s="48" t="s">
+      <c r="AD54" s="49"/>
+      <c r="AE54" s="56"/>
+      <c r="AF54" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="AL50" s="49"/>
-      <c r="AM50" s="49"/>
-      <c r="AN50" s="49"/>
-      <c r="AO50" s="50"/>
-      <c r="AP50" s="35"/>
-    </row>
-    <row r="51" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A51" s="36"/>
-      <c r="B51" s="7" t="s">
+      <c r="AG54" s="49"/>
+      <c r="AH54" s="56"/>
+      <c r="AI54" s="73" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ54" s="49"/>
+      <c r="AK54" s="49"/>
+      <c r="AL54" s="56"/>
+      <c r="AM54" s="48" t="s">
+        <v>21</v>
+      </c>
+      <c r="AN54" s="49"/>
+      <c r="AO54" s="50"/>
+      <c r="AP54" s="34"/>
+    </row>
+    <row r="55" spans="1:42" ht="11.5" customHeight="1">
+      <c r="A55" s="34"/>
+      <c r="B55" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C51" s="8"/>
-      <c r="D51" s="9" t="s">
+      <c r="C55" s="8"/>
+      <c r="D55" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E51" s="10"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="10"/>
-      <c r="M51" s="10"/>
-      <c r="N51" s="10"/>
-      <c r="O51" s="8"/>
-      <c r="P51" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="13"/>
-      <c r="S51" s="11"/>
-      <c r="T51" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="U51" s="25"/>
-      <c r="V51" s="25"/>
-      <c r="W51" s="25"/>
-      <c r="X51" s="25"/>
-      <c r="Y51" s="41"/>
-      <c r="Z51" s="40" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA51" s="25"/>
-      <c r="AB51" s="25"/>
-      <c r="AC51" s="25"/>
-      <c r="AD51" s="25"/>
-      <c r="AE51" s="41"/>
-      <c r="AF51" s="40"/>
-      <c r="AG51" s="25"/>
-      <c r="AH51" s="25"/>
-      <c r="AI51" s="25"/>
-      <c r="AJ51" s="41"/>
-      <c r="AK51" s="71"/>
-      <c r="AL51" s="25"/>
-      <c r="AM51" s="25"/>
-      <c r="AN51" s="25"/>
-      <c r="AO51" s="26"/>
-      <c r="AP51" s="36"/>
-    </row>
-    <row r="52" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A52" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="B52" s="12"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="10"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="10"/>
-      <c r="K52" s="10"/>
-      <c r="L52" s="10"/>
-      <c r="M52" s="10"/>
-      <c r="N52" s="10"/>
-      <c r="O52" s="8"/>
-      <c r="P52" s="13"/>
-      <c r="Q52" s="8"/>
-      <c r="R52" s="13"/>
-      <c r="S52" s="11"/>
-      <c r="T52" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="U52" s="43"/>
-      <c r="V52" s="43"/>
-      <c r="W52" s="43"/>
-      <c r="X52" s="43"/>
-      <c r="Y52" s="44"/>
-      <c r="Z52" s="73" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA52" s="43"/>
-      <c r="AB52" s="43"/>
-      <c r="AC52" s="43"/>
-      <c r="AD52" s="43"/>
-      <c r="AE52" s="44"/>
-      <c r="AF52" s="73" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG52" s="43"/>
-      <c r="AH52" s="43"/>
-      <c r="AI52" s="43"/>
-      <c r="AJ52" s="44"/>
-      <c r="AK52" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="AL52" s="43"/>
-      <c r="AM52" s="43"/>
-      <c r="AN52" s="43"/>
-      <c r="AO52" s="47"/>
-      <c r="AP52" s="34" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="53" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A53" s="35"/>
-      <c r="B53" s="12"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="8"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
-      <c r="K53" s="10"/>
-      <c r="L53" s="10"/>
-      <c r="M53" s="10"/>
-      <c r="N53" s="10"/>
-      <c r="O53" s="8"/>
-      <c r="P53" s="13"/>
-      <c r="Q53" s="8"/>
-      <c r="R53" s="13"/>
-      <c r="S53" s="11"/>
-      <c r="T53" s="57" t="s">
-        <v>23</v>
-      </c>
-      <c r="U53" s="25"/>
-      <c r="V53" s="25"/>
-      <c r="W53" s="25"/>
-      <c r="X53" s="25"/>
-      <c r="Y53" s="41"/>
-      <c r="Z53" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA53" s="25"/>
-      <c r="AB53" s="25"/>
-      <c r="AC53" s="25"/>
-      <c r="AD53" s="25"/>
-      <c r="AE53" s="41"/>
-      <c r="AF53" s="81" t="s">
-        <v>11</v>
-      </c>
-      <c r="AG53" s="25"/>
-      <c r="AH53" s="25"/>
-      <c r="AI53" s="25"/>
-      <c r="AJ53" s="41"/>
-      <c r="AK53" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="AL53" s="25"/>
-      <c r="AM53" s="25"/>
-      <c r="AN53" s="25"/>
-      <c r="AO53" s="26"/>
-      <c r="AP53" s="35"/>
-    </row>
-    <row r="54" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A54" s="35"/>
-      <c r="B54" s="12"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="10"/>
-      <c r="N54" s="10"/>
-      <c r="O54" s="8"/>
-      <c r="P54" s="13"/>
-      <c r="Q54" s="8"/>
-      <c r="R54" s="13"/>
-      <c r="S54" s="11"/>
-      <c r="T54" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="U54" s="43"/>
-      <c r="V54" s="43"/>
-      <c r="W54" s="43"/>
-      <c r="X54" s="43"/>
-      <c r="Y54" s="43"/>
-      <c r="Z54" s="43"/>
-      <c r="AA54" s="44"/>
-      <c r="AB54" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC54" s="43"/>
-      <c r="AD54" s="43"/>
-      <c r="AE54" s="43"/>
-      <c r="AF54" s="43"/>
-      <c r="AG54" s="43"/>
-      <c r="AH54" s="43"/>
-      <c r="AI54" s="43"/>
-      <c r="AJ54" s="43"/>
-      <c r="AK54" s="43"/>
-      <c r="AL54" s="43"/>
-      <c r="AM54" s="43"/>
-      <c r="AN54" s="43"/>
-      <c r="AO54" s="47"/>
-      <c r="AP54" s="35"/>
-    </row>
-    <row r="55" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A55" s="35"/>
-      <c r="B55" s="12"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="13"/>
       <c r="E55" s="10"/>
       <c r="F55" s="8"/>
-      <c r="G55" s="13"/>
+      <c r="G55" s="9" t="s">
+        <v>84</v>
+      </c>
       <c r="H55" s="10"/>
       <c r="I55" s="10"/>
-      <c r="J55" s="10"/>
-      <c r="K55" s="10"/>
-      <c r="L55" s="10"/>
-      <c r="M55" s="10"/>
-      <c r="N55" s="10"/>
-      <c r="O55" s="8"/>
-      <c r="P55" s="13"/>
-      <c r="Q55" s="8"/>
-      <c r="R55" s="13"/>
-      <c r="S55" s="11"/>
-      <c r="T55" s="63" t="s">
-        <v>27</v>
-      </c>
-      <c r="U55" s="64"/>
-      <c r="V55" s="64"/>
-      <c r="W55" s="64"/>
-      <c r="X55" s="64"/>
-      <c r="Y55" s="64"/>
-      <c r="Z55" s="64"/>
+      <c r="J55" s="8"/>
+      <c r="K55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="L55" s="8"/>
+      <c r="M55" s="13"/>
+      <c r="N55" s="11"/>
+      <c r="O55" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="P55" s="65"/>
+      <c r="Q55" s="66"/>
+      <c r="R55" s="83" t="s">
+        <v>23</v>
+      </c>
+      <c r="S55" s="65"/>
+      <c r="T55" s="66"/>
+      <c r="U55" s="83" t="s">
+        <v>13</v>
+      </c>
+      <c r="V55" s="65"/>
+      <c r="W55" s="65"/>
+      <c r="X55" s="66"/>
+      <c r="Y55" s="83" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z55" s="65"/>
       <c r="AA55" s="65"/>
-      <c r="AB55" s="56" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC55" s="25"/>
-      <c r="AD55" s="25"/>
-      <c r="AE55" s="25"/>
-      <c r="AF55" s="25"/>
-      <c r="AG55" s="25"/>
-      <c r="AH55" s="25"/>
-      <c r="AI55" s="25"/>
-      <c r="AJ55" s="25"/>
-      <c r="AK55" s="25"/>
-      <c r="AL55" s="25"/>
-      <c r="AM55" s="25"/>
-      <c r="AN55" s="25"/>
-      <c r="AO55" s="26"/>
-      <c r="AP55" s="35"/>
+      <c r="AB55" s="66"/>
+      <c r="AC55" s="83"/>
+      <c r="AD55" s="65"/>
+      <c r="AE55" s="66"/>
+      <c r="AF55" s="83"/>
+      <c r="AG55" s="65"/>
+      <c r="AH55" s="66"/>
+      <c r="AI55" s="83" t="s">
+        <v>24</v>
+      </c>
+      <c r="AJ55" s="65"/>
+      <c r="AK55" s="65"/>
+      <c r="AL55" s="66"/>
+      <c r="AM55" s="91" t="s">
+        <v>11</v>
+      </c>
+      <c r="AN55" s="65"/>
+      <c r="AO55" s="92"/>
+      <c r="AP55" s="34"/>
     </row>
     <row r="56" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A56" s="35"/>
+      <c r="A56" s="34"/>
       <c r="B56" s="12"/>
       <c r="C56" s="8"/>
       <c r="D56" s="13"/>
@@ -7081,44 +8198,42 @@
       <c r="G56" s="13"/>
       <c r="H56" s="10"/>
       <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
-      <c r="K56" s="10"/>
-      <c r="L56" s="10"/>
-      <c r="M56" s="10"/>
-      <c r="N56" s="10"/>
-      <c r="O56" s="8"/>
-      <c r="P56" s="13"/>
-      <c r="Q56" s="8"/>
-      <c r="R56" s="13"/>
-      <c r="S56" s="11"/>
+      <c r="J56" s="8"/>
+      <c r="K56" s="13"/>
+      <c r="L56" s="8"/>
+      <c r="M56" s="13"/>
+      <c r="N56" s="11"/>
+      <c r="O56" s="67"/>
+      <c r="P56" s="65"/>
+      <c r="Q56" s="66"/>
+      <c r="R56" s="84"/>
+      <c r="S56" s="65"/>
       <c r="T56" s="66"/>
-      <c r="U56" s="64"/>
-      <c r="V56" s="64"/>
-      <c r="W56" s="64"/>
-      <c r="X56" s="64"/>
-      <c r="Y56" s="64"/>
-      <c r="Z56" s="64"/>
+      <c r="U56" s="84"/>
+      <c r="V56" s="65"/>
+      <c r="W56" s="65"/>
+      <c r="X56" s="66"/>
+      <c r="Y56" s="84"/>
+      <c r="Z56" s="65"/>
       <c r="AA56" s="65"/>
-      <c r="AB56" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC56" s="43"/>
-      <c r="AD56" s="43"/>
-      <c r="AE56" s="43"/>
-      <c r="AF56" s="43"/>
-      <c r="AG56" s="43"/>
-      <c r="AH56" s="43"/>
-      <c r="AI56" s="43"/>
-      <c r="AJ56" s="43"/>
-      <c r="AK56" s="43"/>
-      <c r="AL56" s="43"/>
-      <c r="AM56" s="43"/>
-      <c r="AN56" s="43"/>
-      <c r="AO56" s="47"/>
-      <c r="AP56" s="35"/>
+      <c r="AB56" s="66"/>
+      <c r="AC56" s="84"/>
+      <c r="AD56" s="65"/>
+      <c r="AE56" s="66"/>
+      <c r="AF56" s="84"/>
+      <c r="AG56" s="65"/>
+      <c r="AH56" s="66"/>
+      <c r="AI56" s="84"/>
+      <c r="AJ56" s="65"/>
+      <c r="AK56" s="65"/>
+      <c r="AL56" s="66"/>
+      <c r="AM56" s="84"/>
+      <c r="AN56" s="65"/>
+      <c r="AO56" s="92"/>
+      <c r="AP56" s="34"/>
     </row>
     <row r="57" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A57" s="35"/>
+      <c r="A57" s="34"/>
       <c r="B57" s="12"/>
       <c r="C57" s="8"/>
       <c r="D57" s="13"/>
@@ -7127,44 +8242,42 @@
       <c r="G57" s="13"/>
       <c r="H57" s="10"/>
       <c r="I57" s="10"/>
-      <c r="J57" s="10"/>
-      <c r="K57" s="10"/>
-      <c r="L57" s="10"/>
-      <c r="M57" s="10"/>
-      <c r="N57" s="10"/>
-      <c r="O57" s="8"/>
-      <c r="P57" s="13"/>
-      <c r="Q57" s="8"/>
-      <c r="R57" s="13"/>
-      <c r="S57" s="11"/>
-      <c r="T57" s="67"/>
-      <c r="U57" s="25"/>
+      <c r="J57" s="8"/>
+      <c r="K57" s="13"/>
+      <c r="L57" s="8"/>
+      <c r="M57" s="13"/>
+      <c r="N57" s="11"/>
+      <c r="O57" s="68"/>
+      <c r="P57" s="25"/>
+      <c r="Q57" s="41"/>
+      <c r="R57" s="85"/>
+      <c r="S57" s="25"/>
+      <c r="T57" s="41"/>
+      <c r="U57" s="85"/>
       <c r="V57" s="25"/>
       <c r="W57" s="25"/>
-      <c r="X57" s="25"/>
-      <c r="Y57" s="25"/>
+      <c r="X57" s="41"/>
+      <c r="Y57" s="85"/>
       <c r="Z57" s="25"/>
-      <c r="AA57" s="41"/>
-      <c r="AB57" s="71" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC57" s="25"/>
+      <c r="AA57" s="25"/>
+      <c r="AB57" s="41"/>
+      <c r="AC57" s="85"/>
       <c r="AD57" s="25"/>
-      <c r="AE57" s="25"/>
-      <c r="AF57" s="25"/>
+      <c r="AE57" s="41"/>
+      <c r="AF57" s="85"/>
       <c r="AG57" s="25"/>
-      <c r="AH57" s="25"/>
-      <c r="AI57" s="25"/>
+      <c r="AH57" s="41"/>
+      <c r="AI57" s="85"/>
       <c r="AJ57" s="25"/>
       <c r="AK57" s="25"/>
-      <c r="AL57" s="25"/>
-      <c r="AM57" s="25"/>
+      <c r="AL57" s="41"/>
+      <c r="AM57" s="85"/>
       <c r="AN57" s="25"/>
       <c r="AO57" s="26"/>
-      <c r="AP57" s="35"/>
+      <c r="AP57" s="34"/>
     </row>
     <row r="58" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A58" s="35"/>
+      <c r="A58" s="34"/>
       <c r="B58" s="12"/>
       <c r="C58" s="8"/>
       <c r="D58" s="13"/>
@@ -7173,48 +8286,52 @@
       <c r="G58" s="13"/>
       <c r="H58" s="10"/>
       <c r="I58" s="10"/>
-      <c r="J58" s="10"/>
-      <c r="K58" s="10"/>
-      <c r="L58" s="10"/>
-      <c r="M58" s="10"/>
-      <c r="N58" s="10"/>
-      <c r="O58" s="8"/>
-      <c r="P58" s="13"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="13"/>
-      <c r="S58" s="11"/>
-      <c r="T58" s="42" t="s">
+      <c r="J58" s="8"/>
+      <c r="K58" s="13"/>
+      <c r="L58" s="8"/>
+      <c r="M58" s="13"/>
+      <c r="N58" s="11"/>
+      <c r="O58" s="42" t="s">
         <v>31</v>
       </c>
+      <c r="P58" s="43"/>
+      <c r="Q58" s="43"/>
+      <c r="R58" s="43"/>
+      <c r="S58" s="43"/>
+      <c r="T58" s="43"/>
       <c r="U58" s="43"/>
-      <c r="V58" s="43"/>
-      <c r="W58" s="43"/>
+      <c r="V58" s="44"/>
+      <c r="W58" s="74" t="s">
+        <v>25</v>
+      </c>
       <c r="X58" s="43"/>
       <c r="Y58" s="43"/>
       <c r="Z58" s="43"/>
       <c r="AA58" s="43"/>
-      <c r="AB58" s="43"/>
-      <c r="AC58" s="43"/>
+      <c r="AB58" s="44"/>
+      <c r="AC58" s="74" t="s">
+        <v>26</v>
+      </c>
       <c r="AD58" s="43"/>
       <c r="AE58" s="43"/>
       <c r="AF58" s="43"/>
-      <c r="AG58" s="44"/>
-      <c r="AH58" s="73" t="s">
+      <c r="AG58" s="43"/>
+      <c r="AH58" s="43"/>
+      <c r="AI58" s="44"/>
+      <c r="AJ58" s="74" t="s">
         <v>32</v>
       </c>
-      <c r="AI58" s="43"/>
-      <c r="AJ58" s="43"/>
-      <c r="AK58" s="44"/>
-      <c r="AL58" s="46" t="s">
+      <c r="AK58" s="43"/>
+      <c r="AL58" s="44"/>
+      <c r="AM58" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="AM58" s="43"/>
       <c r="AN58" s="43"/>
       <c r="AO58" s="47"/>
-      <c r="AP58" s="35"/>
+      <c r="AP58" s="34"/>
     </row>
     <row r="59" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A59" s="35"/>
+      <c r="A59" s="34"/>
       <c r="B59" s="12"/>
       <c r="C59" s="8"/>
       <c r="D59" s="13"/>
@@ -7223,48 +8340,52 @@
       <c r="G59" s="13"/>
       <c r="H59" s="10"/>
       <c r="I59" s="10"/>
-      <c r="J59" s="10"/>
-      <c r="K59" s="10"/>
-      <c r="L59" s="10"/>
-      <c r="M59" s="10"/>
-      <c r="N59" s="10"/>
-      <c r="O59" s="8"/>
-      <c r="P59" s="13"/>
-      <c r="Q59" s="8"/>
-      <c r="R59" s="13"/>
-      <c r="S59" s="11"/>
-      <c r="T59" s="76" t="s">
+      <c r="J59" s="8"/>
+      <c r="K59" s="13"/>
+      <c r="L59" s="8"/>
+      <c r="M59" s="13"/>
+      <c r="N59" s="11"/>
+      <c r="O59" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="U59" s="64"/>
-      <c r="V59" s="64"/>
-      <c r="W59" s="64"/>
-      <c r="X59" s="64"/>
-      <c r="Y59" s="64"/>
-      <c r="Z59" s="64"/>
-      <c r="AA59" s="64"/>
-      <c r="AB59" s="64"/>
-      <c r="AC59" s="64"/>
-      <c r="AD59" s="64"/>
-      <c r="AE59" s="64"/>
-      <c r="AF59" s="64"/>
-      <c r="AG59" s="65"/>
-      <c r="AH59" s="53" t="s">
+      <c r="P59" s="65"/>
+      <c r="Q59" s="65"/>
+      <c r="R59" s="65"/>
+      <c r="S59" s="65"/>
+      <c r="T59" s="65"/>
+      <c r="U59" s="65"/>
+      <c r="V59" s="66"/>
+      <c r="W59" s="86" t="s">
+        <v>27</v>
+      </c>
+      <c r="X59" s="65"/>
+      <c r="Y59" s="65"/>
+      <c r="Z59" s="65"/>
+      <c r="AA59" s="65"/>
+      <c r="AB59" s="66"/>
+      <c r="AC59" s="81" t="s">
+        <v>85</v>
+      </c>
+      <c r="AD59" s="25"/>
+      <c r="AE59" s="25"/>
+      <c r="AF59" s="25"/>
+      <c r="AG59" s="25"/>
+      <c r="AH59" s="25"/>
+      <c r="AI59" s="41"/>
+      <c r="AJ59" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="AI59" s="25"/>
-      <c r="AJ59" s="25"/>
-      <c r="AK59" s="41"/>
-      <c r="AL59" s="82" t="s">
+      <c r="AK59" s="25"/>
+      <c r="AL59" s="41"/>
+      <c r="AM59" s="82" t="s">
         <v>36</v>
       </c>
-      <c r="AM59" s="25"/>
       <c r="AN59" s="25"/>
       <c r="AO59" s="26"/>
-      <c r="AP59" s="35"/>
+      <c r="AP59" s="34"/>
     </row>
     <row r="60" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A60" s="35"/>
+      <c r="A60" s="34"/>
       <c r="B60" s="12"/>
       <c r="C60" s="8"/>
       <c r="D60" s="13"/>
@@ -7273,44 +8394,46 @@
       <c r="G60" s="13"/>
       <c r="H60" s="10"/>
       <c r="I60" s="10"/>
-      <c r="J60" s="10"/>
-      <c r="K60" s="10"/>
-      <c r="L60" s="10"/>
-      <c r="M60" s="10"/>
-      <c r="N60" s="10"/>
-      <c r="O60" s="8"/>
-      <c r="P60" s="13"/>
-      <c r="Q60" s="8"/>
-      <c r="R60" s="13"/>
-      <c r="S60" s="11"/>
-      <c r="T60" s="66"/>
-      <c r="U60" s="64"/>
-      <c r="V60" s="64"/>
-      <c r="W60" s="64"/>
-      <c r="X60" s="64"/>
-      <c r="Y60" s="64"/>
-      <c r="Z60" s="64"/>
-      <c r="AA60" s="64"/>
-      <c r="AB60" s="64"/>
-      <c r="AC60" s="64"/>
-      <c r="AD60" s="64"/>
-      <c r="AE60" s="64"/>
-      <c r="AF60" s="64"/>
-      <c r="AG60" s="65"/>
-      <c r="AH60" s="46" t="s">
+      <c r="J60" s="8"/>
+      <c r="K60" s="13"/>
+      <c r="L60" s="8"/>
+      <c r="M60" s="13"/>
+      <c r="N60" s="11"/>
+      <c r="O60" s="67"/>
+      <c r="P60" s="65"/>
+      <c r="Q60" s="65"/>
+      <c r="R60" s="65"/>
+      <c r="S60" s="65"/>
+      <c r="T60" s="65"/>
+      <c r="U60" s="65"/>
+      <c r="V60" s="66"/>
+      <c r="W60" s="84"/>
+      <c r="X60" s="65"/>
+      <c r="Y60" s="65"/>
+      <c r="Z60" s="65"/>
+      <c r="AA60" s="65"/>
+      <c r="AB60" s="66"/>
+      <c r="AC60" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD60" s="43"/>
+      <c r="AE60" s="43"/>
+      <c r="AF60" s="43"/>
+      <c r="AG60" s="43"/>
+      <c r="AH60" s="43"/>
+      <c r="AI60" s="44"/>
+      <c r="AJ60" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="AI60" s="43"/>
-      <c r="AJ60" s="43"/>
       <c r="AK60" s="43"/>
       <c r="AL60" s="43"/>
       <c r="AM60" s="43"/>
       <c r="AN60" s="43"/>
       <c r="AO60" s="47"/>
-      <c r="AP60" s="35"/>
+      <c r="AP60" s="34"/>
     </row>
     <row r="61" spans="1:42" ht="11.5" customHeight="1">
-      <c r="A61" s="36"/>
+      <c r="A61" s="35"/>
       <c r="B61" s="14"/>
       <c r="C61" s="15"/>
       <c r="D61" s="16"/>
@@ -7319,39 +8442,41 @@
       <c r="G61" s="16"/>
       <c r="H61" s="17"/>
       <c r="I61" s="17"/>
-      <c r="J61" s="17"/>
-      <c r="K61" s="17"/>
-      <c r="L61" s="17"/>
-      <c r="M61" s="17"/>
-      <c r="N61" s="17"/>
-      <c r="O61" s="15"/>
-      <c r="P61" s="16"/>
-      <c r="Q61" s="15"/>
-      <c r="R61" s="16"/>
-      <c r="S61" s="18"/>
-      <c r="T61" s="77"/>
-      <c r="U61" s="69"/>
-      <c r="V61" s="69"/>
-      <c r="W61" s="69"/>
-      <c r="X61" s="69"/>
-      <c r="Y61" s="69"/>
-      <c r="Z61" s="69"/>
-      <c r="AA61" s="69"/>
-      <c r="AB61" s="69"/>
-      <c r="AC61" s="69"/>
-      <c r="AD61" s="69"/>
-      <c r="AE61" s="69"/>
-      <c r="AF61" s="69"/>
-      <c r="AG61" s="78"/>
-      <c r="AH61" s="68"/>
-      <c r="AI61" s="69"/>
+      <c r="J61" s="15"/>
+      <c r="K61" s="16"/>
+      <c r="L61" s="15"/>
+      <c r="M61" s="16"/>
+      <c r="N61" s="18"/>
+      <c r="O61" s="77"/>
+      <c r="P61" s="70"/>
+      <c r="Q61" s="70"/>
+      <c r="R61" s="70"/>
+      <c r="S61" s="70"/>
+      <c r="T61" s="70"/>
+      <c r="U61" s="70"/>
+      <c r="V61" s="78"/>
+      <c r="W61" s="87"/>
+      <c r="X61" s="70"/>
+      <c r="Y61" s="70"/>
+      <c r="Z61" s="70"/>
+      <c r="AA61" s="70"/>
+      <c r="AB61" s="78"/>
+      <c r="AC61" s="89" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD61" s="70"/>
+      <c r="AE61" s="70"/>
+      <c r="AF61" s="70"/>
+      <c r="AG61" s="70"/>
+      <c r="AH61" s="70"/>
+      <c r="AI61" s="78"/>
       <c r="AJ61" s="69"/>
-      <c r="AK61" s="69"/>
-      <c r="AL61" s="69"/>
-      <c r="AM61" s="69"/>
-      <c r="AN61" s="69"/>
-      <c r="AO61" s="70"/>
-      <c r="AP61" s="36"/>
+      <c r="AK61" s="70"/>
+      <c r="AL61" s="70"/>
+      <c r="AM61" s="70"/>
+      <c r="AN61" s="70"/>
+      <c r="AO61" s="71"/>
+      <c r="AP61" s="35"/>
     </row>
     <row r="62" spans="1:42" ht="11.5" customHeight="1">
       <c r="B62" s="37">
@@ -7412,1168 +8537,1171 @@
       <c r="AO62" s="39"/>
     </row>
     <row r="64" spans="1:42">
-      <c r="B64" s="83" t="s">
+      <c r="B64" s="90" t="s">
+        <v>87</v>
+      </c>
+      <c r="C64" s="60"/>
+      <c r="D64" s="60"/>
+      <c r="E64" s="60"/>
+      <c r="F64" s="60"/>
+      <c r="G64" s="60"/>
+      <c r="H64" s="60"/>
+      <c r="I64" s="60"/>
+      <c r="J64" s="60"/>
+      <c r="K64" s="60"/>
+      <c r="L64" s="60"/>
+      <c r="M64" s="60"/>
+      <c r="N64" s="60"/>
+      <c r="O64" s="60"/>
+      <c r="P64" s="60"/>
+      <c r="Q64" s="60"/>
+      <c r="R64" s="60"/>
+      <c r="S64" s="60"/>
+      <c r="T64" s="60"/>
+      <c r="U64" s="60"/>
+      <c r="V64" s="60"/>
+      <c r="W64" s="60"/>
+      <c r="X64" s="60"/>
+      <c r="Y64" s="60"/>
+      <c r="Z64" s="60"/>
+      <c r="AA64" s="60"/>
+      <c r="AB64" s="60"/>
+      <c r="AC64" s="60"/>
+      <c r="AD64" s="60"/>
+      <c r="AE64" s="60"/>
+      <c r="AF64" s="60"/>
+      <c r="AG64" s="60"/>
+      <c r="AH64" s="60"/>
+      <c r="AI64" s="60"/>
+      <c r="AJ64" s="60"/>
+      <c r="AK64" s="60"/>
+      <c r="AL64" s="60"/>
+      <c r="AM64" s="60"/>
+      <c r="AN64" s="60"/>
+      <c r="AO64" s="60"/>
+    </row>
+    <row r="65" spans="2:42">
+      <c r="B65" s="60"/>
+      <c r="C65" s="60"/>
+      <c r="D65" s="60"/>
+      <c r="E65" s="60"/>
+      <c r="F65" s="60"/>
+      <c r="G65" s="60"/>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="60"/>
+      <c r="K65" s="60"/>
+      <c r="L65" s="60"/>
+      <c r="M65" s="60"/>
+      <c r="N65" s="60"/>
+      <c r="O65" s="60"/>
+      <c r="P65" s="60"/>
+      <c r="Q65" s="60"/>
+      <c r="R65" s="60"/>
+      <c r="S65" s="60"/>
+      <c r="T65" s="60"/>
+      <c r="U65" s="60"/>
+      <c r="V65" s="60"/>
+      <c r="W65" s="60"/>
+      <c r="X65" s="60"/>
+      <c r="Y65" s="60"/>
+      <c r="Z65" s="60"/>
+      <c r="AA65" s="60"/>
+      <c r="AB65" s="60"/>
+      <c r="AC65" s="60"/>
+      <c r="AD65" s="60"/>
+      <c r="AE65" s="60"/>
+      <c r="AF65" s="60"/>
+      <c r="AG65" s="60"/>
+      <c r="AH65" s="60"/>
+      <c r="AI65" s="60"/>
+      <c r="AJ65" s="60"/>
+      <c r="AK65" s="60"/>
+      <c r="AL65" s="60"/>
+      <c r="AM65" s="60"/>
+      <c r="AN65" s="60"/>
+      <c r="AO65" s="60"/>
+    </row>
+    <row r="66" spans="2:42">
+      <c r="B66" s="60"/>
+      <c r="C66" s="60"/>
+      <c r="D66" s="60"/>
+      <c r="E66" s="60"/>
+      <c r="F66" s="60"/>
+      <c r="G66" s="60"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
+      <c r="J66" s="60"/>
+      <c r="K66" s="60"/>
+      <c r="L66" s="60"/>
+      <c r="M66" s="60"/>
+      <c r="N66" s="60"/>
+      <c r="O66" s="60"/>
+      <c r="P66" s="60"/>
+      <c r="Q66" s="60"/>
+      <c r="R66" s="60"/>
+      <c r="S66" s="60"/>
+      <c r="T66" s="60"/>
+      <c r="U66" s="60"/>
+      <c r="V66" s="60"/>
+      <c r="W66" s="60"/>
+      <c r="X66" s="60"/>
+      <c r="Y66" s="60"/>
+      <c r="Z66" s="60"/>
+      <c r="AA66" s="60"/>
+      <c r="AB66" s="60"/>
+      <c r="AC66" s="60"/>
+      <c r="AD66" s="60"/>
+      <c r="AE66" s="60"/>
+      <c r="AF66" s="60"/>
+      <c r="AG66" s="60"/>
+      <c r="AH66" s="60"/>
+      <c r="AI66" s="60"/>
+      <c r="AJ66" s="60"/>
+      <c r="AK66" s="60"/>
+      <c r="AL66" s="60"/>
+      <c r="AM66" s="60"/>
+      <c r="AN66" s="60"/>
+      <c r="AO66" s="60"/>
+    </row>
+    <row r="69" spans="2:42">
+      <c r="C69" s="45" t="s">
+        <v>40</v>
+      </c>
+      <c r="D69" s="31"/>
+      <c r="E69" s="31"/>
+      <c r="F69" s="31"/>
+      <c r="G69" s="31"/>
+      <c r="H69" s="31"/>
+      <c r="I69" s="31"/>
+      <c r="J69" s="31"/>
+      <c r="K69" s="32"/>
+      <c r="L69" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="M69" s="31"/>
+      <c r="N69" s="32"/>
+      <c r="O69" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="P69" s="31"/>
+      <c r="Q69" s="31"/>
+      <c r="R69" s="32"/>
+      <c r="S69" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="T69" s="31"/>
+      <c r="U69" s="31"/>
+      <c r="V69" s="32"/>
+      <c r="W69" s="45" t="s">
+        <v>44</v>
+      </c>
+      <c r="X69" s="31"/>
+      <c r="Y69" s="31"/>
+      <c r="Z69" s="31"/>
+      <c r="AA69" s="31"/>
+      <c r="AB69" s="31"/>
+      <c r="AC69" s="31"/>
+      <c r="AD69" s="31"/>
+      <c r="AE69" s="31"/>
+      <c r="AF69" s="31"/>
+      <c r="AG69" s="31"/>
+      <c r="AH69" s="31"/>
+      <c r="AI69" s="31"/>
+      <c r="AJ69" s="31"/>
+      <c r="AK69" s="31"/>
+      <c r="AL69" s="31"/>
+      <c r="AM69" s="31"/>
+      <c r="AN69" s="31"/>
+      <c r="AO69" s="31"/>
+      <c r="AP69" s="32"/>
+    </row>
+    <row r="70" spans="2:42">
+      <c r="C70" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="D70" s="28"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="28"/>
+      <c r="H70" s="28"/>
+      <c r="I70" s="28"/>
+      <c r="J70" s="28"/>
+      <c r="K70" s="29"/>
+      <c r="L70" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="M70" s="28"/>
+      <c r="N70" s="29"/>
+      <c r="O70" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="P70" s="28"/>
+      <c r="Q70" s="28"/>
+      <c r="R70" s="29"/>
+      <c r="S70" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="T70" s="28"/>
+      <c r="U70" s="28"/>
+      <c r="V70" s="29"/>
+      <c r="W70" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="X70" s="28"/>
+      <c r="Y70" s="28"/>
+      <c r="Z70" s="28"/>
+      <c r="AA70" s="28"/>
+      <c r="AB70" s="28"/>
+      <c r="AC70" s="28"/>
+      <c r="AD70" s="28"/>
+      <c r="AE70" s="28"/>
+      <c r="AF70" s="28"/>
+      <c r="AG70" s="28"/>
+      <c r="AH70" s="28"/>
+      <c r="AI70" s="28"/>
+      <c r="AJ70" s="28"/>
+      <c r="AK70" s="28"/>
+      <c r="AL70" s="28"/>
+      <c r="AM70" s="28"/>
+      <c r="AN70" s="28"/>
+      <c r="AO70" s="28"/>
+      <c r="AP70" s="29"/>
+    </row>
+    <row r="71" spans="2:42">
+      <c r="C71" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="D71" s="28"/>
+      <c r="E71" s="28"/>
+      <c r="F71" s="28"/>
+      <c r="G71" s="28"/>
+      <c r="H71" s="28"/>
+      <c r="I71" s="28"/>
+      <c r="J71" s="28"/>
+      <c r="K71" s="29"/>
+      <c r="L71" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="M71" s="28"/>
+      <c r="N71" s="29"/>
+      <c r="O71" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="P71" s="28"/>
+      <c r="Q71" s="28"/>
+      <c r="R71" s="29"/>
+      <c r="S71" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="T71" s="28"/>
+      <c r="U71" s="28"/>
+      <c r="V71" s="29"/>
+      <c r="W71" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="X71" s="28"/>
+      <c r="Y71" s="28"/>
+      <c r="Z71" s="28"/>
+      <c r="AA71" s="28"/>
+      <c r="AB71" s="28"/>
+      <c r="AC71" s="28"/>
+      <c r="AD71" s="28"/>
+      <c r="AE71" s="28"/>
+      <c r="AF71" s="28"/>
+      <c r="AG71" s="28"/>
+      <c r="AH71" s="28"/>
+      <c r="AI71" s="28"/>
+      <c r="AJ71" s="28"/>
+      <c r="AK71" s="28"/>
+      <c r="AL71" s="28"/>
+      <c r="AM71" s="28"/>
+      <c r="AN71" s="28"/>
+      <c r="AO71" s="28"/>
+      <c r="AP71" s="29"/>
+    </row>
+    <row r="72" spans="2:42">
+      <c r="C72" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="D72" s="28"/>
+      <c r="E72" s="28"/>
+      <c r="F72" s="28"/>
+      <c r="G72" s="28"/>
+      <c r="H72" s="28"/>
+      <c r="I72" s="28"/>
+      <c r="J72" s="28"/>
+      <c r="K72" s="29"/>
+      <c r="L72" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="M72" s="28"/>
+      <c r="N72" s="29"/>
+      <c r="O72" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="P72" s="28"/>
+      <c r="Q72" s="28"/>
+      <c r="R72" s="29"/>
+      <c r="S72" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="T72" s="28"/>
+      <c r="U72" s="28"/>
+      <c r="V72" s="29"/>
+      <c r="W72" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="X72" s="28"/>
+      <c r="Y72" s="28"/>
+      <c r="Z72" s="28"/>
+      <c r="AA72" s="28"/>
+      <c r="AB72" s="28"/>
+      <c r="AC72" s="28"/>
+      <c r="AD72" s="28"/>
+      <c r="AE72" s="28"/>
+      <c r="AF72" s="28"/>
+      <c r="AG72" s="28"/>
+      <c r="AH72" s="28"/>
+      <c r="AI72" s="28"/>
+      <c r="AJ72" s="28"/>
+      <c r="AK72" s="28"/>
+      <c r="AL72" s="28"/>
+      <c r="AM72" s="28"/>
+      <c r="AN72" s="28"/>
+      <c r="AO72" s="28"/>
+      <c r="AP72" s="29"/>
+    </row>
+    <row r="73" spans="2:42">
+      <c r="C73" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D73" s="28"/>
+      <c r="E73" s="28"/>
+      <c r="F73" s="28"/>
+      <c r="G73" s="28"/>
+      <c r="H73" s="28"/>
+      <c r="I73" s="28"/>
+      <c r="J73" s="28"/>
+      <c r="K73" s="29"/>
+      <c r="L73" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="M73" s="28"/>
+      <c r="N73" s="29"/>
+      <c r="O73" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="P73" s="28"/>
+      <c r="Q73" s="28"/>
+      <c r="R73" s="29"/>
+      <c r="S73" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="T73" s="28"/>
+      <c r="U73" s="28"/>
+      <c r="V73" s="29"/>
+      <c r="W73" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="X73" s="28"/>
+      <c r="Y73" s="28"/>
+      <c r="Z73" s="28"/>
+      <c r="AA73" s="28"/>
+      <c r="AB73" s="28"/>
+      <c r="AC73" s="28"/>
+      <c r="AD73" s="28"/>
+      <c r="AE73" s="28"/>
+      <c r="AF73" s="28"/>
+      <c r="AG73" s="28"/>
+      <c r="AH73" s="28"/>
+      <c r="AI73" s="28"/>
+      <c r="AJ73" s="28"/>
+      <c r="AK73" s="28"/>
+      <c r="AL73" s="28"/>
+      <c r="AM73" s="28"/>
+      <c r="AN73" s="28"/>
+      <c r="AO73" s="28"/>
+      <c r="AP73" s="29"/>
+    </row>
+    <row r="74" spans="2:42">
+      <c r="C74" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="D74" s="31"/>
+      <c r="E74" s="31"/>
+      <c r="F74" s="31"/>
+      <c r="G74" s="31"/>
+      <c r="H74" s="31"/>
+      <c r="I74" s="31"/>
+      <c r="J74" s="31"/>
+      <c r="K74" s="32"/>
+      <c r="L74" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="M74" s="31"/>
+      <c r="N74" s="32"/>
+      <c r="O74" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="P74" s="31"/>
+      <c r="Q74" s="31"/>
+      <c r="R74" s="32"/>
+      <c r="S74" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="T74" s="31"/>
+      <c r="U74" s="31"/>
+      <c r="V74" s="32"/>
+      <c r="W74" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="X74" s="31"/>
+      <c r="Y74" s="31"/>
+      <c r="Z74" s="31"/>
+      <c r="AA74" s="31"/>
+      <c r="AB74" s="31"/>
+      <c r="AC74" s="31"/>
+      <c r="AD74" s="31"/>
+      <c r="AE74" s="31"/>
+      <c r="AF74" s="31"/>
+      <c r="AG74" s="31"/>
+      <c r="AH74" s="31"/>
+      <c r="AI74" s="31"/>
+      <c r="AJ74" s="31"/>
+      <c r="AK74" s="31"/>
+      <c r="AL74" s="31"/>
+      <c r="AM74" s="31"/>
+      <c r="AN74" s="31"/>
+      <c r="AO74" s="31"/>
+      <c r="AP74" s="32"/>
+    </row>
+    <row r="75" spans="2:42">
+      <c r="C75" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="D75" s="31"/>
+      <c r="E75" s="31"/>
+      <c r="F75" s="31"/>
+      <c r="G75" s="31"/>
+      <c r="H75" s="31"/>
+      <c r="I75" s="31"/>
+      <c r="J75" s="31"/>
+      <c r="K75" s="32"/>
+      <c r="L75" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="M75" s="31"/>
+      <c r="N75" s="32"/>
+      <c r="O75" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="P75" s="31"/>
+      <c r="Q75" s="31"/>
+      <c r="R75" s="32"/>
+      <c r="S75" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="T75" s="31"/>
+      <c r="U75" s="31"/>
+      <c r="V75" s="32"/>
+      <c r="W75" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="X75" s="31"/>
+      <c r="Y75" s="31"/>
+      <c r="Z75" s="31"/>
+      <c r="AA75" s="31"/>
+      <c r="AB75" s="31"/>
+      <c r="AC75" s="31"/>
+      <c r="AD75" s="31"/>
+      <c r="AE75" s="31"/>
+      <c r="AF75" s="31"/>
+      <c r="AG75" s="31"/>
+      <c r="AH75" s="31"/>
+      <c r="AI75" s="31"/>
+      <c r="AJ75" s="31"/>
+      <c r="AK75" s="31"/>
+      <c r="AL75" s="31"/>
+      <c r="AM75" s="31"/>
+      <c r="AN75" s="31"/>
+      <c r="AO75" s="31"/>
+      <c r="AP75" s="32"/>
+    </row>
+    <row r="76" spans="2:42">
+      <c r="C76" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D76" s="31"/>
+      <c r="E76" s="31"/>
+      <c r="F76" s="31"/>
+      <c r="G76" s="31"/>
+      <c r="H76" s="31"/>
+      <c r="I76" s="31"/>
+      <c r="J76" s="31"/>
+      <c r="K76" s="32"/>
+      <c r="L76" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="M76" s="31"/>
+      <c r="N76" s="32"/>
+      <c r="O76" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="P76" s="31"/>
+      <c r="Q76" s="31"/>
+      <c r="R76" s="32"/>
+      <c r="S76" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="T76" s="31"/>
+      <c r="U76" s="31"/>
+      <c r="V76" s="32"/>
+      <c r="W76" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="X76" s="31"/>
+      <c r="Y76" s="31"/>
+      <c r="Z76" s="31"/>
+      <c r="AA76" s="31"/>
+      <c r="AB76" s="31"/>
+      <c r="AC76" s="31"/>
+      <c r="AD76" s="31"/>
+      <c r="AE76" s="31"/>
+      <c r="AF76" s="31"/>
+      <c r="AG76" s="31"/>
+      <c r="AH76" s="31"/>
+      <c r="AI76" s="31"/>
+      <c r="AJ76" s="31"/>
+      <c r="AK76" s="31"/>
+      <c r="AL76" s="31"/>
+      <c r="AM76" s="31"/>
+      <c r="AN76" s="31"/>
+      <c r="AO76" s="31"/>
+      <c r="AP76" s="32"/>
+    </row>
+    <row r="77" spans="2:42">
+      <c r="C77" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D77" s="31"/>
+      <c r="E77" s="31"/>
+      <c r="F77" s="31"/>
+      <c r="G77" s="31"/>
+      <c r="H77" s="31"/>
+      <c r="I77" s="31"/>
+      <c r="J77" s="31"/>
+      <c r="K77" s="32"/>
+      <c r="L77" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="M77" s="31"/>
+      <c r="N77" s="32"/>
+      <c r="O77" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="P77" s="31"/>
+      <c r="Q77" s="31"/>
+      <c r="R77" s="32"/>
+      <c r="S77" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="T77" s="31"/>
+      <c r="U77" s="31"/>
+      <c r="V77" s="32"/>
+      <c r="W77" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="X77" s="31"/>
+      <c r="Y77" s="31"/>
+      <c r="Z77" s="31"/>
+      <c r="AA77" s="31"/>
+      <c r="AB77" s="31"/>
+      <c r="AC77" s="31"/>
+      <c r="AD77" s="31"/>
+      <c r="AE77" s="31"/>
+      <c r="AF77" s="31"/>
+      <c r="AG77" s="31"/>
+      <c r="AH77" s="31"/>
+      <c r="AI77" s="31"/>
+      <c r="AJ77" s="31"/>
+      <c r="AK77" s="31"/>
+      <c r="AL77" s="31"/>
+      <c r="AM77" s="31"/>
+      <c r="AN77" s="31"/>
+      <c r="AO77" s="31"/>
+      <c r="AP77" s="32"/>
+    </row>
+    <row r="78" spans="2:42">
+      <c r="C78" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D78" s="31"/>
+      <c r="E78" s="31"/>
+      <c r="F78" s="31"/>
+      <c r="G78" s="31"/>
+      <c r="H78" s="31"/>
+      <c r="I78" s="31"/>
+      <c r="J78" s="31"/>
+      <c r="K78" s="32"/>
+      <c r="L78" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="M78" s="31"/>
+      <c r="N78" s="32"/>
+      <c r="O78" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="P78" s="31"/>
+      <c r="Q78" s="31"/>
+      <c r="R78" s="32"/>
+      <c r="S78" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="T78" s="31"/>
+      <c r="U78" s="31"/>
+      <c r="V78" s="32"/>
+      <c r="W78" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="X78" s="31"/>
+      <c r="Y78" s="31"/>
+      <c r="Z78" s="31"/>
+      <c r="AA78" s="31"/>
+      <c r="AB78" s="31"/>
+      <c r="AC78" s="31"/>
+      <c r="AD78" s="31"/>
+      <c r="AE78" s="31"/>
+      <c r="AF78" s="31"/>
+      <c r="AG78" s="31"/>
+      <c r="AH78" s="31"/>
+      <c r="AI78" s="31"/>
+      <c r="AJ78" s="31"/>
+      <c r="AK78" s="31"/>
+      <c r="AL78" s="31"/>
+      <c r="AM78" s="31"/>
+      <c r="AN78" s="31"/>
+      <c r="AO78" s="31"/>
+      <c r="AP78" s="32"/>
+    </row>
+    <row r="79" spans="2:42">
+      <c r="C79" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D79" s="31"/>
+      <c r="E79" s="31"/>
+      <c r="F79" s="31"/>
+      <c r="G79" s="31"/>
+      <c r="H79" s="31"/>
+      <c r="I79" s="31"/>
+      <c r="J79" s="31"/>
+      <c r="K79" s="32"/>
+      <c r="L79" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="M79" s="31"/>
+      <c r="N79" s="32"/>
+      <c r="O79" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="P79" s="31"/>
+      <c r="Q79" s="31"/>
+      <c r="R79" s="32"/>
+      <c r="S79" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="T79" s="31"/>
+      <c r="U79" s="31"/>
+      <c r="V79" s="32"/>
+      <c r="W79" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="X79" s="31"/>
+      <c r="Y79" s="31"/>
+      <c r="Z79" s="31"/>
+      <c r="AA79" s="31"/>
+      <c r="AB79" s="31"/>
+      <c r="AC79" s="31"/>
+      <c r="AD79" s="31"/>
+      <c r="AE79" s="31"/>
+      <c r="AF79" s="31"/>
+      <c r="AG79" s="31"/>
+      <c r="AH79" s="31"/>
+      <c r="AI79" s="31"/>
+      <c r="AJ79" s="31"/>
+      <c r="AK79" s="31"/>
+      <c r="AL79" s="31"/>
+      <c r="AM79" s="31"/>
+      <c r="AN79" s="31"/>
+      <c r="AO79" s="31"/>
+      <c r="AP79" s="32"/>
+    </row>
+    <row r="80" spans="2:42">
+      <c r="C80" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D80" s="31"/>
+      <c r="E80" s="31"/>
+      <c r="F80" s="31"/>
+      <c r="G80" s="31"/>
+      <c r="H80" s="31"/>
+      <c r="I80" s="31"/>
+      <c r="J80" s="31"/>
+      <c r="K80" s="32"/>
+      <c r="L80" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="M80" s="31"/>
+      <c r="N80" s="32"/>
+      <c r="O80" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="P80" s="31"/>
+      <c r="Q80" s="31"/>
+      <c r="R80" s="32"/>
+      <c r="S80" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="T80" s="31"/>
+      <c r="U80" s="31"/>
+      <c r="V80" s="32"/>
+      <c r="W80" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="X80" s="31"/>
+      <c r="Y80" s="31"/>
+      <c r="Z80" s="31"/>
+      <c r="AA80" s="31"/>
+      <c r="AB80" s="31"/>
+      <c r="AC80" s="31"/>
+      <c r="AD80" s="31"/>
+      <c r="AE80" s="31"/>
+      <c r="AF80" s="31"/>
+      <c r="AG80" s="31"/>
+      <c r="AH80" s="31"/>
+      <c r="AI80" s="31"/>
+      <c r="AJ80" s="31"/>
+      <c r="AK80" s="31"/>
+      <c r="AL80" s="31"/>
+      <c r="AM80" s="31"/>
+      <c r="AN80" s="31"/>
+      <c r="AO80" s="31"/>
+      <c r="AP80" s="32"/>
+    </row>
+    <row r="81" spans="3:42">
+      <c r="C81" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="D81" s="31"/>
+      <c r="E81" s="31"/>
+      <c r="F81" s="31"/>
+      <c r="G81" s="31"/>
+      <c r="H81" s="31"/>
+      <c r="I81" s="31"/>
+      <c r="J81" s="31"/>
+      <c r="K81" s="32"/>
+      <c r="L81" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="M81" s="31"/>
+      <c r="N81" s="32"/>
+      <c r="O81" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="P81" s="31"/>
+      <c r="Q81" s="31"/>
+      <c r="R81" s="32"/>
+      <c r="S81" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="T81" s="31"/>
+      <c r="U81" s="31"/>
+      <c r="V81" s="32"/>
+      <c r="W81" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="X81" s="31"/>
+      <c r="Y81" s="31"/>
+      <c r="Z81" s="31"/>
+      <c r="AA81" s="31"/>
+      <c r="AB81" s="31"/>
+      <c r="AC81" s="31"/>
+      <c r="AD81" s="31"/>
+      <c r="AE81" s="31"/>
+      <c r="AF81" s="31"/>
+      <c r="AG81" s="31"/>
+      <c r="AH81" s="31"/>
+      <c r="AI81" s="31"/>
+      <c r="AJ81" s="31"/>
+      <c r="AK81" s="31"/>
+      <c r="AL81" s="31"/>
+      <c r="AM81" s="31"/>
+      <c r="AN81" s="31"/>
+      <c r="AO81" s="31"/>
+      <c r="AP81" s="32"/>
+    </row>
+    <row r="82" spans="3:42">
+      <c r="C82" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="D82" s="31"/>
+      <c r="E82" s="31"/>
+      <c r="F82" s="31"/>
+      <c r="G82" s="31"/>
+      <c r="H82" s="31"/>
+      <c r="I82" s="31"/>
+      <c r="J82" s="31"/>
+      <c r="K82" s="32"/>
+      <c r="L82" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="M82" s="31"/>
+      <c r="N82" s="32"/>
+      <c r="O82" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="P82" s="31"/>
+      <c r="Q82" s="31"/>
+      <c r="R82" s="32"/>
+      <c r="S82" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="T82" s="31"/>
+      <c r="U82" s="31"/>
+      <c r="V82" s="32"/>
+      <c r="W82" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="X82" s="31"/>
+      <c r="Y82" s="31"/>
+      <c r="Z82" s="31"/>
+      <c r="AA82" s="31"/>
+      <c r="AB82" s="31"/>
+      <c r="AC82" s="31"/>
+      <c r="AD82" s="31"/>
+      <c r="AE82" s="31"/>
+      <c r="AF82" s="31"/>
+      <c r="AG82" s="31"/>
+      <c r="AH82" s="31"/>
+      <c r="AI82" s="31"/>
+      <c r="AJ82" s="31"/>
+      <c r="AK82" s="31"/>
+      <c r="AL82" s="31"/>
+      <c r="AM82" s="31"/>
+      <c r="AN82" s="31"/>
+      <c r="AO82" s="31"/>
+      <c r="AP82" s="32"/>
+    </row>
+    <row r="83" spans="3:42">
+      <c r="C83" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="D83" s="31"/>
+      <c r="E83" s="31"/>
+      <c r="F83" s="31"/>
+      <c r="G83" s="31"/>
+      <c r="H83" s="31"/>
+      <c r="I83" s="31"/>
+      <c r="J83" s="31"/>
+      <c r="K83" s="32"/>
+      <c r="L83" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="M83" s="31"/>
+      <c r="N83" s="32"/>
+      <c r="O83" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="P83" s="31"/>
+      <c r="Q83" s="31"/>
+      <c r="R83" s="32"/>
+      <c r="S83" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="T83" s="31"/>
+      <c r="U83" s="31"/>
+      <c r="V83" s="32"/>
+      <c r="W83" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="X83" s="31"/>
+      <c r="Y83" s="31"/>
+      <c r="Z83" s="31"/>
+      <c r="AA83" s="31"/>
+      <c r="AB83" s="31"/>
+      <c r="AC83" s="31"/>
+      <c r="AD83" s="31"/>
+      <c r="AE83" s="31"/>
+      <c r="AF83" s="31"/>
+      <c r="AG83" s="31"/>
+      <c r="AH83" s="31"/>
+      <c r="AI83" s="31"/>
+      <c r="AJ83" s="31"/>
+      <c r="AK83" s="31"/>
+      <c r="AL83" s="31"/>
+      <c r="AM83" s="31"/>
+      <c r="AN83" s="31"/>
+      <c r="AO83" s="31"/>
+      <c r="AP83" s="32"/>
+    </row>
+    <row r="84" spans="3:42">
+      <c r="C84" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="D84" s="31"/>
+      <c r="E84" s="31"/>
+      <c r="F84" s="31"/>
+      <c r="G84" s="31"/>
+      <c r="H84" s="31"/>
+      <c r="I84" s="31"/>
+      <c r="J84" s="31"/>
+      <c r="K84" s="32"/>
+      <c r="L84" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="M84" s="31"/>
+      <c r="N84" s="32"/>
+      <c r="O84" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="59"/>
-      <c r="D64" s="59"/>
-      <c r="E64" s="59"/>
-      <c r="F64" s="59"/>
-      <c r="G64" s="59"/>
-      <c r="H64" s="59"/>
-      <c r="I64" s="59"/>
-      <c r="J64" s="59"/>
-      <c r="K64" s="59"/>
-      <c r="L64" s="59"/>
-      <c r="M64" s="59"/>
-      <c r="N64" s="59"/>
-      <c r="O64" s="59"/>
-      <c r="P64" s="59"/>
-      <c r="Q64" s="59"/>
-      <c r="R64" s="59"/>
-      <c r="S64" s="59"/>
-      <c r="T64" s="59"/>
-      <c r="U64" s="59"/>
-      <c r="V64" s="59"/>
-      <c r="W64" s="59"/>
-      <c r="X64" s="59"/>
-      <c r="Y64" s="59"/>
-      <c r="Z64" s="59"/>
-      <c r="AA64" s="59"/>
-      <c r="AB64" s="59"/>
-      <c r="AC64" s="59"/>
-      <c r="AD64" s="59"/>
-      <c r="AE64" s="59"/>
-      <c r="AF64" s="59"/>
-      <c r="AG64" s="59"/>
-      <c r="AH64" s="59"/>
-      <c r="AI64" s="59"/>
-      <c r="AJ64" s="59"/>
-      <c r="AK64" s="59"/>
-      <c r="AL64" s="59"/>
-      <c r="AM64" s="59"/>
-      <c r="AN64" s="59"/>
-      <c r="AO64" s="59"/>
-    </row>
-    <row r="65" spans="2:41">
-      <c r="B65" s="59"/>
-      <c r="C65" s="59"/>
-      <c r="D65" s="59"/>
-      <c r="E65" s="59"/>
-      <c r="F65" s="59"/>
-      <c r="G65" s="59"/>
-      <c r="H65" s="59"/>
-      <c r="I65" s="59"/>
-      <c r="J65" s="59"/>
-      <c r="K65" s="59"/>
-      <c r="L65" s="59"/>
-      <c r="M65" s="59"/>
-      <c r="N65" s="59"/>
-      <c r="O65" s="59"/>
-      <c r="P65" s="59"/>
-      <c r="Q65" s="59"/>
-      <c r="R65" s="59"/>
-      <c r="S65" s="59"/>
-      <c r="T65" s="59"/>
-      <c r="U65" s="59"/>
-      <c r="V65" s="59"/>
-      <c r="W65" s="59"/>
-      <c r="X65" s="59"/>
-      <c r="Y65" s="59"/>
-      <c r="Z65" s="59"/>
-      <c r="AA65" s="59"/>
-      <c r="AB65" s="59"/>
-      <c r="AC65" s="59"/>
-      <c r="AD65" s="59"/>
-      <c r="AE65" s="59"/>
-      <c r="AF65" s="59"/>
-      <c r="AG65" s="59"/>
-      <c r="AH65" s="59"/>
-      <c r="AI65" s="59"/>
-      <c r="AJ65" s="59"/>
-      <c r="AK65" s="59"/>
-      <c r="AL65" s="59"/>
-      <c r="AM65" s="59"/>
-      <c r="AN65" s="59"/>
-      <c r="AO65" s="59"/>
-    </row>
-    <row r="67" spans="2:41">
-      <c r="B67" s="75" t="s">
-        <v>38</v>
-      </c>
-      <c r="C67" s="59"/>
-      <c r="D67" s="59"/>
-      <c r="E67" s="59"/>
-      <c r="F67" s="59"/>
-      <c r="G67" s="59"/>
-      <c r="H67" s="59"/>
-      <c r="I67" s="59"/>
-      <c r="J67" s="59"/>
-      <c r="K67" s="59"/>
-      <c r="L67" s="59"/>
-      <c r="M67" s="59"/>
-      <c r="N67" s="59"/>
-      <c r="O67" s="59"/>
-      <c r="P67" s="59"/>
-      <c r="Q67" s="59"/>
-      <c r="R67" s="59"/>
-      <c r="S67" s="59"/>
-      <c r="T67" s="59"/>
-      <c r="U67" s="59"/>
-      <c r="V67" s="59"/>
-      <c r="W67" s="59"/>
-      <c r="X67" s="59"/>
-      <c r="Y67" s="59"/>
-      <c r="Z67" s="59"/>
-      <c r="AA67" s="59"/>
-      <c r="AB67" s="59"/>
-      <c r="AC67" s="59"/>
-      <c r="AD67" s="59"/>
-      <c r="AE67" s="59"/>
-      <c r="AF67" s="59"/>
-      <c r="AG67" s="59"/>
-      <c r="AH67" s="59"/>
-      <c r="AI67" s="59"/>
-      <c r="AJ67" s="59"/>
-      <c r="AK67" s="59"/>
-      <c r="AL67" s="59"/>
-      <c r="AM67" s="59"/>
-      <c r="AN67" s="59"/>
-      <c r="AO67" s="59"/>
-    </row>
-    <row r="68" spans="2:41">
-      <c r="B68" s="58" t="s">
-        <v>39</v>
-      </c>
-      <c r="C68" s="59"/>
-      <c r="D68" s="59"/>
-      <c r="E68" s="59"/>
-      <c r="F68" s="59"/>
-      <c r="G68" s="59"/>
-      <c r="H68" s="59"/>
-      <c r="I68" s="59"/>
-      <c r="J68" s="59"/>
-      <c r="K68" s="59"/>
-      <c r="L68" s="59"/>
-      <c r="M68" s="59"/>
-      <c r="N68" s="59"/>
-      <c r="O68" s="59"/>
-      <c r="P68" s="59"/>
-      <c r="Q68" s="59"/>
-      <c r="R68" s="59"/>
-      <c r="S68" s="59"/>
-      <c r="T68" s="59"/>
-      <c r="U68" s="59"/>
-      <c r="V68" s="59"/>
-      <c r="W68" s="59"/>
-      <c r="X68" s="59"/>
-      <c r="Y68" s="59"/>
-      <c r="Z68" s="59"/>
-      <c r="AA68" s="59"/>
-      <c r="AB68" s="59"/>
-      <c r="AC68" s="59"/>
-      <c r="AD68" s="59"/>
-      <c r="AE68" s="59"/>
-      <c r="AF68" s="59"/>
-      <c r="AG68" s="59"/>
-      <c r="AH68" s="59"/>
-      <c r="AI68" s="59"/>
-      <c r="AJ68" s="59"/>
-      <c r="AK68" s="59"/>
-      <c r="AL68" s="59"/>
-      <c r="AM68" s="59"/>
-      <c r="AN68" s="59"/>
-      <c r="AO68" s="59"/>
-    </row>
-    <row r="69" spans="2:41">
-      <c r="B69" s="74" t="s">
-        <v>40</v>
-      </c>
-      <c r="C69" s="28"/>
-      <c r="D69" s="28"/>
-      <c r="E69" s="28"/>
-      <c r="F69" s="28"/>
-      <c r="G69" s="28"/>
-      <c r="H69" s="28"/>
-      <c r="I69" s="28"/>
-      <c r="J69" s="28"/>
-      <c r="K69" s="29"/>
-      <c r="L69" s="74" t="s">
-        <v>41</v>
-      </c>
-      <c r="M69" s="28"/>
-      <c r="N69" s="29"/>
-      <c r="O69" s="74" t="s">
-        <v>42</v>
-      </c>
-      <c r="P69" s="28"/>
-      <c r="Q69" s="28"/>
-      <c r="R69" s="29"/>
-      <c r="S69" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="T69" s="28"/>
-      <c r="U69" s="28"/>
-      <c r="V69" s="28"/>
-      <c r="W69" s="28"/>
-      <c r="X69" s="28"/>
-      <c r="Y69" s="28"/>
-      <c r="Z69" s="28"/>
-      <c r="AA69" s="28"/>
-      <c r="AB69" s="28"/>
-      <c r="AC69" s="28"/>
-      <c r="AD69" s="28"/>
-      <c r="AE69" s="28"/>
-      <c r="AF69" s="28"/>
-      <c r="AG69" s="28"/>
-      <c r="AH69" s="28"/>
-      <c r="AI69" s="28"/>
-      <c r="AJ69" s="28"/>
-      <c r="AK69" s="28"/>
-      <c r="AL69" s="28"/>
-      <c r="AM69" s="28"/>
-      <c r="AN69" s="28"/>
-      <c r="AO69" s="29"/>
-    </row>
-    <row r="70" spans="2:41">
-      <c r="B70" s="45" t="s">
-        <v>44</v>
-      </c>
-      <c r="C70" s="32"/>
-      <c r="D70" s="32"/>
-      <c r="E70" s="32"/>
-      <c r="F70" s="32"/>
-      <c r="G70" s="32"/>
-      <c r="H70" s="32"/>
-      <c r="I70" s="32"/>
-      <c r="J70" s="32"/>
-      <c r="K70" s="33"/>
-      <c r="L70" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="M70" s="32"/>
-      <c r="N70" s="33"/>
-      <c r="O70" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="P70" s="32"/>
-      <c r="Q70" s="32"/>
-      <c r="R70" s="33"/>
-      <c r="S70" s="45" t="s">
-        <v>47</v>
-      </c>
-      <c r="T70" s="32"/>
-      <c r="U70" s="32"/>
-      <c r="V70" s="32"/>
-      <c r="W70" s="32"/>
-      <c r="X70" s="32"/>
-      <c r="Y70" s="32"/>
-      <c r="Z70" s="32"/>
-      <c r="AA70" s="32"/>
-      <c r="AB70" s="32"/>
-      <c r="AC70" s="32"/>
-      <c r="AD70" s="32"/>
-      <c r="AE70" s="32"/>
-      <c r="AF70" s="32"/>
-      <c r="AG70" s="32"/>
-      <c r="AH70" s="32"/>
-      <c r="AI70" s="32"/>
-      <c r="AJ70" s="32"/>
-      <c r="AK70" s="32"/>
-      <c r="AL70" s="32"/>
-      <c r="AM70" s="32"/>
-      <c r="AN70" s="32"/>
-      <c r="AO70" s="33"/>
-    </row>
-    <row r="71" spans="2:41">
-      <c r="B71" s="45" t="s">
-        <v>48</v>
-      </c>
-      <c r="C71" s="32"/>
-      <c r="D71" s="32"/>
-      <c r="E71" s="32"/>
-      <c r="F71" s="32"/>
-      <c r="G71" s="32"/>
-      <c r="H71" s="32"/>
-      <c r="I71" s="32"/>
-      <c r="J71" s="32"/>
-      <c r="K71" s="33"/>
-      <c r="L71" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="M71" s="32"/>
-      <c r="N71" s="33"/>
-      <c r="O71" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="P71" s="32"/>
-      <c r="Q71" s="32"/>
-      <c r="R71" s="33"/>
-      <c r="S71" s="45" t="s">
-        <v>50</v>
-      </c>
-      <c r="T71" s="32"/>
-      <c r="U71" s="32"/>
-      <c r="V71" s="32"/>
-      <c r="W71" s="32"/>
-      <c r="X71" s="32"/>
-      <c r="Y71" s="32"/>
-      <c r="Z71" s="32"/>
-      <c r="AA71" s="32"/>
-      <c r="AB71" s="32"/>
-      <c r="AC71" s="32"/>
-      <c r="AD71" s="32"/>
-      <c r="AE71" s="32"/>
-      <c r="AF71" s="32"/>
-      <c r="AG71" s="32"/>
-      <c r="AH71" s="32"/>
-      <c r="AI71" s="32"/>
-      <c r="AJ71" s="32"/>
-      <c r="AK71" s="32"/>
-      <c r="AL71" s="32"/>
-      <c r="AM71" s="32"/>
-      <c r="AN71" s="32"/>
-      <c r="AO71" s="33"/>
-    </row>
-    <row r="72" spans="2:41">
-      <c r="B72" s="45" t="s">
-        <v>51</v>
-      </c>
-      <c r="C72" s="32"/>
-      <c r="D72" s="32"/>
-      <c r="E72" s="32"/>
-      <c r="F72" s="32"/>
-      <c r="G72" s="32"/>
-      <c r="H72" s="32"/>
-      <c r="I72" s="32"/>
-      <c r="J72" s="32"/>
-      <c r="K72" s="33"/>
-      <c r="L72" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="M72" s="32"/>
-      <c r="N72" s="33"/>
-      <c r="O72" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="P72" s="32"/>
-      <c r="Q72" s="32"/>
-      <c r="R72" s="33"/>
-      <c r="S72" s="45" t="s">
-        <v>53</v>
-      </c>
-      <c r="T72" s="32"/>
-      <c r="U72" s="32"/>
-      <c r="V72" s="32"/>
-      <c r="W72" s="32"/>
-      <c r="X72" s="32"/>
-      <c r="Y72" s="32"/>
-      <c r="Z72" s="32"/>
-      <c r="AA72" s="32"/>
-      <c r="AB72" s="32"/>
-      <c r="AC72" s="32"/>
-      <c r="AD72" s="32"/>
-      <c r="AE72" s="32"/>
-      <c r="AF72" s="32"/>
-      <c r="AG72" s="32"/>
-      <c r="AH72" s="32"/>
-      <c r="AI72" s="32"/>
-      <c r="AJ72" s="32"/>
-      <c r="AK72" s="32"/>
-      <c r="AL72" s="32"/>
-      <c r="AM72" s="32"/>
-      <c r="AN72" s="32"/>
-      <c r="AO72" s="33"/>
-    </row>
-    <row r="73" spans="2:41">
-      <c r="B73" s="45" t="s">
-        <v>54</v>
-      </c>
-      <c r="C73" s="32"/>
-      <c r="D73" s="32"/>
-      <c r="E73" s="32"/>
-      <c r="F73" s="32"/>
-      <c r="G73" s="32"/>
-      <c r="H73" s="32"/>
-      <c r="I73" s="32"/>
-      <c r="J73" s="32"/>
-      <c r="K73" s="33"/>
-      <c r="L73" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="M73" s="32"/>
-      <c r="N73" s="33"/>
-      <c r="O73" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="P73" s="32"/>
-      <c r="Q73" s="32"/>
-      <c r="R73" s="33"/>
-      <c r="S73" s="45" t="s">
-        <v>55</v>
-      </c>
-      <c r="T73" s="32"/>
-      <c r="U73" s="32"/>
-      <c r="V73" s="32"/>
-      <c r="W73" s="32"/>
-      <c r="X73" s="32"/>
-      <c r="Y73" s="32"/>
-      <c r="Z73" s="32"/>
-      <c r="AA73" s="32"/>
-      <c r="AB73" s="32"/>
-      <c r="AC73" s="32"/>
-      <c r="AD73" s="32"/>
-      <c r="AE73" s="32"/>
-      <c r="AF73" s="32"/>
-      <c r="AG73" s="32"/>
-      <c r="AH73" s="32"/>
-      <c r="AI73" s="32"/>
-      <c r="AJ73" s="32"/>
-      <c r="AK73" s="32"/>
-      <c r="AL73" s="32"/>
-      <c r="AM73" s="32"/>
-      <c r="AN73" s="32"/>
-      <c r="AO73" s="33"/>
-    </row>
-    <row r="74" spans="2:41">
-      <c r="B74" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C74" s="28"/>
-      <c r="D74" s="28"/>
-      <c r="E74" s="28"/>
-      <c r="F74" s="28"/>
-      <c r="G74" s="28"/>
-      <c r="H74" s="28"/>
-      <c r="I74" s="28"/>
-      <c r="J74" s="28"/>
-      <c r="K74" s="29"/>
-      <c r="L74" s="30" t="s">
+      <c r="P84" s="31"/>
+      <c r="Q84" s="31"/>
+      <c r="R84" s="32"/>
+      <c r="S84" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="T84" s="31"/>
+      <c r="U84" s="31"/>
+      <c r="V84" s="32"/>
+      <c r="W84" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="X84" s="31"/>
+      <c r="Y84" s="31"/>
+      <c r="Z84" s="31"/>
+      <c r="AA84" s="31"/>
+      <c r="AB84" s="31"/>
+      <c r="AC84" s="31"/>
+      <c r="AD84" s="31"/>
+      <c r="AE84" s="31"/>
+      <c r="AF84" s="31"/>
+      <c r="AG84" s="31"/>
+      <c r="AH84" s="31"/>
+      <c r="AI84" s="31"/>
+      <c r="AJ84" s="31"/>
+      <c r="AK84" s="31"/>
+      <c r="AL84" s="31"/>
+      <c r="AM84" s="31"/>
+      <c r="AN84" s="31"/>
+      <c r="AO84" s="31"/>
+      <c r="AP84" s="32"/>
+    </row>
+    <row r="85" spans="3:42">
+      <c r="C85" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="D85" s="31"/>
+      <c r="E85" s="31"/>
+      <c r="F85" s="31"/>
+      <c r="G85" s="31"/>
+      <c r="H85" s="31"/>
+      <c r="I85" s="31"/>
+      <c r="J85" s="31"/>
+      <c r="K85" s="32"/>
+      <c r="L85" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="M85" s="31"/>
+      <c r="N85" s="32"/>
+      <c r="O85" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="P85" s="31"/>
+      <c r="Q85" s="31"/>
+      <c r="R85" s="32"/>
+      <c r="S85" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="M74" s="28"/>
-      <c r="N74" s="29"/>
-      <c r="O74" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="P74" s="28"/>
-      <c r="Q74" s="28"/>
-      <c r="R74" s="29"/>
-      <c r="S74" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="T74" s="28"/>
-      <c r="U74" s="28"/>
-      <c r="V74" s="28"/>
-      <c r="W74" s="28"/>
-      <c r="X74" s="28"/>
-      <c r="Y74" s="28"/>
-      <c r="Z74" s="28"/>
-      <c r="AA74" s="28"/>
-      <c r="AB74" s="28"/>
-      <c r="AC74" s="28"/>
-      <c r="AD74" s="28"/>
-      <c r="AE74" s="28"/>
-      <c r="AF74" s="28"/>
-      <c r="AG74" s="28"/>
-      <c r="AH74" s="28"/>
-      <c r="AI74" s="28"/>
-      <c r="AJ74" s="28"/>
-      <c r="AK74" s="28"/>
-      <c r="AL74" s="28"/>
-      <c r="AM74" s="28"/>
-      <c r="AN74" s="28"/>
-      <c r="AO74" s="29"/>
-    </row>
-    <row r="75" spans="2:41">
-      <c r="B75" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="C75" s="28"/>
-      <c r="D75" s="28"/>
-      <c r="E75" s="28"/>
-      <c r="F75" s="28"/>
-      <c r="G75" s="28"/>
-      <c r="H75" s="28"/>
-      <c r="I75" s="28"/>
-      <c r="J75" s="28"/>
-      <c r="K75" s="29"/>
-      <c r="L75" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="M75" s="28"/>
-      <c r="N75" s="29"/>
-      <c r="O75" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="P75" s="28"/>
-      <c r="Q75" s="28"/>
-      <c r="R75" s="29"/>
-      <c r="S75" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="T75" s="28"/>
-      <c r="U75" s="28"/>
-      <c r="V75" s="28"/>
-      <c r="W75" s="28"/>
-      <c r="X75" s="28"/>
-      <c r="Y75" s="28"/>
-      <c r="Z75" s="28"/>
-      <c r="AA75" s="28"/>
-      <c r="AB75" s="28"/>
-      <c r="AC75" s="28"/>
-      <c r="AD75" s="28"/>
-      <c r="AE75" s="28"/>
-      <c r="AF75" s="28"/>
-      <c r="AG75" s="28"/>
-      <c r="AH75" s="28"/>
-      <c r="AI75" s="28"/>
-      <c r="AJ75" s="28"/>
-      <c r="AK75" s="28"/>
-      <c r="AL75" s="28"/>
-      <c r="AM75" s="28"/>
-      <c r="AN75" s="28"/>
-      <c r="AO75" s="29"/>
-    </row>
-    <row r="76" spans="2:41">
-      <c r="B76" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C76" s="28"/>
-      <c r="D76" s="28"/>
-      <c r="E76" s="28"/>
-      <c r="F76" s="28"/>
-      <c r="G76" s="28"/>
-      <c r="H76" s="28"/>
-      <c r="I76" s="28"/>
-      <c r="J76" s="28"/>
-      <c r="K76" s="29"/>
-      <c r="L76" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="M76" s="28"/>
-      <c r="N76" s="29"/>
-      <c r="O76" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="P76" s="28"/>
-      <c r="Q76" s="28"/>
-      <c r="R76" s="29"/>
-      <c r="S76" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="T76" s="28"/>
-      <c r="U76" s="28"/>
-      <c r="V76" s="28"/>
-      <c r="W76" s="28"/>
-      <c r="X76" s="28"/>
-      <c r="Y76" s="28"/>
-      <c r="Z76" s="28"/>
-      <c r="AA76" s="28"/>
-      <c r="AB76" s="28"/>
-      <c r="AC76" s="28"/>
-      <c r="AD76" s="28"/>
-      <c r="AE76" s="28"/>
-      <c r="AF76" s="28"/>
-      <c r="AG76" s="28"/>
-      <c r="AH76" s="28"/>
-      <c r="AI76" s="28"/>
-      <c r="AJ76" s="28"/>
-      <c r="AK76" s="28"/>
-      <c r="AL76" s="28"/>
-      <c r="AM76" s="28"/>
-      <c r="AN76" s="28"/>
-      <c r="AO76" s="29"/>
-    </row>
-    <row r="77" spans="2:41">
-      <c r="B77" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="C77" s="28"/>
-      <c r="D77" s="28"/>
-      <c r="E77" s="28"/>
-      <c r="F77" s="28"/>
-      <c r="G77" s="28"/>
-      <c r="H77" s="28"/>
-      <c r="I77" s="28"/>
-      <c r="J77" s="28"/>
-      <c r="K77" s="29"/>
-      <c r="L77" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="M77" s="28"/>
-      <c r="N77" s="29"/>
-      <c r="O77" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="P77" s="28"/>
-      <c r="Q77" s="28"/>
-      <c r="R77" s="29"/>
-      <c r="S77" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="T77" s="28"/>
-      <c r="U77" s="28"/>
-      <c r="V77" s="28"/>
-      <c r="W77" s="28"/>
-      <c r="X77" s="28"/>
-      <c r="Y77" s="28"/>
-      <c r="Z77" s="28"/>
-      <c r="AA77" s="28"/>
-      <c r="AB77" s="28"/>
-      <c r="AC77" s="28"/>
-      <c r="AD77" s="28"/>
-      <c r="AE77" s="28"/>
-      <c r="AF77" s="28"/>
-      <c r="AG77" s="28"/>
-      <c r="AH77" s="28"/>
-      <c r="AI77" s="28"/>
-      <c r="AJ77" s="28"/>
-      <c r="AK77" s="28"/>
-      <c r="AL77" s="28"/>
-      <c r="AM77" s="28"/>
-      <c r="AN77" s="28"/>
-      <c r="AO77" s="29"/>
-    </row>
-    <row r="78" spans="2:41">
-      <c r="B78" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="C78" s="28"/>
-      <c r="D78" s="28"/>
-      <c r="E78" s="28"/>
-      <c r="F78" s="28"/>
-      <c r="G78" s="28"/>
-      <c r="H78" s="28"/>
-      <c r="I78" s="28"/>
-      <c r="J78" s="28"/>
-      <c r="K78" s="29"/>
-      <c r="L78" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="M78" s="28"/>
-      <c r="N78" s="29"/>
-      <c r="O78" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="P78" s="28"/>
-      <c r="Q78" s="28"/>
-      <c r="R78" s="29"/>
-      <c r="S78" s="27" t="s">
-        <v>63</v>
-      </c>
-      <c r="T78" s="28"/>
-      <c r="U78" s="28"/>
-      <c r="V78" s="28"/>
-      <c r="W78" s="28"/>
-      <c r="X78" s="28"/>
-      <c r="Y78" s="28"/>
-      <c r="Z78" s="28"/>
-      <c r="AA78" s="28"/>
-      <c r="AB78" s="28"/>
-      <c r="AC78" s="28"/>
-      <c r="AD78" s="28"/>
-      <c r="AE78" s="28"/>
-      <c r="AF78" s="28"/>
-      <c r="AG78" s="28"/>
-      <c r="AH78" s="28"/>
-      <c r="AI78" s="28"/>
-      <c r="AJ78" s="28"/>
-      <c r="AK78" s="28"/>
-      <c r="AL78" s="28"/>
-      <c r="AM78" s="28"/>
-      <c r="AN78" s="28"/>
-      <c r="AO78" s="29"/>
-    </row>
-    <row r="79" spans="2:41">
-      <c r="B79" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C79" s="28"/>
-      <c r="D79" s="28"/>
-      <c r="E79" s="28"/>
-      <c r="F79" s="28"/>
-      <c r="G79" s="28"/>
-      <c r="H79" s="28"/>
-      <c r="I79" s="28"/>
-      <c r="J79" s="28"/>
-      <c r="K79" s="29"/>
-      <c r="L79" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="M79" s="28"/>
-      <c r="N79" s="29"/>
-      <c r="O79" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="P79" s="28"/>
-      <c r="Q79" s="28"/>
-      <c r="R79" s="29"/>
-      <c r="S79" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="T79" s="28"/>
-      <c r="U79" s="28"/>
-      <c r="V79" s="28"/>
-      <c r="W79" s="28"/>
-      <c r="X79" s="28"/>
-      <c r="Y79" s="28"/>
-      <c r="Z79" s="28"/>
-      <c r="AA79" s="28"/>
-      <c r="AB79" s="28"/>
-      <c r="AC79" s="28"/>
-      <c r="AD79" s="28"/>
-      <c r="AE79" s="28"/>
-      <c r="AF79" s="28"/>
-      <c r="AG79" s="28"/>
-      <c r="AH79" s="28"/>
-      <c r="AI79" s="28"/>
-      <c r="AJ79" s="28"/>
-      <c r="AK79" s="28"/>
-      <c r="AL79" s="28"/>
-      <c r="AM79" s="28"/>
-      <c r="AN79" s="28"/>
-      <c r="AO79" s="29"/>
-    </row>
-    <row r="80" spans="2:41">
-      <c r="B80" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C80" s="28"/>
-      <c r="D80" s="28"/>
-      <c r="E80" s="28"/>
-      <c r="F80" s="28"/>
-      <c r="G80" s="28"/>
-      <c r="H80" s="28"/>
-      <c r="I80" s="28"/>
-      <c r="J80" s="28"/>
-      <c r="K80" s="29"/>
-      <c r="L80" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="M80" s="28"/>
-      <c r="N80" s="29"/>
-      <c r="O80" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="P80" s="28"/>
-      <c r="Q80" s="28"/>
-      <c r="R80" s="29"/>
-      <c r="S80" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="T80" s="28"/>
-      <c r="U80" s="28"/>
-      <c r="V80" s="28"/>
-      <c r="W80" s="28"/>
-      <c r="X80" s="28"/>
-      <c r="Y80" s="28"/>
-      <c r="Z80" s="28"/>
-      <c r="AA80" s="28"/>
-      <c r="AB80" s="28"/>
-      <c r="AC80" s="28"/>
-      <c r="AD80" s="28"/>
-      <c r="AE80" s="28"/>
-      <c r="AF80" s="28"/>
-      <c r="AG80" s="28"/>
-      <c r="AH80" s="28"/>
-      <c r="AI80" s="28"/>
-      <c r="AJ80" s="28"/>
-      <c r="AK80" s="28"/>
-      <c r="AL80" s="28"/>
-      <c r="AM80" s="28"/>
-      <c r="AN80" s="28"/>
-      <c r="AO80" s="29"/>
-    </row>
-    <row r="81" spans="2:41">
-      <c r="B81" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C81" s="28"/>
-      <c r="D81" s="28"/>
-      <c r="E81" s="28"/>
-      <c r="F81" s="28"/>
-      <c r="G81" s="28"/>
-      <c r="H81" s="28"/>
-      <c r="I81" s="28"/>
-      <c r="J81" s="28"/>
-      <c r="K81" s="29"/>
-      <c r="L81" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="M81" s="28"/>
-      <c r="N81" s="29"/>
-      <c r="O81" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="P81" s="28"/>
-      <c r="Q81" s="28"/>
-      <c r="R81" s="29"/>
-      <c r="S81" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="T81" s="28"/>
-      <c r="U81" s="28"/>
-      <c r="V81" s="28"/>
-      <c r="W81" s="28"/>
-      <c r="X81" s="28"/>
-      <c r="Y81" s="28"/>
-      <c r="Z81" s="28"/>
-      <c r="AA81" s="28"/>
-      <c r="AB81" s="28"/>
-      <c r="AC81" s="28"/>
-      <c r="AD81" s="28"/>
-      <c r="AE81" s="28"/>
-      <c r="AF81" s="28"/>
-      <c r="AG81" s="28"/>
-      <c r="AH81" s="28"/>
-      <c r="AI81" s="28"/>
-      <c r="AJ81" s="28"/>
-      <c r="AK81" s="28"/>
-      <c r="AL81" s="28"/>
-      <c r="AM81" s="28"/>
-      <c r="AN81" s="28"/>
-      <c r="AO81" s="29"/>
-    </row>
-    <row r="82" spans="2:41">
-      <c r="B82" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C82" s="28"/>
-      <c r="D82" s="28"/>
-      <c r="E82" s="28"/>
-      <c r="F82" s="28"/>
-      <c r="G82" s="28"/>
-      <c r="H82" s="28"/>
-      <c r="I82" s="28"/>
-      <c r="J82" s="28"/>
-      <c r="K82" s="29"/>
-      <c r="L82" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="M82" s="28"/>
-      <c r="N82" s="29"/>
-      <c r="O82" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="P82" s="28"/>
-      <c r="Q82" s="28"/>
-      <c r="R82" s="29"/>
-      <c r="S82" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="T82" s="28"/>
-      <c r="U82" s="28"/>
-      <c r="V82" s="28"/>
-      <c r="W82" s="28"/>
-      <c r="X82" s="28"/>
-      <c r="Y82" s="28"/>
-      <c r="Z82" s="28"/>
-      <c r="AA82" s="28"/>
-      <c r="AB82" s="28"/>
-      <c r="AC82" s="28"/>
-      <c r="AD82" s="28"/>
-      <c r="AE82" s="28"/>
-      <c r="AF82" s="28"/>
-      <c r="AG82" s="28"/>
-      <c r="AH82" s="28"/>
-      <c r="AI82" s="28"/>
-      <c r="AJ82" s="28"/>
-      <c r="AK82" s="28"/>
-      <c r="AL82" s="28"/>
-      <c r="AM82" s="28"/>
-      <c r="AN82" s="28"/>
-      <c r="AO82" s="29"/>
-    </row>
-    <row r="83" spans="2:41">
-      <c r="B83" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="C83" s="28"/>
-      <c r="D83" s="28"/>
-      <c r="E83" s="28"/>
-      <c r="F83" s="28"/>
-      <c r="G83" s="28"/>
-      <c r="H83" s="28"/>
-      <c r="I83" s="28"/>
-      <c r="J83" s="28"/>
-      <c r="K83" s="29"/>
-      <c r="L83" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="M83" s="28"/>
-      <c r="N83" s="29"/>
-      <c r="O83" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="P83" s="28"/>
-      <c r="Q83" s="28"/>
-      <c r="R83" s="29"/>
-      <c r="S83" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="T83" s="28"/>
-      <c r="U83" s="28"/>
-      <c r="V83" s="28"/>
-      <c r="W83" s="28"/>
-      <c r="X83" s="28"/>
-      <c r="Y83" s="28"/>
-      <c r="Z83" s="28"/>
-      <c r="AA83" s="28"/>
-      <c r="AB83" s="28"/>
-      <c r="AC83" s="28"/>
-      <c r="AD83" s="28"/>
-      <c r="AE83" s="28"/>
-      <c r="AF83" s="28"/>
-      <c r="AG83" s="28"/>
-      <c r="AH83" s="28"/>
-      <c r="AI83" s="28"/>
-      <c r="AJ83" s="28"/>
-      <c r="AK83" s="28"/>
-      <c r="AL83" s="28"/>
-      <c r="AM83" s="28"/>
-      <c r="AN83" s="28"/>
-      <c r="AO83" s="29"/>
-    </row>
-    <row r="84" spans="2:41">
-      <c r="B84" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="C84" s="28"/>
-      <c r="D84" s="28"/>
-      <c r="E84" s="28"/>
-      <c r="F84" s="28"/>
-      <c r="G84" s="28"/>
-      <c r="H84" s="28"/>
-      <c r="I84" s="28"/>
-      <c r="J84" s="28"/>
-      <c r="K84" s="29"/>
-      <c r="L84" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="M84" s="28"/>
-      <c r="N84" s="29"/>
-      <c r="O84" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="P84" s="28"/>
-      <c r="Q84" s="28"/>
-      <c r="R84" s="29"/>
-      <c r="S84" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="T84" s="28"/>
-      <c r="U84" s="28"/>
-      <c r="V84" s="28"/>
-      <c r="W84" s="28"/>
-      <c r="X84" s="28"/>
-      <c r="Y84" s="28"/>
-      <c r="Z84" s="28"/>
-      <c r="AA84" s="28"/>
-      <c r="AB84" s="28"/>
-      <c r="AC84" s="28"/>
-      <c r="AD84" s="28"/>
-      <c r="AE84" s="28"/>
-      <c r="AF84" s="28"/>
-      <c r="AG84" s="28"/>
-      <c r="AH84" s="28"/>
-      <c r="AI84" s="28"/>
-      <c r="AJ84" s="28"/>
-      <c r="AK84" s="28"/>
-      <c r="AL84" s="28"/>
-      <c r="AM84" s="28"/>
-      <c r="AN84" s="28"/>
-      <c r="AO84" s="29"/>
-    </row>
-    <row r="85" spans="2:41">
-      <c r="B85" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="C85" s="28"/>
-      <c r="D85" s="28"/>
-      <c r="E85" s="28"/>
-      <c r="F85" s="28"/>
-      <c r="G85" s="28"/>
-      <c r="H85" s="28"/>
-      <c r="I85" s="28"/>
-      <c r="J85" s="28"/>
-      <c r="K85" s="29"/>
-      <c r="L85" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="M85" s="28"/>
-      <c r="N85" s="29"/>
-      <c r="O85" s="30" t="s">
-        <v>76</v>
-      </c>
-      <c r="P85" s="28"/>
-      <c r="Q85" s="28"/>
-      <c r="R85" s="29"/>
-      <c r="S85" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="T85" s="28"/>
-      <c r="U85" s="28"/>
-      <c r="V85" s="28"/>
-      <c r="W85" s="28"/>
-      <c r="X85" s="28"/>
-      <c r="Y85" s="28"/>
-      <c r="Z85" s="28"/>
-      <c r="AA85" s="28"/>
-      <c r="AB85" s="28"/>
-      <c r="AC85" s="28"/>
-      <c r="AD85" s="28"/>
-      <c r="AE85" s="28"/>
-      <c r="AF85" s="28"/>
-      <c r="AG85" s="28"/>
-      <c r="AH85" s="28"/>
-      <c r="AI85" s="28"/>
-      <c r="AJ85" s="28"/>
-      <c r="AK85" s="28"/>
-      <c r="AL85" s="28"/>
-      <c r="AM85" s="28"/>
-      <c r="AN85" s="28"/>
-      <c r="AO85" s="29"/>
+      <c r="T85" s="31"/>
+      <c r="U85" s="31"/>
+      <c r="V85" s="32"/>
+      <c r="W85" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="X85" s="31"/>
+      <c r="Y85" s="31"/>
+      <c r="Z85" s="31"/>
+      <c r="AA85" s="31"/>
+      <c r="AB85" s="31"/>
+      <c r="AC85" s="31"/>
+      <c r="AD85" s="31"/>
+      <c r="AE85" s="31"/>
+      <c r="AF85" s="31"/>
+      <c r="AG85" s="31"/>
+      <c r="AH85" s="31"/>
+      <c r="AI85" s="31"/>
+      <c r="AJ85" s="31"/>
+      <c r="AK85" s="31"/>
+      <c r="AL85" s="31"/>
+      <c r="AM85" s="31"/>
+      <c r="AN85" s="31"/>
+      <c r="AO85" s="31"/>
+      <c r="AP85" s="32"/>
     </row>
   </sheetData>
-  <mergeCells count="135">
+  <mergeCells count="150">
+    <mergeCell ref="C85:K85"/>
+    <mergeCell ref="L85:N85"/>
+    <mergeCell ref="O85:R85"/>
+    <mergeCell ref="S85:V85"/>
+    <mergeCell ref="W85:AP85"/>
+    <mergeCell ref="C84:K84"/>
+    <mergeCell ref="L84:N84"/>
+    <mergeCell ref="O84:R84"/>
+    <mergeCell ref="S84:V84"/>
+    <mergeCell ref="W84:AP84"/>
+    <mergeCell ref="C83:K83"/>
+    <mergeCell ref="L83:N83"/>
+    <mergeCell ref="O83:R83"/>
+    <mergeCell ref="S83:V83"/>
+    <mergeCell ref="W83:AP83"/>
+    <mergeCell ref="C82:K82"/>
     <mergeCell ref="L82:N82"/>
-    <mergeCell ref="B85:K85"/>
+    <mergeCell ref="O82:R82"/>
+    <mergeCell ref="S82:V82"/>
+    <mergeCell ref="W82:AP82"/>
+    <mergeCell ref="C81:K81"/>
+    <mergeCell ref="L81:N81"/>
+    <mergeCell ref="O81:R81"/>
+    <mergeCell ref="S81:V81"/>
+    <mergeCell ref="W81:AP81"/>
+    <mergeCell ref="C80:K80"/>
+    <mergeCell ref="L80:N80"/>
+    <mergeCell ref="O80:R80"/>
+    <mergeCell ref="S80:V80"/>
+    <mergeCell ref="W80:AP80"/>
+    <mergeCell ref="C79:K79"/>
+    <mergeCell ref="L79:N79"/>
+    <mergeCell ref="O79:R79"/>
+    <mergeCell ref="S79:V79"/>
+    <mergeCell ref="W79:AP79"/>
+    <mergeCell ref="C78:K78"/>
+    <mergeCell ref="L78:N78"/>
+    <mergeCell ref="O78:R78"/>
+    <mergeCell ref="S78:V78"/>
+    <mergeCell ref="W78:AP78"/>
+    <mergeCell ref="C77:K77"/>
+    <mergeCell ref="L77:N77"/>
+    <mergeCell ref="O77:R77"/>
+    <mergeCell ref="S77:V77"/>
+    <mergeCell ref="W77:AP77"/>
+    <mergeCell ref="C76:K76"/>
+    <mergeCell ref="L76:N76"/>
+    <mergeCell ref="O76:R76"/>
+    <mergeCell ref="S76:V76"/>
+    <mergeCell ref="W76:AP76"/>
+    <mergeCell ref="C75:K75"/>
+    <mergeCell ref="L75:N75"/>
+    <mergeCell ref="O75:R75"/>
+    <mergeCell ref="S75:V75"/>
+    <mergeCell ref="W75:AP75"/>
+    <mergeCell ref="C74:K74"/>
     <mergeCell ref="L74:N74"/>
-    <mergeCell ref="B77:K77"/>
-    <mergeCell ref="B71:K71"/>
-    <mergeCell ref="O85:R85"/>
-    <mergeCell ref="L76:N76"/>
-    <mergeCell ref="B79:K79"/>
-    <mergeCell ref="O81:R81"/>
+    <mergeCell ref="O74:R74"/>
+    <mergeCell ref="S74:V74"/>
+    <mergeCell ref="W74:AP74"/>
+    <mergeCell ref="C73:K73"/>
+    <mergeCell ref="L73:N73"/>
+    <mergeCell ref="O73:R73"/>
+    <mergeCell ref="S73:V73"/>
+    <mergeCell ref="W73:AP73"/>
+    <mergeCell ref="C72:K72"/>
     <mergeCell ref="L72:N72"/>
-    <mergeCell ref="B75:K75"/>
-    <mergeCell ref="B73:K73"/>
-    <mergeCell ref="B78:K78"/>
+    <mergeCell ref="O72:R72"/>
+    <mergeCell ref="S72:V72"/>
+    <mergeCell ref="W72:AP72"/>
+    <mergeCell ref="C71:K71"/>
+    <mergeCell ref="L71:N71"/>
     <mergeCell ref="O71:R71"/>
-    <mergeCell ref="L80:N80"/>
-    <mergeCell ref="O82:R82"/>
-    <mergeCell ref="L77:N77"/>
+    <mergeCell ref="S71:V71"/>
+    <mergeCell ref="W71:AP71"/>
+    <mergeCell ref="C70:K70"/>
+    <mergeCell ref="L70:N70"/>
+    <mergeCell ref="O70:R70"/>
+    <mergeCell ref="S70:V70"/>
+    <mergeCell ref="W70:AP70"/>
+    <mergeCell ref="C69:K69"/>
+    <mergeCell ref="L69:N69"/>
     <mergeCell ref="O69:R69"/>
-    <mergeCell ref="B67:AO67"/>
-    <mergeCell ref="O80:R80"/>
-    <mergeCell ref="O77:R77"/>
-    <mergeCell ref="S77:AO77"/>
-    <mergeCell ref="B68:AO68"/>
-    <mergeCell ref="S80:AO80"/>
-    <mergeCell ref="S73:AO73"/>
-    <mergeCell ref="S70:AO70"/>
-    <mergeCell ref="S72:AO72"/>
-    <mergeCell ref="S78:AO78"/>
-    <mergeCell ref="O70:R70"/>
-    <mergeCell ref="O75:R75"/>
-    <mergeCell ref="L79:N79"/>
-    <mergeCell ref="L70:N70"/>
-    <mergeCell ref="L73:N73"/>
-    <mergeCell ref="S85:AO85"/>
-    <mergeCell ref="L84:N84"/>
-    <mergeCell ref="B69:K69"/>
-    <mergeCell ref="S69:AO69"/>
-    <mergeCell ref="B80:K80"/>
-    <mergeCell ref="S71:AO71"/>
-    <mergeCell ref="L85:N85"/>
-    <mergeCell ref="B70:K70"/>
-    <mergeCell ref="O78:R78"/>
-    <mergeCell ref="L69:N69"/>
-    <mergeCell ref="L78:N78"/>
-    <mergeCell ref="B72:K72"/>
-    <mergeCell ref="B81:K81"/>
-    <mergeCell ref="L71:N71"/>
-    <mergeCell ref="B76:K76"/>
-    <mergeCell ref="O84:R84"/>
-    <mergeCell ref="O79:R79"/>
-    <mergeCell ref="S84:AO84"/>
-    <mergeCell ref="B82:K82"/>
-    <mergeCell ref="S74:AO74"/>
-    <mergeCell ref="B84:K84"/>
-    <mergeCell ref="S76:AO76"/>
-    <mergeCell ref="L75:N75"/>
-    <mergeCell ref="L83:N83"/>
-    <mergeCell ref="B74:K74"/>
-    <mergeCell ref="L81:N81"/>
-    <mergeCell ref="O74:R74"/>
-    <mergeCell ref="O76:R76"/>
-    <mergeCell ref="S81:AO81"/>
-    <mergeCell ref="B83:K83"/>
-    <mergeCell ref="S83:AO83"/>
-    <mergeCell ref="O72:R72"/>
-    <mergeCell ref="S79:AO79"/>
-    <mergeCell ref="O83:R83"/>
-    <mergeCell ref="S82:AO82"/>
-    <mergeCell ref="O73:R73"/>
-    <mergeCell ref="S75:AO75"/>
-    <mergeCell ref="B64:AO65"/>
-    <mergeCell ref="A42:A51"/>
-    <mergeCell ref="AA62:AE62"/>
-    <mergeCell ref="T53:Y53"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="AF52:AJ52"/>
-    <mergeCell ref="AH59:AK59"/>
-    <mergeCell ref="V62:Z62"/>
-    <mergeCell ref="A12:A21"/>
-    <mergeCell ref="AF50:AJ50"/>
-    <mergeCell ref="AB57:AO57"/>
-    <mergeCell ref="AP22:AP31"/>
-    <mergeCell ref="AP2:AP11"/>
-    <mergeCell ref="A2:A11"/>
-    <mergeCell ref="AK52:AO52"/>
-    <mergeCell ref="A32:A41"/>
-    <mergeCell ref="A22:A31"/>
+    <mergeCell ref="S69:V69"/>
+    <mergeCell ref="W69:AP69"/>
+    <mergeCell ref="B64:AO66"/>
+    <mergeCell ref="AM55:AO57"/>
+    <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="AK1:AO1"/>
+    <mergeCell ref="Y54:AB54"/>
+    <mergeCell ref="AJ60:AO60"/>
+    <mergeCell ref="Y55:AB57"/>
+    <mergeCell ref="AJ59:AL59"/>
+    <mergeCell ref="O58:V58"/>
+    <mergeCell ref="AC58:AI58"/>
+    <mergeCell ref="O59:V61"/>
+    <mergeCell ref="AF1:AJ1"/>
+    <mergeCell ref="AI55:AL57"/>
+    <mergeCell ref="G1:K1"/>
     <mergeCell ref="AP12:AP21"/>
     <mergeCell ref="L62:P62"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="AF62:AJ62"/>
-    <mergeCell ref="AK51:AO51"/>
+    <mergeCell ref="W58:AB58"/>
     <mergeCell ref="AP42:AP51"/>
     <mergeCell ref="G62:K62"/>
-    <mergeCell ref="T55:AA57"/>
-    <mergeCell ref="AL59:AO59"/>
     <mergeCell ref="AP52:AP61"/>
-    <mergeCell ref="T52:Y52"/>
-    <mergeCell ref="AB56:AO56"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="L1:P1"/>
-    <mergeCell ref="G50:O50"/>
-    <mergeCell ref="T59:AG61"/>
+    <mergeCell ref="AP22:AP31"/>
+    <mergeCell ref="AP2:AP11"/>
+    <mergeCell ref="AA62:AE62"/>
+    <mergeCell ref="AJ58:AL58"/>
+    <mergeCell ref="AJ61:AO61"/>
+    <mergeCell ref="AM58:AO58"/>
+    <mergeCell ref="V62:Z62"/>
     <mergeCell ref="AP32:AP41"/>
-    <mergeCell ref="Z52:AE52"/>
+    <mergeCell ref="W59:AB61"/>
+    <mergeCell ref="AC59:AI59"/>
+    <mergeCell ref="K54:L54"/>
     <mergeCell ref="AK62:AO62"/>
-    <mergeCell ref="T51:Y51"/>
-    <mergeCell ref="AF53:AJ53"/>
-    <mergeCell ref="AB54:AO54"/>
-    <mergeCell ref="Z53:AE53"/>
-    <mergeCell ref="Z51:AE51"/>
-    <mergeCell ref="T58:AG58"/>
-    <mergeCell ref="T54:AA54"/>
-    <mergeCell ref="AF51:AJ51"/>
-    <mergeCell ref="AH60:AO60"/>
-    <mergeCell ref="AK50:AO50"/>
-    <mergeCell ref="AH61:AO61"/>
-    <mergeCell ref="AH58:AK58"/>
+    <mergeCell ref="AC54:AE54"/>
+    <mergeCell ref="R54:T54"/>
+    <mergeCell ref="AF55:AH57"/>
+    <mergeCell ref="AM54:AO54"/>
+    <mergeCell ref="O55:Q57"/>
+    <mergeCell ref="AC61:AI61"/>
+    <mergeCell ref="M54:N54"/>
+    <mergeCell ref="AI54:AL54"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="O54:Q54"/>
+    <mergeCell ref="AC55:AE57"/>
+    <mergeCell ref="AA1:AE1"/>
     <mergeCell ref="A52:A61"/>
-    <mergeCell ref="AB55:AO55"/>
-    <mergeCell ref="P50:Q50"/>
-    <mergeCell ref="AL58:AO58"/>
+    <mergeCell ref="U54:X54"/>
+    <mergeCell ref="G54:J54"/>
+    <mergeCell ref="U55:X57"/>
     <mergeCell ref="Q62:U62"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="T50:Y50"/>
-    <mergeCell ref="Z50:AE50"/>
-    <mergeCell ref="B62:F62"/>
-    <mergeCell ref="AK53:AO53"/>
-    <mergeCell ref="AA1:AE1"/>
     <mergeCell ref="V1:Z1"/>
     <mergeCell ref="J20:AG22"/>
-    <mergeCell ref="AK1:AO1"/>
-    <mergeCell ref="AF1:AJ1"/>
-    <mergeCell ref="G1:K1"/>
+    <mergeCell ref="A12:A21"/>
+    <mergeCell ref="A2:A11"/>
+    <mergeCell ref="A42:A51"/>
+    <mergeCell ref="A32:A41"/>
+    <mergeCell ref="A22:A31"/>
+    <mergeCell ref="AF54:AH54"/>
+    <mergeCell ref="AM59:AO59"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="R55:T57"/>
+    <mergeCell ref="AC60:AI60"/>
   </mergeCells>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup paperSize="8" orientation="landscape"/>
 </worksheet>
@@ -8593,67 +9721,67 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="21" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="26">
       <c r="A2" s="22" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="26">
       <c r="A3" s="22" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="26">
       <c r="A4" s="22" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="E4" s="22" t="s">
         <v>11</v>
@@ -8661,16 +9789,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="22" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="E5" s="22" t="s">
         <v>35</v>
@@ -8678,84 +9806,84 @@
     </row>
     <row r="6" spans="1:5" ht="26">
       <c r="A6" s="23" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="23" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="23" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="23" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="23" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E10" s="23" t="s">
         <v>24</v>
@@ -8763,16 +9891,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="23" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E11" s="23" t="s">
         <v>13</v>
@@ -8780,33 +9908,33 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="23" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="23" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E13" s="23" t="s">
         <v>13</v>
@@ -8814,16 +9942,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="23" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E14" s="23" t="s">
         <v>36</v>
@@ -8831,40 +9959,40 @@
     </row>
     <row r="15" spans="1:5" ht="26">
       <c r="A15" s="23" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="26">
       <c r="A16" s="23" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>